--- a/data/processed/eksposur_pontianak_0423.xlsx
+++ b/data/processed/eksposur_pontianak_0423.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14380" windowHeight="4190" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14380" windowHeight="4190" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="BMD Pemprov Kalbar" sheetId="10" r:id="rId1"/>
@@ -5711,15 +5711,6 @@
     <xf numFmtId="49" fontId="18" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5729,31 +5720,22 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5762,8 +5744,26 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="49" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -34808,7 +34808,7 @@
       <c r="B2" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="75" t="s">
+      <c r="C2" s="78" t="s">
         <v>673</v>
       </c>
       <c r="D2" s="68" t="s">
@@ -34856,7 +34856,7 @@
     <row r="3" spans="1:20" s="55" customFormat="1" ht="34.5">
       <c r="A3" s="68"/>
       <c r="B3" s="68"/>
-      <c r="C3" s="77"/>
+      <c r="C3" s="79"/>
       <c r="D3" s="68"/>
       <c r="E3" s="68"/>
       <c r="F3" s="68"/>
@@ -35855,6 +35855,13 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="K1:P1"/>
+    <mergeCell ref="T1:T3"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="Q1:S1"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:O2"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="I2:I3"/>
@@ -35866,13 +35873,6 @@
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="C2:C3"/>
-    <mergeCell ref="K1:P1"/>
-    <mergeCell ref="T1:T3"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="Q1:S1"/>
-    <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:O2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -36783,9 +36783,7 @@
       <c r="L4" s="66">
         <v>48</v>
       </c>
-      <c r="M4" s="66">
-        <v>0</v>
-      </c>
+      <c r="M4" s="66"/>
       <c r="N4" s="67"/>
       <c r="O4" s="66">
         <v>1982</v>
@@ -36827,9 +36825,7 @@
       <c r="L5" s="66">
         <v>36</v>
       </c>
-      <c r="M5" s="66">
-        <v>0</v>
-      </c>
+      <c r="M5" s="66"/>
       <c r="N5" s="67"/>
       <c r="O5" s="66">
         <v>1983</v>
@@ -36871,9 +36867,7 @@
       <c r="L6" s="66">
         <v>36</v>
       </c>
-      <c r="M6" s="66">
-        <v>0</v>
-      </c>
+      <c r="M6" s="66"/>
       <c r="N6" s="67"/>
       <c r="O6" s="66">
         <v>1983</v>
@@ -36915,9 +36909,7 @@
       <c r="L7" s="66">
         <v>48</v>
       </c>
-      <c r="M7" s="66">
-        <v>0</v>
-      </c>
+      <c r="M7" s="66"/>
       <c r="N7" s="67"/>
       <c r="O7" s="66">
         <v>1983</v>
@@ -36959,9 +36951,7 @@
       <c r="L8" s="66">
         <v>45</v>
       </c>
-      <c r="M8" s="66">
-        <v>0</v>
-      </c>
+      <c r="M8" s="66"/>
       <c r="N8" s="67"/>
       <c r="O8" s="66">
         <v>1983</v>
@@ -37003,9 +36993,7 @@
       <c r="L9" s="66">
         <v>119</v>
       </c>
-      <c r="M9" s="66">
-        <v>0</v>
-      </c>
+      <c r="M9" s="66"/>
       <c r="N9" s="67"/>
       <c r="O9" s="66">
         <v>1983</v>
@@ -37047,9 +37035,7 @@
       <c r="L10" s="66">
         <v>36</v>
       </c>
-      <c r="M10" s="66">
-        <v>0</v>
-      </c>
+      <c r="M10" s="66"/>
       <c r="N10" s="67"/>
       <c r="O10" s="66">
         <v>1983</v>
@@ -37091,9 +37077,7 @@
       <c r="L11" s="66">
         <v>70</v>
       </c>
-      <c r="M11" s="66">
-        <v>0</v>
-      </c>
+      <c r="M11" s="66"/>
       <c r="N11" s="67"/>
       <c r="O11" s="66">
         <v>1983</v>
@@ -37135,9 +37119,7 @@
       <c r="L12" s="66">
         <v>147</v>
       </c>
-      <c r="M12" s="66">
-        <v>0</v>
-      </c>
+      <c r="M12" s="66"/>
       <c r="N12" s="67"/>
       <c r="O12" s="66">
         <v>1983</v>
@@ -37179,9 +37161,7 @@
       <c r="L13" s="66">
         <v>36</v>
       </c>
-      <c r="M13" s="66">
-        <v>0</v>
-      </c>
+      <c r="M13" s="66"/>
       <c r="N13" s="67"/>
       <c r="O13" s="66">
         <v>1984</v>
@@ -37223,9 +37203,7 @@
       <c r="L14" s="66">
         <v>54</v>
       </c>
-      <c r="M14" s="66">
-        <v>0</v>
-      </c>
+      <c r="M14" s="66"/>
       <c r="N14" s="67"/>
       <c r="O14" s="66">
         <v>1984</v>
@@ -37267,9 +37245,7 @@
       <c r="L15" s="66">
         <v>36</v>
       </c>
-      <c r="M15" s="66">
-        <v>0</v>
-      </c>
+      <c r="M15" s="66"/>
       <c r="N15" s="67"/>
       <c r="O15" s="66">
         <v>1984</v>
@@ -37311,9 +37287,7 @@
       <c r="L16" s="66">
         <v>70</v>
       </c>
-      <c r="M16" s="66">
-        <v>0</v>
-      </c>
+      <c r="M16" s="66"/>
       <c r="N16" s="67"/>
       <c r="O16" s="66">
         <v>1989</v>
@@ -37355,9 +37329,7 @@
       <c r="L17" s="66">
         <v>657</v>
       </c>
-      <c r="M17" s="66">
-        <v>0</v>
-      </c>
+      <c r="M17" s="66"/>
       <c r="N17" s="67"/>
       <c r="O17" s="66">
         <v>1998</v>
@@ -37399,9 +37371,7 @@
       <c r="L18" s="66">
         <v>120</v>
       </c>
-      <c r="M18" s="66">
-        <v>0</v>
-      </c>
+      <c r="M18" s="66"/>
       <c r="N18" s="67"/>
       <c r="O18" s="66">
         <v>1976</v>
@@ -37443,9 +37413,7 @@
       <c r="L19" s="66">
         <v>144</v>
       </c>
-      <c r="M19" s="66">
-        <v>0</v>
-      </c>
+      <c r="M19" s="66"/>
       <c r="N19" s="67"/>
       <c r="O19" s="66">
         <v>1976</v>
@@ -37487,9 +37455,7 @@
       <c r="L20" s="66">
         <v>819</v>
       </c>
-      <c r="M20" s="66">
-        <v>0</v>
-      </c>
+      <c r="M20" s="66"/>
       <c r="N20" s="67"/>
       <c r="O20" s="66">
         <v>1976</v>
@@ -37531,9 +37497,7 @@
       <c r="L21" s="66">
         <v>819</v>
       </c>
-      <c r="M21" s="66">
-        <v>0</v>
-      </c>
+      <c r="M21" s="66"/>
       <c r="N21" s="67"/>
       <c r="O21" s="66">
         <v>1976</v>
@@ -37575,9 +37539,7 @@
       <c r="L22" s="66">
         <v>567</v>
       </c>
-      <c r="M22" s="66">
-        <v>0</v>
-      </c>
+      <c r="M22" s="66"/>
       <c r="N22" s="67"/>
       <c r="O22" s="66">
         <v>1976</v>
@@ -37619,9 +37581,7 @@
       <c r="L23" s="66">
         <v>504</v>
       </c>
-      <c r="M23" s="66">
-        <v>0</v>
-      </c>
+      <c r="M23" s="66"/>
       <c r="N23" s="67"/>
       <c r="O23" s="66">
         <v>1996</v>
@@ -37663,9 +37623,7 @@
       <c r="L24" s="66">
         <v>81</v>
       </c>
-      <c r="M24" s="66">
-        <v>0</v>
-      </c>
+      <c r="M24" s="66"/>
       <c r="N24" s="67"/>
       <c r="O24" s="66">
         <v>1976</v>
@@ -37707,9 +37665,7 @@
       <c r="L25" s="66">
         <v>9</v>
       </c>
-      <c r="M25" s="66">
-        <v>0</v>
-      </c>
+      <c r="M25" s="66"/>
       <c r="N25" s="67"/>
       <c r="O25" s="66">
         <v>1976</v>
@@ -37751,9 +37707,7 @@
       <c r="L26" s="66">
         <v>45</v>
       </c>
-      <c r="M26" s="66">
-        <v>0</v>
-      </c>
+      <c r="M26" s="66"/>
       <c r="N26" s="67"/>
       <c r="O26" s="66">
         <v>1982</v>
@@ -37795,9 +37749,7 @@
       <c r="L27" s="66">
         <v>45</v>
       </c>
-      <c r="M27" s="66">
-        <v>0</v>
-      </c>
+      <c r="M27" s="66"/>
       <c r="N27" s="67"/>
       <c r="O27" s="66">
         <v>1981</v>
@@ -37839,9 +37791,7 @@
       <c r="L28" s="66">
         <v>45</v>
       </c>
-      <c r="M28" s="66">
-        <v>0</v>
-      </c>
+      <c r="M28" s="66"/>
       <c r="N28" s="67"/>
       <c r="O28" s="66">
         <v>1981</v>
@@ -37883,9 +37833,7 @@
       <c r="L29" s="66">
         <v>200</v>
       </c>
-      <c r="M29" s="66">
-        <v>0</v>
-      </c>
+      <c r="M29" s="66"/>
       <c r="N29" s="67"/>
       <c r="O29" s="66">
         <v>2003</v>
@@ -37927,9 +37875,7 @@
       <c r="L30" s="66">
         <v>200</v>
       </c>
-      <c r="M30" s="66">
-        <v>0</v>
-      </c>
+      <c r="M30" s="66"/>
       <c r="N30" s="67"/>
       <c r="O30" s="66">
         <v>2006</v>
@@ -37971,9 +37917,7 @@
       <c r="L31" s="66">
         <v>54</v>
       </c>
-      <c r="M31" s="66">
-        <v>0</v>
-      </c>
+      <c r="M31" s="66"/>
       <c r="N31" s="67"/>
       <c r="O31" s="66">
         <v>1976</v>
@@ -38015,9 +37959,7 @@
       <c r="L32" s="66">
         <v>380</v>
       </c>
-      <c r="M32" s="66">
-        <v>0</v>
-      </c>
+      <c r="M32" s="66"/>
       <c r="N32" s="67"/>
       <c r="O32" s="66">
         <v>1977</v>
@@ -38059,9 +38001,7 @@
       <c r="L33" s="66">
         <v>60</v>
       </c>
-      <c r="M33" s="66">
-        <v>0</v>
-      </c>
+      <c r="M33" s="66"/>
       <c r="N33" s="67"/>
       <c r="O33" s="66">
         <v>2008</v>
@@ -38101,9 +38041,7 @@
       <c r="L34" s="66">
         <v>250</v>
       </c>
-      <c r="M34" s="66">
-        <v>0</v>
-      </c>
+      <c r="M34" s="66"/>
       <c r="N34" s="67"/>
       <c r="O34" s="66">
         <v>1997</v>
@@ -38145,9 +38083,7 @@
       <c r="L35" s="66">
         <v>70</v>
       </c>
-      <c r="M35" s="66">
-        <v>0</v>
-      </c>
+      <c r="M35" s="66"/>
       <c r="N35" s="67"/>
       <c r="O35" s="66">
         <v>1982</v>
@@ -38189,9 +38125,7 @@
       <c r="L36" s="66">
         <v>70</v>
       </c>
-      <c r="M36" s="66">
-        <v>0</v>
-      </c>
+      <c r="M36" s="66"/>
       <c r="N36" s="67"/>
       <c r="O36" s="66">
         <v>1982</v>
@@ -38233,9 +38167,7 @@
       <c r="L37" s="66">
         <v>36</v>
       </c>
-      <c r="M37" s="66">
-        <v>0</v>
-      </c>
+      <c r="M37" s="66"/>
       <c r="N37" s="67"/>
       <c r="O37" s="66">
         <v>1983</v>
@@ -38277,9 +38209,7 @@
       <c r="L38" s="66">
         <v>36</v>
       </c>
-      <c r="M38" s="66">
-        <v>0</v>
-      </c>
+      <c r="M38" s="66"/>
       <c r="N38" s="67"/>
       <c r="O38" s="66">
         <v>1984</v>
@@ -38321,9 +38251,7 @@
       <c r="L39" s="66">
         <v>120</v>
       </c>
-      <c r="M39" s="66">
-        <v>0</v>
-      </c>
+      <c r="M39" s="66"/>
       <c r="N39" s="67"/>
       <c r="O39" s="66">
         <v>1983</v>
@@ -38365,9 +38293,7 @@
       <c r="L40" s="66">
         <v>70</v>
       </c>
-      <c r="M40" s="66">
-        <v>0</v>
-      </c>
+      <c r="M40" s="66"/>
       <c r="N40" s="67"/>
       <c r="O40" s="66">
         <v>1981</v>
@@ -38409,9 +38335,7 @@
       <c r="L41" s="66">
         <v>45</v>
       </c>
-      <c r="M41" s="66">
-        <v>0</v>
-      </c>
+      <c r="M41" s="66"/>
       <c r="N41" s="67"/>
       <c r="O41" s="66">
         <v>1981</v>
@@ -38453,9 +38377,7 @@
       <c r="L42" s="66">
         <v>45</v>
       </c>
-      <c r="M42" s="66">
-        <v>0</v>
-      </c>
+      <c r="M42" s="66"/>
       <c r="N42" s="67"/>
       <c r="O42" s="66">
         <v>1982</v>
@@ -38497,9 +38419,7 @@
       <c r="L43" s="66">
         <v>45</v>
       </c>
-      <c r="M43" s="66">
-        <v>0</v>
-      </c>
+      <c r="M43" s="66"/>
       <c r="N43" s="67"/>
       <c r="O43" s="66">
         <v>1982</v>
@@ -38541,9 +38461,7 @@
       <c r="L44" s="66">
         <v>70</v>
       </c>
-      <c r="M44" s="66">
-        <v>0</v>
-      </c>
+      <c r="M44" s="66"/>
       <c r="N44" s="67"/>
       <c r="O44" s="66">
         <v>1981</v>
@@ -38585,9 +38503,7 @@
       <c r="L45" s="66">
         <v>45</v>
       </c>
-      <c r="M45" s="66">
-        <v>0</v>
-      </c>
+      <c r="M45" s="66"/>
       <c r="N45" s="67"/>
       <c r="O45" s="66">
         <v>1982</v>
@@ -38629,9 +38545,7 @@
       <c r="L46" s="66">
         <v>45</v>
       </c>
-      <c r="M46" s="66">
-        <v>0</v>
-      </c>
+      <c r="M46" s="66"/>
       <c r="N46" s="67"/>
       <c r="O46" s="66">
         <v>1982</v>
@@ -38673,9 +38587,7 @@
       <c r="L47" s="66">
         <v>45</v>
       </c>
-      <c r="M47" s="66">
-        <v>0</v>
-      </c>
+      <c r="M47" s="66"/>
       <c r="N47" s="67"/>
       <c r="O47" s="66">
         <v>1981</v>
@@ -38717,9 +38629,7 @@
       <c r="L48" s="66">
         <v>45</v>
       </c>
-      <c r="M48" s="66">
-        <v>0</v>
-      </c>
+      <c r="M48" s="66"/>
       <c r="N48" s="67"/>
       <c r="O48" s="66">
         <v>1982</v>
@@ -38761,9 +38671,7 @@
       <c r="L49" s="66">
         <v>45</v>
       </c>
-      <c r="M49" s="66">
-        <v>0</v>
-      </c>
+      <c r="M49" s="66"/>
       <c r="N49" s="67"/>
       <c r="O49" s="66">
         <v>1981</v>
@@ -38805,9 +38713,7 @@
       <c r="L50" s="66">
         <v>70</v>
       </c>
-      <c r="M50" s="66">
-        <v>0</v>
-      </c>
+      <c r="M50" s="66"/>
       <c r="N50" s="67"/>
       <c r="O50" s="66">
         <v>1981</v>
@@ -38849,9 +38755,7 @@
       <c r="L51" s="66">
         <v>45</v>
       </c>
-      <c r="M51" s="66">
-        <v>0</v>
-      </c>
+      <c r="M51" s="66"/>
       <c r="N51" s="67"/>
       <c r="O51" s="66">
         <v>1981</v>
@@ -38893,9 +38797,7 @@
       <c r="L52" s="66">
         <v>45</v>
       </c>
-      <c r="M52" s="66">
-        <v>0</v>
-      </c>
+      <c r="M52" s="66"/>
       <c r="N52" s="67"/>
       <c r="O52" s="66">
         <v>1982</v>
@@ -38937,9 +38839,7 @@
       <c r="L53" s="66">
         <v>45</v>
       </c>
-      <c r="M53" s="66">
-        <v>0</v>
-      </c>
+      <c r="M53" s="66"/>
       <c r="N53" s="67"/>
       <c r="O53" s="66">
         <v>1982</v>
@@ -38981,9 +38881,7 @@
       <c r="L54" s="66">
         <v>45</v>
       </c>
-      <c r="M54" s="66">
-        <v>0</v>
-      </c>
+      <c r="M54" s="66"/>
       <c r="N54" s="67"/>
       <c r="O54" s="66">
         <v>1981</v>
@@ -39025,9 +38923,7 @@
       <c r="L55" s="66">
         <v>45</v>
       </c>
-      <c r="M55" s="66">
-        <v>0</v>
-      </c>
+      <c r="M55" s="66"/>
       <c r="N55" s="67"/>
       <c r="O55" s="66">
         <v>1982</v>
@@ -39069,9 +38965,7 @@
       <c r="L56" s="66">
         <v>45</v>
       </c>
-      <c r="M56" s="66">
-        <v>0</v>
-      </c>
+      <c r="M56" s="66"/>
       <c r="N56" s="67"/>
       <c r="O56" s="66">
         <v>1981</v>
@@ -39113,9 +39007,7 @@
       <c r="L57" s="66">
         <v>45</v>
       </c>
-      <c r="M57" s="66">
-        <v>0</v>
-      </c>
+      <c r="M57" s="66"/>
       <c r="N57" s="67"/>
       <c r="O57" s="66">
         <v>1981</v>
@@ -39157,9 +39049,7 @@
       <c r="L58" s="66">
         <v>45</v>
       </c>
-      <c r="M58" s="66">
-        <v>0</v>
-      </c>
+      <c r="M58" s="66"/>
       <c r="N58" s="67"/>
       <c r="O58" s="66">
         <v>1981</v>
@@ -39201,9 +39091,7 @@
       <c r="L59" s="66">
         <v>45</v>
       </c>
-      <c r="M59" s="66">
-        <v>0</v>
-      </c>
+      <c r="M59" s="66"/>
       <c r="N59" s="67"/>
       <c r="O59" s="66">
         <v>1982</v>
@@ -39245,9 +39133,7 @@
       <c r="L60" s="66">
         <v>45</v>
       </c>
-      <c r="M60" s="66">
-        <v>0</v>
-      </c>
+      <c r="M60" s="66"/>
       <c r="N60" s="67"/>
       <c r="O60" s="66">
         <v>1984</v>
@@ -39289,9 +39175,7 @@
       <c r="L61" s="66">
         <v>45</v>
       </c>
-      <c r="M61" s="66">
-        <v>0</v>
-      </c>
+      <c r="M61" s="66"/>
       <c r="N61" s="67"/>
       <c r="O61" s="66">
         <v>1981</v>
@@ -39333,9 +39217,7 @@
       <c r="L62" s="66">
         <v>70</v>
       </c>
-      <c r="M62" s="66">
-        <v>0</v>
-      </c>
+      <c r="M62" s="66"/>
       <c r="N62" s="67"/>
       <c r="O62" s="66">
         <v>1981</v>
@@ -39377,9 +39259,7 @@
       <c r="L63" s="66">
         <v>70</v>
       </c>
-      <c r="M63" s="66">
-        <v>0</v>
-      </c>
+      <c r="M63" s="66"/>
       <c r="N63" s="67"/>
       <c r="O63" s="66">
         <v>1981</v>
@@ -39421,9 +39301,7 @@
       <c r="L64" s="66">
         <v>45</v>
       </c>
-      <c r="M64" s="66">
-        <v>0</v>
-      </c>
+      <c r="M64" s="66"/>
       <c r="N64" s="67"/>
       <c r="O64" s="66">
         <v>1981</v>
@@ -39465,9 +39343,7 @@
       <c r="L65" s="66">
         <v>45</v>
       </c>
-      <c r="M65" s="66">
-        <v>0</v>
-      </c>
+      <c r="M65" s="66"/>
       <c r="N65" s="67"/>
       <c r="O65" s="66">
         <v>1984</v>
@@ -39509,9 +39385,7 @@
       <c r="L66" s="66">
         <v>45</v>
       </c>
-      <c r="M66" s="66">
-        <v>0</v>
-      </c>
+      <c r="M66" s="66"/>
       <c r="N66" s="67"/>
       <c r="O66" s="66">
         <v>1984</v>
@@ -39553,9 +39427,7 @@
       <c r="L67" s="66">
         <v>36</v>
       </c>
-      <c r="M67" s="66">
-        <v>0</v>
-      </c>
+      <c r="M67" s="66"/>
       <c r="N67" s="67"/>
       <c r="O67" s="66">
         <v>1984</v>
@@ -39597,9 +39469,7 @@
       <c r="L68" s="66">
         <v>54</v>
       </c>
-      <c r="M68" s="66">
-        <v>0</v>
-      </c>
+      <c r="M68" s="66"/>
       <c r="N68" s="67"/>
       <c r="O68" s="66">
         <v>1960</v>
@@ -39641,9 +39511,7 @@
       <c r="L69" s="66">
         <v>54</v>
       </c>
-      <c r="M69" s="66">
-        <v>0</v>
-      </c>
+      <c r="M69" s="66"/>
       <c r="N69" s="67"/>
       <c r="O69" s="66">
         <v>1982</v>
@@ -39685,9 +39553,7 @@
       <c r="L70" s="66">
         <v>54</v>
       </c>
-      <c r="M70" s="66">
-        <v>0</v>
-      </c>
+      <c r="M70" s="66"/>
       <c r="N70" s="67"/>
       <c r="O70" s="66">
         <v>1982</v>
@@ -39729,9 +39595,7 @@
       <c r="L71" s="66">
         <v>189</v>
       </c>
-      <c r="M71" s="66">
-        <v>0</v>
-      </c>
+      <c r="M71" s="66"/>
       <c r="N71" s="67"/>
       <c r="O71" s="66">
         <v>1976</v>
@@ -39773,9 +39637,7 @@
       <c r="L72" s="66">
         <v>975</v>
       </c>
-      <c r="M72" s="66">
-        <v>0</v>
-      </c>
+      <c r="M72" s="66"/>
       <c r="N72" s="67"/>
       <c r="O72" s="66">
         <v>2021</v>
@@ -39815,9 +39677,7 @@
       <c r="L73" s="66">
         <v>975</v>
       </c>
-      <c r="M73" s="66">
-        <v>0</v>
-      </c>
+      <c r="M73" s="66"/>
       <c r="N73" s="67"/>
       <c r="O73" s="66">
         <v>2021</v>
@@ -39857,9 +39717,7 @@
       <c r="L74" s="66">
         <v>567</v>
       </c>
-      <c r="M74" s="66">
-        <v>0</v>
-      </c>
+      <c r="M74" s="66"/>
       <c r="N74" s="67"/>
       <c r="O74" s="66">
         <v>1976</v>
@@ -39901,9 +39759,7 @@
       <c r="L75" s="66">
         <v>690</v>
       </c>
-      <c r="M75" s="66">
-        <v>0</v>
-      </c>
+      <c r="M75" s="66"/>
       <c r="N75" s="67"/>
       <c r="O75" s="66">
         <v>1983</v>
@@ -39945,9 +39801,7 @@
       <c r="L76" s="66">
         <v>213.44</v>
       </c>
-      <c r="M76" s="66">
-        <v>0</v>
-      </c>
+      <c r="M76" s="66"/>
       <c r="N76" s="67"/>
       <c r="O76" s="66">
         <v>2010</v>
@@ -39989,9 +39843,7 @@
       <c r="L77" s="66">
         <v>4367</v>
       </c>
-      <c r="M77" s="66">
-        <v>0</v>
-      </c>
+      <c r="M77" s="66"/>
       <c r="N77" s="67"/>
       <c r="O77" s="66">
         <v>1999</v>
@@ -40033,9 +39885,7 @@
       <c r="L78" s="66">
         <v>120</v>
       </c>
-      <c r="M78" s="66">
-        <v>0</v>
-      </c>
+      <c r="M78" s="66"/>
       <c r="N78" s="67"/>
       <c r="O78" s="66">
         <v>1983</v>
@@ -40077,9 +39927,7 @@
       <c r="L79" s="66">
         <v>1227</v>
       </c>
-      <c r="M79" s="66">
-        <v>0</v>
-      </c>
+      <c r="M79" s="66"/>
       <c r="N79" s="67"/>
       <c r="O79" s="66">
         <v>2009</v>
@@ -40121,9 +39969,7 @@
       <c r="L80" s="66">
         <v>44985.599999999999</v>
       </c>
-      <c r="M80" s="66">
-        <v>0</v>
-      </c>
+      <c r="M80" s="66"/>
       <c r="N80" s="67"/>
       <c r="O80" s="66">
         <v>2013</v>
@@ -40165,9 +40011,7 @@
       <c r="L81" s="66">
         <v>945</v>
       </c>
-      <c r="M81" s="66">
-        <v>0</v>
-      </c>
+      <c r="M81" s="66"/>
       <c r="N81" s="67"/>
       <c r="O81" s="66">
         <v>1983</v>
@@ -40209,9 +40053,7 @@
       <c r="L82" s="66">
         <v>361</v>
       </c>
-      <c r="M82" s="66">
-        <v>0</v>
-      </c>
+      <c r="M82" s="66"/>
       <c r="N82" s="67"/>
       <c r="O82" s="66">
         <v>2004</v>
@@ -40253,9 +40095,7 @@
       <c r="L83" s="66">
         <v>510</v>
       </c>
-      <c r="M83" s="66">
-        <v>0</v>
-      </c>
+      <c r="M83" s="66"/>
       <c r="N83" s="67"/>
       <c r="O83" s="66">
         <v>2006</v>
@@ -40297,9 +40137,7 @@
       <c r="L84" s="66">
         <v>3822</v>
       </c>
-      <c r="M84" s="66">
-        <v>0</v>
-      </c>
+      <c r="M84" s="66"/>
       <c r="N84" s="67"/>
       <c r="O84" s="66">
         <v>2009</v>
@@ -40341,9 +40179,7 @@
       <c r="L85" s="66">
         <v>2778</v>
       </c>
-      <c r="M85" s="66">
-        <v>0</v>
-      </c>
+      <c r="M85" s="66"/>
       <c r="N85" s="67"/>
       <c r="O85" s="66">
         <v>1983</v>
@@ -40385,9 +40221,7 @@
       <c r="L86" s="66">
         <v>29</v>
       </c>
-      <c r="M86" s="66">
-        <v>0</v>
-      </c>
+      <c r="M86" s="66"/>
       <c r="N86" s="67"/>
       <c r="O86" s="66">
         <v>1996</v>
@@ -40429,9 +40263,7 @@
       <c r="L87" s="66">
         <v>24</v>
       </c>
-      <c r="M87" s="66">
-        <v>0</v>
-      </c>
+      <c r="M87" s="66"/>
       <c r="N87" s="67"/>
       <c r="O87" s="66">
         <v>2006</v>
@@ -40473,9 +40305,7 @@
       <c r="L88" s="66">
         <v>4471.0200000000004</v>
       </c>
-      <c r="M88" s="66">
-        <v>0</v>
-      </c>
+      <c r="M88" s="66"/>
       <c r="N88" s="67"/>
       <c r="O88" s="66">
         <v>2006</v>
@@ -40517,9 +40347,7 @@
       <c r="L89" s="66">
         <v>1890</v>
       </c>
-      <c r="M89" s="66">
-        <v>0</v>
-      </c>
+      <c r="M89" s="66"/>
       <c r="N89" s="67"/>
       <c r="O89" s="66">
         <v>2013</v>
@@ -40561,9 +40389,7 @@
       <c r="L90" s="66">
         <v>500</v>
       </c>
-      <c r="M90" s="66">
-        <v>0</v>
-      </c>
+      <c r="M90" s="66"/>
       <c r="N90" s="67"/>
       <c r="O90" s="66">
         <v>1983</v>
@@ -40605,9 +40431,7 @@
       <c r="L91" s="66">
         <v>2928</v>
       </c>
-      <c r="M91" s="66">
-        <v>0</v>
-      </c>
+      <c r="M91" s="66"/>
       <c r="N91" s="67"/>
       <c r="O91" s="66">
         <v>2010</v>
@@ -40649,9 +40473,7 @@
       <c r="L92" s="66">
         <v>900</v>
       </c>
-      <c r="M92" s="66">
-        <v>0</v>
-      </c>
+      <c r="M92" s="66"/>
       <c r="N92" s="67"/>
       <c r="O92" s="66">
         <v>2016</v>
@@ -40693,9 +40515,7 @@
       <c r="L93" s="66">
         <v>217</v>
       </c>
-      <c r="M93" s="66">
-        <v>0</v>
-      </c>
+      <c r="M93" s="66"/>
       <c r="N93" s="67"/>
       <c r="O93" s="66">
         <v>1999</v>
@@ -40737,9 +40557,7 @@
       <c r="L94" s="66">
         <v>127</v>
       </c>
-      <c r="M94" s="66">
-        <v>0</v>
-      </c>
+      <c r="M94" s="66"/>
       <c r="N94" s="67"/>
       <c r="O94" s="66">
         <v>1998</v>
@@ -40781,9 +40599,7 @@
       <c r="L95" s="66">
         <v>127</v>
       </c>
-      <c r="M95" s="66">
-        <v>0</v>
-      </c>
+      <c r="M95" s="66"/>
       <c r="N95" s="67"/>
       <c r="O95" s="66">
         <v>1998</v>
@@ -40825,9 +40641,7 @@
       <c r="L96" s="66">
         <v>237</v>
       </c>
-      <c r="M96" s="66">
-        <v>0</v>
-      </c>
+      <c r="M96" s="66"/>
       <c r="N96" s="67"/>
       <c r="O96" s="66">
         <v>1999</v>
@@ -40869,9 +40683,7 @@
       <c r="L97" s="66">
         <v>193</v>
       </c>
-      <c r="M97" s="66">
-        <v>0</v>
-      </c>
+      <c r="M97" s="66"/>
       <c r="N97" s="67"/>
       <c r="O97" s="66">
         <v>1999</v>
@@ -40913,9 +40725,7 @@
       <c r="L98" s="66">
         <v>127</v>
       </c>
-      <c r="M98" s="66">
-        <v>0</v>
-      </c>
+      <c r="M98" s="66"/>
       <c r="N98" s="67"/>
       <c r="O98" s="66">
         <v>1998</v>
@@ -40957,9 +40767,7 @@
       <c r="L99" s="66">
         <v>4234.3</v>
       </c>
-      <c r="M99" s="66">
-        <v>0</v>
-      </c>
+      <c r="M99" s="66"/>
       <c r="N99" s="67"/>
       <c r="O99" s="66">
         <v>2009</v>
@@ -41001,9 +40809,7 @@
       <c r="L100" s="66">
         <v>613.35</v>
       </c>
-      <c r="M100" s="66">
-        <v>0</v>
-      </c>
+      <c r="M100" s="66"/>
       <c r="N100" s="67"/>
       <c r="O100" s="66">
         <v>1984</v>
@@ -41045,9 +40851,7 @@
       <c r="L101" s="66">
         <v>9</v>
       </c>
-      <c r="M101" s="66">
-        <v>0</v>
-      </c>
+      <c r="M101" s="66"/>
       <c r="N101" s="67"/>
       <c r="O101" s="66">
         <v>2015</v>
@@ -41089,9 +40893,7 @@
       <c r="L102" s="66">
         <v>2879.82</v>
       </c>
-      <c r="M102" s="66">
-        <v>0</v>
-      </c>
+      <c r="M102" s="66"/>
       <c r="N102" s="67"/>
       <c r="O102" s="66">
         <v>2018</v>
@@ -41133,9 +40935,7 @@
       <c r="L103" s="66">
         <v>2387</v>
       </c>
-      <c r="M103" s="66">
-        <v>0</v>
-      </c>
+      <c r="M103" s="66"/>
       <c r="N103" s="67"/>
       <c r="O103" s="66">
         <v>2020</v>
@@ -41177,9 +40977,7 @@
       <c r="L104" s="66">
         <v>148.4</v>
       </c>
-      <c r="M104" s="66">
-        <v>0</v>
-      </c>
+      <c r="M104" s="66"/>
       <c r="N104" s="67"/>
       <c r="O104" s="66">
         <v>2017</v>
@@ -41221,9 +41019,7 @@
       <c r="L105" s="66">
         <v>1227</v>
       </c>
-      <c r="M105" s="66">
-        <v>0</v>
-      </c>
+      <c r="M105" s="66"/>
       <c r="N105" s="67"/>
       <c r="O105" s="66">
         <v>2009</v>
@@ -41265,9 +41061,7 @@
       <c r="L106" s="66">
         <v>6692</v>
       </c>
-      <c r="M106" s="66">
-        <v>0</v>
-      </c>
+      <c r="M106" s="66"/>
       <c r="N106" s="67"/>
       <c r="O106" s="66">
         <v>2023</v>
@@ -41307,9 +41101,7 @@
       <c r="L107" s="66">
         <v>4.0599999999999996</v>
       </c>
-      <c r="M107" s="66">
-        <v>0</v>
-      </c>
+      <c r="M107" s="66"/>
       <c r="N107" s="67"/>
       <c r="O107" s="66">
         <v>2019</v>
@@ -41349,9 +41141,7 @@
       <c r="L108" s="66">
         <v>0</v>
       </c>
-      <c r="M108" s="66">
-        <v>0</v>
-      </c>
+      <c r="M108" s="66"/>
       <c r="N108" s="67"/>
       <c r="O108" s="66">
         <v>2024</v>
@@ -41391,9 +41181,7 @@
       <c r="L109" s="66">
         <v>238</v>
       </c>
-      <c r="M109" s="66">
-        <v>0</v>
-      </c>
+      <c r="M109" s="66"/>
       <c r="N109" s="67"/>
       <c r="O109" s="66">
         <v>2024</v>
@@ -41433,9 +41221,7 @@
       <c r="L110" s="66">
         <v>306</v>
       </c>
-      <c r="M110" s="66">
-        <v>0</v>
-      </c>
+      <c r="M110" s="66"/>
       <c r="N110" s="67"/>
       <c r="O110" s="66">
         <v>2007</v>
@@ -41475,9 +41261,7 @@
       <c r="L111" s="66">
         <v>181</v>
       </c>
-      <c r="M111" s="66">
-        <v>0</v>
-      </c>
+      <c r="M111" s="66"/>
       <c r="N111" s="67"/>
       <c r="O111" s="66">
         <v>2012</v>
@@ -41519,9 +41303,7 @@
       <c r="L112" s="66">
         <v>130</v>
       </c>
-      <c r="M112" s="66">
-        <v>0</v>
-      </c>
+      <c r="M112" s="66"/>
       <c r="N112" s="67"/>
       <c r="O112" s="66">
         <v>2011</v>
@@ -41561,9 +41343,7 @@
       <c r="L113" s="66">
         <v>36</v>
       </c>
-      <c r="M113" s="66">
-        <v>0</v>
-      </c>
+      <c r="M113" s="66"/>
       <c r="N113" s="67"/>
       <c r="O113" s="66">
         <v>2009</v>
@@ -41605,9 +41385,7 @@
       <c r="L114" s="66">
         <v>168</v>
       </c>
-      <c r="M114" s="66">
-        <v>0</v>
-      </c>
+      <c r="M114" s="66"/>
       <c r="N114" s="67"/>
       <c r="O114" s="66">
         <v>2015</v>
@@ -41649,9 +41427,7 @@
       <c r="L115" s="66">
         <v>79</v>
       </c>
-      <c r="M115" s="66">
-        <v>0</v>
-      </c>
+      <c r="M115" s="66"/>
       <c r="N115" s="67"/>
       <c r="O115" s="66">
         <v>2016</v>
@@ -41693,9 +41469,7 @@
       <c r="L116" s="66">
         <v>100</v>
       </c>
-      <c r="M116" s="66">
-        <v>0</v>
-      </c>
+      <c r="M116" s="66"/>
       <c r="N116" s="67"/>
       <c r="O116" s="66">
         <v>1987</v>
@@ -41737,9 +41511,7 @@
       <c r="L117" s="66">
         <v>90</v>
       </c>
-      <c r="M117" s="66">
-        <v>0</v>
-      </c>
+      <c r="M117" s="66"/>
       <c r="N117" s="67"/>
       <c r="O117" s="66">
         <v>1984</v>
@@ -41781,9 +41553,7 @@
       <c r="L118" s="66">
         <v>3573.3</v>
       </c>
-      <c r="M118" s="66">
-        <v>0</v>
-      </c>
+      <c r="M118" s="66"/>
       <c r="N118" s="67"/>
       <c r="O118" s="66">
         <v>2014</v>
@@ -41825,9 +41595,7 @@
       <c r="L119" s="66">
         <v>143</v>
       </c>
-      <c r="M119" s="66">
-        <v>0</v>
-      </c>
+      <c r="M119" s="66"/>
       <c r="N119" s="67"/>
       <c r="O119" s="66">
         <v>2019</v>
@@ -41867,9 +41635,7 @@
       <c r="L120" s="66">
         <v>336</v>
       </c>
-      <c r="M120" s="66">
-        <v>0</v>
-      </c>
+      <c r="M120" s="66"/>
       <c r="N120" s="67"/>
       <c r="O120" s="66">
         <v>2019</v>
@@ -41909,9 +41675,7 @@
       <c r="L121" s="66">
         <v>16</v>
       </c>
-      <c r="M121" s="66">
-        <v>0</v>
-      </c>
+      <c r="M121" s="66"/>
       <c r="N121" s="67"/>
       <c r="O121" s="66">
         <v>2016</v>
@@ -41951,9 +41715,7 @@
       <c r="L122" s="66">
         <v>1285</v>
       </c>
-      <c r="M122" s="66">
-        <v>0</v>
-      </c>
+      <c r="M122" s="66"/>
       <c r="N122" s="67"/>
       <c r="O122" s="66">
         <v>2013</v>
@@ -41993,9 +41755,7 @@
       <c r="L123" s="66">
         <v>83</v>
       </c>
-      <c r="M123" s="66">
-        <v>0</v>
-      </c>
+      <c r="M123" s="66"/>
       <c r="N123" s="67"/>
       <c r="O123" s="66">
         <v>2010</v>
@@ -42037,9 +41797,7 @@
       <c r="L124" s="66">
         <v>12</v>
       </c>
-      <c r="M124" s="66">
-        <v>0</v>
-      </c>
+      <c r="M124" s="66"/>
       <c r="N124" s="67"/>
       <c r="O124" s="66">
         <v>2012</v>
@@ -42081,9 +41839,7 @@
       <c r="L125" s="66">
         <v>124</v>
       </c>
-      <c r="M125" s="66">
-        <v>0</v>
-      </c>
+      <c r="M125" s="66"/>
       <c r="N125" s="67"/>
       <c r="O125" s="66">
         <v>2014</v>
@@ -42123,9 +41879,7 @@
       <c r="L126" s="66">
         <v>131</v>
       </c>
-      <c r="M126" s="66">
-        <v>0</v>
-      </c>
+      <c r="M126" s="66"/>
       <c r="N126" s="67"/>
       <c r="O126" s="66">
         <v>2010</v>
@@ -42165,9 +41919,7 @@
       <c r="L127" s="66">
         <v>53.54</v>
       </c>
-      <c r="M127" s="66">
-        <v>0</v>
-      </c>
+      <c r="M127" s="66"/>
       <c r="N127" s="67"/>
       <c r="O127" s="66">
         <v>2016</v>
@@ -42209,9 +41961,7 @@
       <c r="L128" s="66">
         <v>20</v>
       </c>
-      <c r="M128" s="66">
-        <v>0</v>
-      </c>
+      <c r="M128" s="66"/>
       <c r="N128" s="67"/>
       <c r="O128" s="66">
         <v>2013</v>
@@ -42251,9 +42001,7 @@
       <c r="L129" s="66">
         <v>904.7</v>
       </c>
-      <c r="M129" s="66">
-        <v>0</v>
-      </c>
+      <c r="M129" s="66"/>
       <c r="N129" s="67"/>
       <c r="O129" s="66">
         <v>2019</v>
@@ -42293,9 +42041,7 @@
       <c r="L130" s="66">
         <v>138.54</v>
       </c>
-      <c r="M130" s="66">
-        <v>0</v>
-      </c>
+      <c r="M130" s="66"/>
       <c r="N130" s="67"/>
       <c r="O130" s="66">
         <v>2019</v>
@@ -42335,9 +42081,7 @@
       <c r="L131" s="66">
         <v>382.5</v>
       </c>
-      <c r="M131" s="66">
-        <v>0</v>
-      </c>
+      <c r="M131" s="66"/>
       <c r="N131" s="67"/>
       <c r="O131" s="66">
         <v>2016</v>
@@ -42379,9 +42123,7 @@
       <c r="L132" s="66">
         <v>7.9</v>
       </c>
-      <c r="M132" s="66">
-        <v>0</v>
-      </c>
+      <c r="M132" s="66"/>
       <c r="N132" s="67"/>
       <c r="O132" s="66">
         <v>2016</v>
@@ -42423,9 +42165,7 @@
       <c r="L133" s="66">
         <v>679</v>
       </c>
-      <c r="M133" s="66">
-        <v>0</v>
-      </c>
+      <c r="M133" s="66"/>
       <c r="N133" s="67"/>
       <c r="O133" s="66">
         <v>2013</v>
@@ -42467,9 +42207,7 @@
       <c r="L134" s="66">
         <v>5359</v>
       </c>
-      <c r="M134" s="66">
-        <v>0</v>
-      </c>
+      <c r="M134" s="66"/>
       <c r="N134" s="67"/>
       <c r="O134" s="66">
         <v>2009</v>
@@ -42511,9 +42249,7 @@
       <c r="L135" s="66">
         <v>300</v>
       </c>
-      <c r="M135" s="66">
-        <v>0</v>
-      </c>
+      <c r="M135" s="66"/>
       <c r="N135" s="67"/>
       <c r="O135" s="66">
         <v>2007</v>
@@ -42555,9 +42291,7 @@
       <c r="L136" s="66">
         <v>105</v>
       </c>
-      <c r="M136" s="66">
-        <v>0</v>
-      </c>
+      <c r="M136" s="66"/>
       <c r="N136" s="67"/>
       <c r="O136" s="66">
         <v>2019</v>
@@ -42597,9 +42331,7 @@
       <c r="L137" s="66">
         <v>17</v>
       </c>
-      <c r="M137" s="66">
-        <v>0</v>
-      </c>
+      <c r="M137" s="66"/>
       <c r="N137" s="67"/>
       <c r="O137" s="66">
         <v>2020</v>
@@ -42639,9 +42371,7 @@
       <c r="L138" s="66">
         <v>321</v>
       </c>
-      <c r="M138" s="66">
-        <v>0</v>
-      </c>
+      <c r="M138" s="66"/>
       <c r="N138" s="67"/>
       <c r="O138" s="66">
         <v>1995</v>
@@ -42683,9 +42413,7 @@
       <c r="L139" s="66">
         <v>100</v>
       </c>
-      <c r="M139" s="66">
-        <v>0</v>
-      </c>
+      <c r="M139" s="66"/>
       <c r="N139" s="67"/>
       <c r="O139" s="66">
         <v>2008</v>
@@ -42727,9 +42455,7 @@
       <c r="L140" s="66">
         <v>120</v>
       </c>
-      <c r="M140" s="66">
-        <v>0</v>
-      </c>
+      <c r="M140" s="66"/>
       <c r="N140" s="67"/>
       <c r="O140" s="66">
         <v>1995</v>
@@ -42771,9 +42497,7 @@
       <c r="L141" s="66">
         <v>359.21</v>
       </c>
-      <c r="M141" s="66">
-        <v>0</v>
-      </c>
+      <c r="M141" s="66"/>
       <c r="N141" s="67"/>
       <c r="O141" s="66">
         <v>1979</v>
@@ -42815,9 +42539,7 @@
       <c r="L142" s="66">
         <v>45</v>
       </c>
-      <c r="M142" s="66">
-        <v>0</v>
-      </c>
+      <c r="M142" s="66"/>
       <c r="N142" s="67"/>
       <c r="O142" s="66">
         <v>2018</v>
@@ -42859,9 +42581,7 @@
       <c r="L143" s="66">
         <v>50</v>
       </c>
-      <c r="M143" s="66">
-        <v>0</v>
-      </c>
+      <c r="M143" s="66"/>
       <c r="N143" s="67"/>
       <c r="O143" s="66">
         <v>1980</v>
@@ -42903,9 +42623,7 @@
       <c r="L144" s="66">
         <v>50</v>
       </c>
-      <c r="M144" s="66">
-        <v>0</v>
-      </c>
+      <c r="M144" s="66"/>
       <c r="N144" s="67"/>
       <c r="O144" s="66">
         <v>1985</v>
@@ -42947,9 +42665,7 @@
       <c r="L145" s="66">
         <v>45.5</v>
       </c>
-      <c r="M145" s="66">
-        <v>0</v>
-      </c>
+      <c r="M145" s="66"/>
       <c r="N145" s="67"/>
       <c r="O145" s="66">
         <v>1980</v>
@@ -42991,9 +42707,7 @@
       <c r="L146" s="66">
         <v>5</v>
       </c>
-      <c r="M146" s="66">
-        <v>0</v>
-      </c>
+      <c r="M146" s="66"/>
       <c r="N146" s="67"/>
       <c r="O146" s="66">
         <v>2019</v>
@@ -43033,9 +42747,7 @@
       <c r="L147" s="66">
         <v>100</v>
       </c>
-      <c r="M147" s="66">
-        <v>0</v>
-      </c>
+      <c r="M147" s="66"/>
       <c r="N147" s="67"/>
       <c r="O147" s="66">
         <v>1981</v>
@@ -43077,9 +42789,7 @@
       <c r="L148" s="66">
         <v>2181</v>
       </c>
-      <c r="M148" s="66">
-        <v>2</v>
-      </c>
+      <c r="M148" s="66"/>
       <c r="N148" s="67"/>
       <c r="O148" s="66">
         <v>1988</v>
@@ -43121,9 +42831,7 @@
       <c r="L149" s="66">
         <v>10</v>
       </c>
-      <c r="M149" s="66">
-        <v>1</v>
-      </c>
+      <c r="M149" s="66"/>
       <c r="N149" s="67"/>
       <c r="O149" s="66">
         <v>1988</v>
@@ -43165,9 +42873,7 @@
       <c r="L150" s="66">
         <v>27</v>
       </c>
-      <c r="M150" s="66">
-        <v>1</v>
-      </c>
+      <c r="M150" s="66"/>
       <c r="N150" s="67"/>
       <c r="O150" s="66">
         <v>1988</v>
@@ -43209,9 +42915,7 @@
       <c r="L151" s="66">
         <v>10</v>
       </c>
-      <c r="M151" s="66">
-        <v>1</v>
-      </c>
+      <c r="M151" s="66"/>
       <c r="N151" s="67"/>
       <c r="O151" s="66">
         <v>1988</v>
@@ -43253,9 +42957,7 @@
       <c r="L152" s="66">
         <v>180</v>
       </c>
-      <c r="M152" s="66">
-        <v>0</v>
-      </c>
+      <c r="M152" s="66"/>
       <c r="N152" s="67"/>
       <c r="O152" s="66">
         <v>2009</v>
@@ -43297,9 +42999,7 @@
       <c r="L153" s="66">
         <v>2320</v>
       </c>
-      <c r="M153" s="66">
-        <v>0</v>
-      </c>
+      <c r="M153" s="66"/>
       <c r="N153" s="67"/>
       <c r="O153" s="66">
         <v>2009</v>
@@ -43341,9 +43041,7 @@
       <c r="L154" s="66">
         <v>574</v>
       </c>
-      <c r="M154" s="66">
-        <v>0</v>
-      </c>
+      <c r="M154" s="66"/>
       <c r="N154" s="67"/>
       <c r="O154" s="66">
         <v>2014</v>
@@ -43385,9 +43083,7 @@
       <c r="L155" s="66">
         <v>28</v>
       </c>
-      <c r="M155" s="66">
-        <v>0</v>
-      </c>
+      <c r="M155" s="66"/>
       <c r="N155" s="67"/>
       <c r="O155" s="66">
         <v>2014</v>
@@ -43429,9 +43125,7 @@
       <c r="L156" s="66">
         <v>70</v>
       </c>
-      <c r="M156" s="66">
-        <v>0</v>
-      </c>
+      <c r="M156" s="66"/>
       <c r="N156" s="67"/>
       <c r="O156" s="66">
         <v>1979</v>
@@ -43473,9 +43167,7 @@
       <c r="L157" s="66">
         <v>80</v>
       </c>
-      <c r="M157" s="66">
-        <v>0</v>
-      </c>
+      <c r="M157" s="66"/>
       <c r="N157" s="67"/>
       <c r="O157" s="66">
         <v>2006</v>
@@ -43517,9 +43209,7 @@
       <c r="L158" s="66">
         <v>80</v>
       </c>
-      <c r="M158" s="66">
-        <v>0</v>
-      </c>
+      <c r="M158" s="66"/>
       <c r="N158" s="67"/>
       <c r="O158" s="66">
         <v>1996</v>
@@ -43561,9 +43251,7 @@
       <c r="L159" s="66">
         <v>432</v>
       </c>
-      <c r="M159" s="66">
-        <v>0</v>
-      </c>
+      <c r="M159" s="66"/>
       <c r="N159" s="67"/>
       <c r="O159" s="66">
         <v>2009</v>
@@ -43605,9 +43293,7 @@
       <c r="L160" s="66">
         <v>290</v>
       </c>
-      <c r="M160" s="66">
-        <v>0</v>
-      </c>
+      <c r="M160" s="66"/>
       <c r="N160" s="67"/>
       <c r="O160" s="66">
         <v>1983</v>
@@ -43649,9 +43335,7 @@
       <c r="L161" s="66">
         <v>120</v>
       </c>
-      <c r="M161" s="66">
-        <v>0</v>
-      </c>
+      <c r="M161" s="66"/>
       <c r="N161" s="67"/>
       <c r="O161" s="66">
         <v>1982</v>
@@ -43693,9 +43377,7 @@
       <c r="L162" s="66">
         <v>120</v>
       </c>
-      <c r="M162" s="66">
-        <v>0</v>
-      </c>
+      <c r="M162" s="66"/>
       <c r="N162" s="67"/>
       <c r="O162" s="66">
         <v>1986</v>
@@ -43737,9 +43419,7 @@
       <c r="L163" s="66">
         <v>400</v>
       </c>
-      <c r="M163" s="66">
-        <v>0</v>
-      </c>
+      <c r="M163" s="66"/>
       <c r="N163" s="67"/>
       <c r="O163" s="66">
         <v>1984</v>
@@ -43781,9 +43461,7 @@
       <c r="L164" s="66">
         <v>139</v>
       </c>
-      <c r="M164" s="66">
-        <v>0</v>
-      </c>
+      <c r="M164" s="66"/>
       <c r="N164" s="67"/>
       <c r="O164" s="66">
         <v>1959</v>
@@ -43825,9 +43503,7 @@
       <c r="L165" s="66">
         <v>137.25</v>
       </c>
-      <c r="M165" s="66">
-        <v>0</v>
-      </c>
+      <c r="M165" s="66"/>
       <c r="N165" s="67"/>
       <c r="O165" s="66">
         <v>1984</v>
@@ -43869,9 +43545,7 @@
       <c r="L166" s="66">
         <v>134.6</v>
       </c>
-      <c r="M166" s="66">
-        <v>0</v>
-      </c>
+      <c r="M166" s="66"/>
       <c r="N166" s="67"/>
       <c r="O166" s="66">
         <v>1952</v>
@@ -43913,9 +43587,7 @@
       <c r="L167" s="66">
         <v>210.75</v>
       </c>
-      <c r="M167" s="66">
-        <v>0</v>
-      </c>
+      <c r="M167" s="66"/>
       <c r="N167" s="67"/>
       <c r="O167" s="66">
         <v>1980</v>
@@ -43957,9 +43629,7 @@
       <c r="L168" s="66">
         <v>101</v>
       </c>
-      <c r="M168" s="66">
-        <v>0</v>
-      </c>
+      <c r="M168" s="66"/>
       <c r="N168" s="67"/>
       <c r="O168" s="66">
         <v>1970</v>
@@ -44001,9 +43671,7 @@
       <c r="L169" s="66">
         <v>205.1</v>
       </c>
-      <c r="M169" s="66">
-        <v>0</v>
-      </c>
+      <c r="M169" s="66"/>
       <c r="N169" s="67"/>
       <c r="O169" s="66">
         <v>1952</v>
@@ -44045,9 +43713,7 @@
       <c r="L170" s="66">
         <v>144</v>
       </c>
-      <c r="M170" s="66">
-        <v>0</v>
-      </c>
+      <c r="M170" s="66"/>
       <c r="N170" s="67"/>
       <c r="O170" s="66">
         <v>1989</v>
@@ -44089,9 +43755,7 @@
       <c r="L171" s="66">
         <v>82.49</v>
       </c>
-      <c r="M171" s="66">
-        <v>0</v>
-      </c>
+      <c r="M171" s="66"/>
       <c r="N171" s="67"/>
       <c r="O171" s="66">
         <v>1984</v>
@@ -44133,9 +43797,7 @@
       <c r="L172" s="66">
         <v>72</v>
       </c>
-      <c r="M172" s="66">
-        <v>0</v>
-      </c>
+      <c r="M172" s="66"/>
       <c r="N172" s="67"/>
       <c r="O172" s="66">
         <v>1991</v>
@@ -44177,9 +43839,7 @@
       <c r="L173" s="66">
         <v>90.82</v>
       </c>
-      <c r="M173" s="66">
-        <v>0</v>
-      </c>
+      <c r="M173" s="66"/>
       <c r="N173" s="67"/>
       <c r="O173" s="66">
         <v>1991</v>
@@ -44221,9 +43881,7 @@
       <c r="L174" s="66">
         <v>67</v>
       </c>
-      <c r="M174" s="66">
-        <v>0</v>
-      </c>
+      <c r="M174" s="66"/>
       <c r="N174" s="67"/>
       <c r="O174" s="66">
         <v>1970</v>
@@ -44265,9 +43923,7 @@
       <c r="L175" s="66">
         <v>82.49</v>
       </c>
-      <c r="M175" s="66">
-        <v>0</v>
-      </c>
+      <c r="M175" s="66"/>
       <c r="N175" s="67"/>
       <c r="O175" s="66">
         <v>1984</v>
@@ -44309,9 +43965,7 @@
       <c r="L176" s="66">
         <v>72</v>
       </c>
-      <c r="M176" s="66">
-        <v>0</v>
-      </c>
+      <c r="M176" s="66"/>
       <c r="N176" s="67"/>
       <c r="O176" s="66">
         <v>1991</v>
@@ -44353,9 +44007,7 @@
       <c r="L177" s="66">
         <v>1800</v>
       </c>
-      <c r="M177" s="66">
-        <v>0</v>
-      </c>
+      <c r="M177" s="66"/>
       <c r="N177" s="67"/>
       <c r="O177" s="66">
         <v>1986</v>
@@ -44395,9 +44047,7 @@
       <c r="L178" s="66">
         <v>300</v>
       </c>
-      <c r="M178" s="66">
-        <v>0</v>
-      </c>
+      <c r="M178" s="66"/>
       <c r="N178" s="67"/>
       <c r="O178" s="66">
         <v>1996</v>
@@ -44437,9 +44087,7 @@
       <c r="L179" s="66">
         <v>270</v>
       </c>
-      <c r="M179" s="66">
-        <v>0</v>
-      </c>
+      <c r="M179" s="66"/>
       <c r="N179" s="67"/>
       <c r="O179" s="66">
         <v>1986</v>
@@ -44479,9 +44127,7 @@
       <c r="L180" s="66">
         <v>14</v>
       </c>
-      <c r="M180" s="66">
-        <v>0</v>
-      </c>
+      <c r="M180" s="66"/>
       <c r="N180" s="67"/>
       <c r="O180" s="66">
         <v>2015</v>
@@ -44521,9 +44167,7 @@
       <c r="L181" s="66">
         <v>656</v>
       </c>
-      <c r="M181" s="66">
-        <v>0</v>
-      </c>
+      <c r="M181" s="66"/>
       <c r="N181" s="67"/>
       <c r="O181" s="66">
         <v>1992</v>
@@ -44563,9 +44207,7 @@
       <c r="L182" s="66">
         <v>104</v>
       </c>
-      <c r="M182" s="66">
-        <v>0</v>
-      </c>
+      <c r="M182" s="66"/>
       <c r="N182" s="67"/>
       <c r="O182" s="66">
         <v>1953</v>
@@ -44607,9 +44249,7 @@
       <c r="L183" s="66">
         <v>70</v>
       </c>
-      <c r="M183" s="66">
-        <v>0</v>
-      </c>
+      <c r="M183" s="66"/>
       <c r="N183" s="67"/>
       <c r="O183" s="66">
         <v>1979</v>
@@ -44651,9 +44291,7 @@
       <c r="L184" s="66">
         <v>70</v>
       </c>
-      <c r="M184" s="66">
-        <v>0</v>
-      </c>
+      <c r="M184" s="66"/>
       <c r="N184" s="67"/>
       <c r="O184" s="66">
         <v>1979</v>
@@ -44695,9 +44333,7 @@
       <c r="L185" s="66">
         <v>70</v>
       </c>
-      <c r="M185" s="66">
-        <v>0</v>
-      </c>
+      <c r="M185" s="66"/>
       <c r="N185" s="67"/>
       <c r="O185" s="66">
         <v>1979</v>
@@ -44739,9 +44375,7 @@
       <c r="L186" s="66">
         <v>70</v>
       </c>
-      <c r="M186" s="66">
-        <v>0</v>
-      </c>
+      <c r="M186" s="66"/>
       <c r="N186" s="67"/>
       <c r="O186" s="66">
         <v>1979</v>
@@ -44783,9 +44417,7 @@
       <c r="L187" s="66">
         <v>70</v>
       </c>
-      <c r="M187" s="66">
-        <v>0</v>
-      </c>
+      <c r="M187" s="66"/>
       <c r="N187" s="67"/>
       <c r="O187" s="66">
         <v>1979</v>
@@ -44827,9 +44459,7 @@
       <c r="L188" s="66">
         <v>70</v>
       </c>
-      <c r="M188" s="66">
-        <v>0</v>
-      </c>
+      <c r="M188" s="66"/>
       <c r="N188" s="67"/>
       <c r="O188" s="66">
         <v>1979</v>
@@ -44871,9 +44501,7 @@
       <c r="L189" s="66">
         <v>70</v>
       </c>
-      <c r="M189" s="66">
-        <v>0</v>
-      </c>
+      <c r="M189" s="66"/>
       <c r="N189" s="67"/>
       <c r="O189" s="66">
         <v>1979</v>
@@ -44915,9 +44543,7 @@
       <c r="L190" s="66">
         <v>70</v>
       </c>
-      <c r="M190" s="66">
-        <v>0</v>
-      </c>
+      <c r="M190" s="66"/>
       <c r="N190" s="67"/>
       <c r="O190" s="66">
         <v>1979</v>
@@ -44959,9 +44585,7 @@
       <c r="L191" s="66">
         <v>268</v>
       </c>
-      <c r="M191" s="66">
-        <v>0</v>
-      </c>
+      <c r="M191" s="66"/>
       <c r="N191" s="67"/>
       <c r="O191" s="66">
         <v>1999</v>
@@ -45003,9 +44627,7 @@
       <c r="L192" s="66">
         <v>839</v>
       </c>
-      <c r="M192" s="66">
-        <v>0</v>
-      </c>
+      <c r="M192" s="66"/>
       <c r="N192" s="67"/>
       <c r="O192" s="66">
         <v>1984</v>
@@ -45047,9 +44669,7 @@
       <c r="L193" s="66">
         <v>70</v>
       </c>
-      <c r="M193" s="66">
-        <v>0</v>
-      </c>
+      <c r="M193" s="66"/>
       <c r="N193" s="67"/>
       <c r="O193" s="66">
         <v>1983</v>
@@ -45091,9 +44711,7 @@
       <c r="L194" s="66">
         <v>296</v>
       </c>
-      <c r="M194" s="66">
-        <v>0</v>
-      </c>
+      <c r="M194" s="66"/>
       <c r="N194" s="67"/>
       <c r="O194" s="66">
         <v>1960</v>
@@ -45135,9 +44753,7 @@
       <c r="L195" s="66">
         <v>70</v>
       </c>
-      <c r="M195" s="66">
-        <v>0</v>
-      </c>
+      <c r="M195" s="66"/>
       <c r="N195" s="67"/>
       <c r="O195" s="66">
         <v>1994</v>
@@ -45179,9 +44795,7 @@
       <c r="L196" s="66">
         <v>70</v>
       </c>
-      <c r="M196" s="66">
-        <v>0</v>
-      </c>
+      <c r="M196" s="66"/>
       <c r="N196" s="67"/>
       <c r="O196" s="66">
         <v>1999</v>
@@ -45223,9 +44837,7 @@
       <c r="L197" s="66">
         <v>70</v>
       </c>
-      <c r="M197" s="66">
-        <v>0</v>
-      </c>
+      <c r="M197" s="66"/>
       <c r="N197" s="67"/>
       <c r="O197" s="66">
         <v>1999</v>
@@ -45267,9 +44879,7 @@
       <c r="L198" s="66">
         <v>70</v>
       </c>
-      <c r="M198" s="66">
-        <v>0</v>
-      </c>
+      <c r="M198" s="66"/>
       <c r="N198" s="67"/>
       <c r="O198" s="66">
         <v>1999</v>
@@ -45311,9 +44921,7 @@
       <c r="L199" s="66">
         <v>70</v>
       </c>
-      <c r="M199" s="66">
-        <v>0</v>
-      </c>
+      <c r="M199" s="66"/>
       <c r="N199" s="67"/>
       <c r="O199" s="66">
         <v>1999</v>
@@ -45355,9 +44963,7 @@
       <c r="L200" s="66">
         <v>260</v>
       </c>
-      <c r="M200" s="66">
-        <v>0</v>
-      </c>
+      <c r="M200" s="66"/>
       <c r="N200" s="67"/>
       <c r="O200" s="66">
         <v>1996</v>
@@ -45397,9 +45003,7 @@
       <c r="L201" s="66">
         <v>70</v>
       </c>
-      <c r="M201" s="66">
-        <v>0</v>
-      </c>
+      <c r="M201" s="66"/>
       <c r="N201" s="67"/>
       <c r="O201" s="66">
         <v>2009</v>
@@ -45441,9 +45045,7 @@
       <c r="L202" s="66">
         <v>960</v>
       </c>
-      <c r="M202" s="66">
-        <v>0</v>
-      </c>
+      <c r="M202" s="66"/>
       <c r="N202" s="67"/>
       <c r="O202" s="66">
         <v>2022</v>
@@ -45464,6 +45066,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="J2:K2"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="J1:O1"/>
@@ -45480,7 +45083,6 @@
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:K2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -45497,87 +45099,87 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="60" customFormat="1" ht="36" customHeight="1">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="78" t="s">
+      <c r="B1" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="78" t="s">
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="79"/>
-      <c r="O1" s="80"/>
-      <c r="P1" s="78" t="s">
+      <c r="K1" s="76"/>
+      <c r="L1" s="76"/>
+      <c r="M1" s="76"/>
+      <c r="N1" s="76"/>
+      <c r="O1" s="77"/>
+      <c r="P1" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="Q1" s="80"/>
+      <c r="Q1" s="77"/>
     </row>
     <row r="2" spans="1:17" s="60" customFormat="1" ht="36" customHeight="1">
-      <c r="A2" s="76"/>
-      <c r="B2" s="75" t="s">
+      <c r="A2" s="80"/>
+      <c r="B2" s="78" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="75" t="s">
+      <c r="C2" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="75" t="s">
+      <c r="D2" s="78" t="s">
         <v>583</v>
       </c>
-      <c r="E2" s="75" t="s">
+      <c r="E2" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="75" t="s">
+      <c r="F2" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="75" t="s">
+      <c r="G2" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="75" t="s">
+      <c r="H2" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="75" t="s">
+      <c r="I2" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="78" t="s">
+      <c r="J2" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="80"/>
-      <c r="L2" s="78" t="s">
+      <c r="K2" s="77"/>
+      <c r="L2" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="79"/>
-      <c r="N2" s="80"/>
+      <c r="M2" s="76"/>
+      <c r="N2" s="77"/>
       <c r="O2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="75" t="s">
+      <c r="P2" s="78" t="s">
         <v>584</v>
       </c>
-      <c r="Q2" s="75" t="s">
+      <c r="Q2" s="78" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:17" s="60" customFormat="1" ht="69">
-      <c r="A3" s="77"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
+      <c r="A3" s="79"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="79"/>
       <c r="J3" s="7" t="s">
         <v>585</v>
       </c>
@@ -45596,8 +45198,8 @@
       <c r="O3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
+      <c r="P3" s="79"/>
+      <c r="Q3" s="79"/>
     </row>
     <row r="4" spans="1:17" ht="34.5">
       <c r="A4" s="8">
@@ -47839,12 +47441,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="J1:O1"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="P2:P3"/>
-    <mergeCell ref="Q2:Q3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="B2:B3"/>
@@ -47855,6 +47451,12 @@
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="D2:D3"/>
+    <mergeCell ref="J1:O1"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="P2:P3"/>
+    <mergeCell ref="Q2:Q3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -48681,7 +48283,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="103.5">
+    <row r="18" spans="1:18" ht="115">
       <c r="A18" s="8">
         <v>15</v>
       </c>
@@ -49031,7 +48633,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="92">
+    <row r="25" spans="1:18" ht="103.5">
       <c r="A25" s="8">
         <v>22</v>
       </c>
@@ -50470,7 +50072,7 @@
       <c r="B2" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="75" t="s">
+      <c r="C2" s="78" t="s">
         <v>673</v>
       </c>
       <c r="D2" s="68" t="s">
@@ -50514,7 +50116,7 @@
     <row r="3" spans="1:18" ht="57.5">
       <c r="A3" s="68"/>
       <c r="B3" s="68"/>
-      <c r="C3" s="77"/>
+      <c r="C3" s="79"/>
       <c r="D3" s="68"/>
       <c r="E3" s="68"/>
       <c r="F3" s="68"/>
@@ -50815,6 +50417,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="Q2:Q3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="R1:R3"/>
     <mergeCell ref="A1:A3"/>
@@ -50831,7 +50434,6 @@
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="P2:P3"/>
-    <mergeCell ref="Q2:Q3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -67884,6 +67486,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="V1:V3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="J1:O1"/>
@@ -67900,11 +67507,6 @@
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="C2:C3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="V1:V3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -67924,77 +67526,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" s="27" customFormat="1">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="89" t="s">
+      <c r="B1" s="86" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="82"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="84"/>
-      <c r="J1" s="89" t="s">
+      <c r="C1" s="91"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
+      <c r="H1" s="87"/>
+      <c r="I1" s="90"/>
+      <c r="J1" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
-      <c r="M1" s="83"/>
-      <c r="N1" s="83"/>
-      <c r="O1" s="84"/>
-      <c r="P1" s="89" t="s">
+      <c r="K1" s="87"/>
+      <c r="L1" s="87"/>
+      <c r="M1" s="87"/>
+      <c r="N1" s="87"/>
+      <c r="O1" s="90"/>
+      <c r="P1" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="Q1" s="83"/>
+      <c r="Q1" s="87"/>
       <c r="R1" s="68" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:18" s="27" customFormat="1" ht="36" customHeight="1">
-      <c r="A2" s="87"/>
-      <c r="B2" s="85" t="s">
+      <c r="A2" s="92"/>
+      <c r="B2" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="85" t="s">
+      <c r="C2" s="82" t="s">
         <v>673</v>
       </c>
-      <c r="D2" s="85" t="s">
+      <c r="D2" s="82" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="92" t="s">
+      <c r="E2" s="89" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="92" t="s">
+      <c r="F2" s="89" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="85" t="s">
+      <c r="G2" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="85" t="s">
+      <c r="H2" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="85" t="s">
+      <c r="I2" s="82" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="89" t="s">
+      <c r="J2" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="84"/>
-      <c r="L2" s="82" t="s">
+      <c r="K2" s="90"/>
+      <c r="L2" s="91" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="83"/>
-      <c r="N2" s="84"/>
+      <c r="M2" s="87"/>
+      <c r="N2" s="90"/>
       <c r="O2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="85" t="s">
+      <c r="P2" s="82" t="s">
         <v>584</v>
       </c>
-      <c r="Q2" s="90" t="s">
+      <c r="Q2" s="84" t="s">
         <v>18</v>
       </c>
       <c r="R2" s="68"/>
@@ -68002,7 +67604,7 @@
     <row r="3" spans="1:18" s="27" customFormat="1" ht="69">
       <c r="A3" s="88"/>
       <c r="B3" s="88"/>
-      <c r="C3" s="86"/>
+      <c r="C3" s="83"/>
       <c r="D3" s="88"/>
       <c r="E3" s="88"/>
       <c r="F3" s="88"/>
@@ -68027,8 +67629,8 @@
       <c r="O3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="P3" s="86"/>
-      <c r="Q3" s="91"/>
+      <c r="P3" s="83"/>
+      <c r="Q3" s="85"/>
       <c r="R3" s="68"/>
     </row>
     <row r="4" spans="1:18" ht="34.5">
@@ -71283,6 +70885,9 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="J1:O1"/>
     <mergeCell ref="R1:R3"/>
     <mergeCell ref="P2:P3"/>
     <mergeCell ref="Q2:Q3"/>
@@ -71297,9 +70902,6 @@
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="C2:C3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="J1:O1"/>
   </mergeCells>
   <phoneticPr fontId="22" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -71352,7 +70954,7 @@
       <c r="B2" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="75" t="s">
+      <c r="C2" s="78" t="s">
         <v>673</v>
       </c>
       <c r="D2" s="68" t="s">
@@ -71385,10 +70987,10 @@
       <c r="O2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="75" t="s">
+      <c r="P2" s="78" t="s">
         <v>584</v>
       </c>
-      <c r="Q2" s="75" t="s">
+      <c r="Q2" s="78" t="s">
         <v>18</v>
       </c>
       <c r="R2" s="68"/>
@@ -71396,7 +70998,7 @@
     <row r="3" spans="1:18" s="32" customFormat="1" ht="57.5">
       <c r="A3" s="93"/>
       <c r="B3" s="93"/>
-      <c r="C3" s="77"/>
+      <c r="C3" s="79"/>
       <c r="D3" s="93"/>
       <c r="E3" s="93"/>
       <c r="F3" s="93"/>
@@ -71421,8 +71023,8 @@
       <c r="O3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
+      <c r="P3" s="79"/>
+      <c r="Q3" s="79"/>
       <c r="R3" s="68"/>
     </row>
     <row r="4" spans="1:18" ht="34.5">
@@ -71715,6 +71317,9 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="J1:O1"/>
     <mergeCell ref="R1:R3"/>
     <mergeCell ref="P2:P3"/>
     <mergeCell ref="Q2:Q3"/>
@@ -71729,9 +71334,6 @@
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="C2:C3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="J1:O1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -71939,15 +71541,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="15954fb3-4959-4f5b-ae14-d7aa01180869">
@@ -71956,6 +71549,15 @@
     <TaxCatchAll xmlns="4ce1a36b-806a-4732-b893-33b689d3fa0c" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -71978,14 +71580,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{513001CF-EFDC-47ED-A578-E98A932356EC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54AE2609-C9F0-494C-8358-7B12B3AE88B2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -71994,4 +71588,12 @@
     <ds:schemaRef ds:uri="4ce1a36b-806a-4732-b893-33b689d3fa0c"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{513001CF-EFDC-47ED-A578-E98A932356EC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/processed/eksposur_pontianak_0423.xlsx
+++ b/data/processed/eksposur_pontianak_0423.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" firstSheet="2" activeTab="3"/>
+    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" firstSheet="2" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="BMD Pemprov Kalbar" sheetId="10" r:id="rId1"/>
@@ -24,6 +24,9 @@
     <sheet name="Drainage" sheetId="6" r:id="rId10"/>
     <sheet name="Infrastructure" sheetId="11" r:id="rId11"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Education!$I$1:$I$317</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -45,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9907" uniqueCount="1528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9907" uniqueCount="1527">
   <si>
     <t>No</t>
   </si>
@@ -3213,9 +3216,6 @@
   </si>
   <si>
     <t>± 0,1 - 1.5 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Pontianak Utara</t>
   </si>
   <si>
     <t>± 1.757 m²</t>
@@ -5732,6 +5732,15 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5746,15 +5755,6 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -35364,6 +35364,10 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:K1"/>
+    <mergeCell ref="L1:Q1"/>
+    <mergeCell ref="R1:S1"/>
     <mergeCell ref="T1:T3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="F2:F3"/>
@@ -35377,10 +35381,6 @@
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="C2:C3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:K1"/>
-    <mergeCell ref="L1:Q1"/>
-    <mergeCell ref="R1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -35413,7 +35413,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="75" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="C1" s="75"/>
       <c r="D1" s="75"/>
@@ -35449,7 +35449,7 @@
         <v>674</v>
       </c>
       <c r="D2" s="75" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="E2" s="75" t="s">
         <v>6</v>
@@ -35461,7 +35461,7 @@
         <v>10</v>
       </c>
       <c r="H2" s="75" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="I2" s="75" t="s">
         <v>12</v>
@@ -35482,10 +35482,10 @@
         <v>16</v>
       </c>
       <c r="Q2" s="75" t="s">
+        <v>1464</v>
+      </c>
+      <c r="R2" s="75" t="s">
         <v>1465</v>
-      </c>
-      <c r="R2" s="75" t="s">
-        <v>1466</v>
       </c>
       <c r="S2" s="75"/>
       <c r="T2" s="75"/>
@@ -35511,20 +35511,20 @@
         <v>21</v>
       </c>
       <c r="N3" s="7" t="s">
+        <v>1466</v>
+      </c>
+      <c r="O3" s="7" t="s">
         <v>1467</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="P3" s="7" t="s">
         <v>1468</v>
-      </c>
-      <c r="P3" s="7" t="s">
-        <v>1469</v>
       </c>
       <c r="Q3" s="75"/>
       <c r="R3" s="7" t="s">
+        <v>1469</v>
+      </c>
+      <c r="S3" s="7" t="s">
         <v>1470</v>
-      </c>
-      <c r="S3" s="7" t="s">
-        <v>1471</v>
       </c>
       <c r="T3" s="75"/>
     </row>
@@ -35534,13 +35534,13 @@
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="8" t="s">
+        <v>1471</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>1472</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="E4" s="9" t="s">
         <v>1473</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>1474</v>
       </c>
       <c r="F4" s="9">
         <v>-2.6519999999999998E-2</v>
@@ -35556,17 +35556,17 @@
         <v>29</v>
       </c>
       <c r="K4" s="9" t="s">
+        <v>1474</v>
+      </c>
+      <c r="L4" s="9" t="s">
         <v>1475</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>1476</v>
       </c>
       <c r="M4" s="9"/>
       <c r="N4" s="52">
         <v>825</v>
       </c>
       <c r="O4" s="28" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="P4" s="9">
         <v>2025</v>
@@ -35577,7 +35577,7 @@
       <c r="R4" s="9"/>
       <c r="S4" s="9"/>
       <c r="T4" s="9" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="34.5">
@@ -35586,10 +35586,10 @@
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="8" t="s">
+        <v>1471</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>1472</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>1473</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>42</v>
@@ -35608,17 +35608,17 @@
         <v>43</v>
       </c>
       <c r="K5" s="9" t="s">
+        <v>1474</v>
+      </c>
+      <c r="L5" s="9" t="s">
         <v>1475</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>1476</v>
       </c>
       <c r="M5" s="9"/>
       <c r="N5" s="52">
         <v>4500</v>
       </c>
       <c r="O5" s="28" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="P5" s="9">
         <v>2025</v>
@@ -35629,7 +35629,7 @@
       <c r="R5" s="9"/>
       <c r="S5" s="9"/>
       <c r="T5" s="9" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="34.5">
@@ -35638,13 +35638,13 @@
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="8" t="s">
+        <v>1471</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>1472</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>1473</v>
-      </c>
       <c r="E6" s="9" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="F6" s="9">
         <v>-5.6816999999999999E-2</v>
@@ -35660,17 +35660,17 @@
         <v>43</v>
       </c>
       <c r="K6" s="9" t="s">
+        <v>1474</v>
+      </c>
+      <c r="L6" s="9" t="s">
         <v>1475</v>
-      </c>
-      <c r="L6" s="9" t="s">
-        <v>1476</v>
       </c>
       <c r="M6" s="9"/>
       <c r="N6" s="52">
         <v>3800</v>
       </c>
       <c r="O6" s="28" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="P6" s="9">
         <v>2025</v>
@@ -35681,7 +35681,7 @@
       <c r="R6" s="9"/>
       <c r="S6" s="9"/>
       <c r="T6" s="9" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="34.5">
@@ -35690,13 +35690,13 @@
       </c>
       <c r="B7" s="9"/>
       <c r="C7" s="8" t="s">
+        <v>1471</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>1472</v>
       </c>
-      <c r="D7" s="9" t="s">
-        <v>1473</v>
-      </c>
       <c r="E7" s="9" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="F7" s="9">
         <v>-6.4637E-2</v>
@@ -35712,17 +35712,17 @@
         <v>43</v>
       </c>
       <c r="K7" s="9" t="s">
+        <v>1474</v>
+      </c>
+      <c r="L7" s="9" t="s">
         <v>1475</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>1476</v>
       </c>
       <c r="M7" s="9"/>
       <c r="N7" s="52">
         <v>4600</v>
       </c>
       <c r="O7" s="28" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="P7" s="9">
         <v>2025</v>
@@ -35733,7 +35733,7 @@
       <c r="R7" s="9"/>
       <c r="S7" s="9"/>
       <c r="T7" s="9" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="34.5">
@@ -35742,13 +35742,13 @@
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="8" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>1472</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>1480</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>1473</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>1481</v>
       </c>
       <c r="F8" s="9">
         <v>-7.3205999999999993E-2</v>
@@ -35758,23 +35758,23 @@
       </c>
       <c r="H8" s="9"/>
       <c r="I8" s="9" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="J8" s="9" t="s">
         <v>43</v>
       </c>
       <c r="K8" s="9" t="s">
+        <v>1474</v>
+      </c>
+      <c r="L8" s="9" t="s">
         <v>1475</v>
-      </c>
-      <c r="L8" s="9" t="s">
-        <v>1476</v>
       </c>
       <c r="M8" s="9"/>
       <c r="N8" s="52">
         <v>6300</v>
       </c>
       <c r="O8" s="28" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="P8" s="9">
         <v>2025</v>
@@ -35785,7 +35785,7 @@
       <c r="R8" s="9"/>
       <c r="S8" s="9"/>
       <c r="T8" s="9" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="34.5">
@@ -35794,13 +35794,13 @@
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="8" t="s">
+        <v>1471</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>1472</v>
       </c>
-      <c r="D9" s="9" t="s">
-        <v>1473</v>
-      </c>
       <c r="E9" s="9" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="F9" s="9">
         <v>-6.6999000000000003E-2</v>
@@ -35816,17 +35816,17 @@
         <v>43</v>
       </c>
       <c r="K9" s="9" t="s">
+        <v>1474</v>
+      </c>
+      <c r="L9" s="9" t="s">
         <v>1475</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>1476</v>
       </c>
       <c r="M9" s="9"/>
       <c r="N9" s="52">
         <v>2100</v>
       </c>
       <c r="O9" s="28" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="P9" s="9">
         <v>2025</v>
@@ -35837,7 +35837,7 @@
       <c r="R9" s="9"/>
       <c r="S9" s="9"/>
       <c r="T9" s="9" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="46">
@@ -35846,13 +35846,13 @@
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="8" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>1472</v>
+      </c>
+      <c r="E10" s="9" t="s">
         <v>1483</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>1473</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>1484</v>
       </c>
       <c r="F10" s="9">
         <v>-2.4538889000000001E-2</v>
@@ -35868,7 +35868,7 @@
         <v>43</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="L10" s="9" t="s">
         <v>678</v>
@@ -35887,7 +35887,7 @@
       <c r="R10" s="9"/>
       <c r="S10" s="9"/>
       <c r="T10" s="9" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="46">
@@ -35896,13 +35896,13 @@
       </c>
       <c r="B11" s="9"/>
       <c r="C11" s="8" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="F11" s="9">
         <v>-5.7777800000000004E-4</v>
@@ -35918,7 +35918,7 @@
         <v>43</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="L11" s="9" t="s">
         <v>678</v>
@@ -35937,7 +35937,7 @@
       <c r="R11" s="9"/>
       <c r="S11" s="9"/>
       <c r="T11" s="9" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="69">
@@ -35946,13 +35946,13 @@
       </c>
       <c r="B12" s="9"/>
       <c r="C12" s="8" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="F12" s="9">
         <v>-3.3805556E-2</v>
@@ -35968,7 +35968,7 @@
         <v>66</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="L12" s="9" t="s">
         <v>678</v>
@@ -35987,7 +35987,7 @@
       <c r="R12" s="9"/>
       <c r="S12" s="9"/>
       <c r="T12" s="9" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="69">
@@ -35996,13 +35996,13 @@
       </c>
       <c r="B13" s="9"/>
       <c r="C13" s="8" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="F13" s="9">
         <v>-3.3805556E-2</v>
@@ -36018,7 +36018,7 @@
         <v>43</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="L13" s="9" t="s">
         <v>678</v>
@@ -36037,7 +36037,7 @@
       <c r="R13" s="9"/>
       <c r="S13" s="9"/>
       <c r="T13" s="9" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="57.5">
@@ -36046,13 +36046,13 @@
       </c>
       <c r="B14" s="9"/>
       <c r="C14" s="8" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="F14" s="9">
         <v>-3.8888900000000001E-4</v>
@@ -36068,7 +36068,7 @@
         <v>43</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="L14" s="9" t="s">
         <v>678</v>
@@ -36087,7 +36087,7 @@
       <c r="R14" s="9"/>
       <c r="S14" s="9"/>
       <c r="T14" s="9" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="69">
@@ -36096,13 +36096,13 @@
       </c>
       <c r="B15" s="9"/>
       <c r="C15" s="8" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="F15" s="9">
         <v>-3.3805556E-2</v>
@@ -36118,7 +36118,7 @@
         <v>66</v>
       </c>
       <c r="K15" s="9" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="L15" s="9" t="s">
         <v>678</v>
@@ -36137,7 +36137,7 @@
       <c r="R15" s="9"/>
       <c r="S15" s="9"/>
       <c r="T15" s="9" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="57.5">
@@ -36146,13 +36146,13 @@
       </c>
       <c r="B16" s="9"/>
       <c r="C16" s="8" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="F16" s="9">
         <v>-3.5644443999999997E-2</v>
@@ -36168,7 +36168,7 @@
         <v>43</v>
       </c>
       <c r="K16" s="9" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="L16" s="9" t="s">
         <v>678</v>
@@ -36187,7 +36187,7 @@
       <c r="R16" s="9"/>
       <c r="S16" s="9"/>
       <c r="T16" s="9" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="57.5">
@@ -36196,13 +36196,13 @@
       </c>
       <c r="B17" s="9"/>
       <c r="C17" s="8" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="F17" s="9">
         <v>-3.1629999999999998E-2</v>
@@ -36218,7 +36218,7 @@
         <v>43</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="L17" s="9" t="s">
         <v>678</v>
@@ -36237,7 +36237,7 @@
       <c r="R17" s="9"/>
       <c r="S17" s="9"/>
       <c r="T17" s="9" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="69">
@@ -36246,13 +36246,13 @@
       </c>
       <c r="B18" s="9"/>
       <c r="C18" s="8" t="s">
+        <v>1471</v>
+      </c>
+      <c r="D18" s="9" t="s">
         <v>1472</v>
       </c>
-      <c r="D18" s="9" t="s">
-        <v>1473</v>
-      </c>
       <c r="E18" s="9" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="F18" s="9">
         <v>-6.3280000000000003E-2</v>
@@ -36268,7 +36268,7 @@
         <v>43</v>
       </c>
       <c r="K18" s="9" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="L18" s="9" t="s">
         <v>678</v>
@@ -36287,7 +36287,7 @@
       <c r="R18" s="9"/>
       <c r="S18" s="9"/>
       <c r="T18" s="9" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="92">
@@ -36296,13 +36296,13 @@
       </c>
       <c r="B19" s="9"/>
       <c r="C19" s="8" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="F19" s="9">
         <v>-2.9803E-2</v>
@@ -36318,7 +36318,7 @@
         <v>104</v>
       </c>
       <c r="K19" s="9" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="L19" s="9" t="s">
         <v>678</v>
@@ -36337,7 +36337,7 @@
       <c r="R19" s="9"/>
       <c r="S19" s="9"/>
       <c r="T19" s="9" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="20" spans="1:20" ht="92">
@@ -36346,13 +36346,13 @@
       </c>
       <c r="B20" s="9"/>
       <c r="C20" s="8" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="F20" s="9">
         <v>-1.1709999999999999E-3</v>
@@ -36362,13 +36362,13 @@
       </c>
       <c r="H20" s="9"/>
       <c r="I20" s="9" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="J20" s="9" t="s">
         <v>58</v>
       </c>
       <c r="K20" s="9" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="L20" s="9" t="s">
         <v>678</v>
@@ -36387,7 +36387,7 @@
       <c r="R20" s="9"/>
       <c r="S20" s="9"/>
       <c r="T20" s="9" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="21" spans="1:20" ht="80.5">
@@ -36396,13 +36396,13 @@
       </c>
       <c r="B21" s="9"/>
       <c r="C21" s="8" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="F21" s="9">
         <v>5.3839999999999999E-3</v>
@@ -36418,7 +36418,7 @@
         <v>58</v>
       </c>
       <c r="K21" s="9" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="L21" s="9" t="s">
         <v>678</v>
@@ -36437,7 +36437,7 @@
       <c r="R21" s="9"/>
       <c r="S21" s="9"/>
       <c r="T21" s="9" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="46">
@@ -36446,13 +36446,13 @@
       </c>
       <c r="B22" s="9"/>
       <c r="C22" s="8" t="s">
+        <v>1471</v>
+      </c>
+      <c r="D22" s="9" t="s">
         <v>1472</v>
       </c>
-      <c r="D22" s="9" t="s">
-        <v>1473</v>
-      </c>
       <c r="E22" s="19" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="F22" s="9">
         <v>-2.9825000000000001E-2</v>
@@ -36468,7 +36468,7 @@
         <v>58</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="L22" s="9" t="s">
         <v>678</v>
@@ -36487,18 +36487,11 @@
       <c r="R22" s="9"/>
       <c r="S22" s="9"/>
       <c r="T22" s="9" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="K1:P1"/>
-    <mergeCell ref="T1:T3"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="Q1:S1"/>
-    <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:O2"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="I2:I3"/>
@@ -36510,6 +36503,13 @@
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="C2:C3"/>
+    <mergeCell ref="K1:P1"/>
+    <mergeCell ref="T1:T3"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="Q1:S1"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:O2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -36547,7 +36547,7 @@
       <c r="K1" s="101"/>
       <c r="L1" s="102"/>
       <c r="M1" s="101" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="N1" s="102"/>
       <c r="O1" s="98" t="s">
@@ -36563,17 +36563,17 @@
         <v>674</v>
       </c>
       <c r="D2" s="103" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="E2" s="80" t="s">
         <v>6</v>
       </c>
       <c r="F2" s="99" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="G2" s="100"/>
       <c r="H2" s="99" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="I2" s="100"/>
       <c r="J2" s="80" t="s">
@@ -36586,10 +36586,10 @@
         <v>13</v>
       </c>
       <c r="M2" s="78" t="s">
+        <v>1497</v>
+      </c>
+      <c r="N2" s="93" t="s">
         <v>1498</v>
-      </c>
-      <c r="N2" s="90" t="s">
-        <v>1499</v>
       </c>
       <c r="O2" s="98"/>
     </row>
@@ -36615,7 +36615,7 @@
       <c r="K3" s="80"/>
       <c r="L3" s="99"/>
       <c r="M3" s="78"/>
-      <c r="N3" s="90"/>
+      <c r="N3" s="93"/>
       <c r="O3" s="98"/>
     </row>
     <row r="4" spans="1:15" ht="69">
@@ -36624,13 +36624,13 @@
       </c>
       <c r="B4" s="56"/>
       <c r="C4" s="3" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>1500</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="56" t="s">
         <v>1501</v>
-      </c>
-      <c r="E4" s="56" t="s">
-        <v>1502</v>
       </c>
       <c r="F4" s="56">
         <v>-4.9502259999999999E-2</v>
@@ -36652,7 +36652,7 @@
       <c r="M4" s="56"/>
       <c r="N4" s="69"/>
       <c r="O4" s="68" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="69">
@@ -36661,13 +36661,13 @@
       </c>
       <c r="B5" s="56"/>
       <c r="C5" s="3" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>1500</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>1501</v>
-      </c>
       <c r="E5" s="56" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="F5" s="56">
         <v>-3.0405000000000001E-2</v>
@@ -36689,7 +36689,7 @@
       <c r="M5" s="56"/>
       <c r="N5" s="69"/>
       <c r="O5" s="68" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="69">
@@ -36698,13 +36698,13 @@
       </c>
       <c r="B6" s="56"/>
       <c r="C6" s="3" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>1500</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>1501</v>
-      </c>
       <c r="E6" s="56" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="F6" s="56">
         <v>-4.2117000000000002E-2</v>
@@ -36726,7 +36726,7 @@
       <c r="M6" s="56"/>
       <c r="N6" s="69"/>
       <c r="O6" s="68" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="69">
@@ -36735,13 +36735,13 @@
       </c>
       <c r="B7" s="56"/>
       <c r="C7" s="3" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>1500</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>1501</v>
-      </c>
       <c r="E7" s="56" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="F7" s="56">
         <v>-4.1271000000000002E-2</v>
@@ -36763,7 +36763,7 @@
       <c r="M7" s="56"/>
       <c r="N7" s="69"/>
       <c r="O7" s="68" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="69">
@@ -36772,13 +36772,13 @@
       </c>
       <c r="B8" s="56"/>
       <c r="C8" s="3" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>1500</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>1501</v>
-      </c>
       <c r="E8" s="56" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="F8" s="56">
         <v>-4.9947999999999999E-2</v>
@@ -36800,7 +36800,7 @@
       <c r="M8" s="56"/>
       <c r="N8" s="69"/>
       <c r="O8" s="68" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="69">
@@ -36809,13 +36809,13 @@
       </c>
       <c r="B9" s="56"/>
       <c r="C9" s="3" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>1500</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>1501</v>
-      </c>
       <c r="E9" s="56" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="F9" s="56">
         <v>-6.3731999999999997E-2</v>
@@ -36837,7 +36837,7 @@
       <c r="M9" s="56"/>
       <c r="N9" s="69"/>
       <c r="O9" s="68" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="69">
@@ -36846,13 +36846,13 @@
       </c>
       <c r="B10" s="56"/>
       <c r="C10" s="3" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>1500</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>1501</v>
-      </c>
       <c r="E10" s="56" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="F10" s="56">
         <v>-5.8363699999999998E-2</v>
@@ -36874,7 +36874,7 @@
       <c r="M10" s="56"/>
       <c r="N10" s="69"/>
       <c r="O10" s="68" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="69">
@@ -36883,13 +36883,13 @@
       </c>
       <c r="B11" s="56"/>
       <c r="C11" s="3" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>1500</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>1501</v>
-      </c>
       <c r="E11" s="56" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="F11" s="56">
         <v>-2.6185E-2</v>
@@ -36911,7 +36911,7 @@
       <c r="M11" s="56"/>
       <c r="N11" s="69"/>
       <c r="O11" s="68" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="69">
@@ -36920,13 +36920,13 @@
       </c>
       <c r="B12" s="56"/>
       <c r="C12" s="3" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>1500</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>1501</v>
-      </c>
       <c r="E12" s="56" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="F12" s="56">
         <v>-1.866E-2</v>
@@ -36948,7 +36948,7 @@
       <c r="M12" s="56"/>
       <c r="N12" s="69"/>
       <c r="O12" s="68" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="69">
@@ -36957,13 +36957,13 @@
       </c>
       <c r="B13" s="56"/>
       <c r="C13" s="3" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>1500</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>1501</v>
-      </c>
       <c r="E13" s="56" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="F13" s="56">
         <v>-3.5164000000000001E-2</v>
@@ -36985,7 +36985,7 @@
       <c r="M13" s="56"/>
       <c r="N13" s="69"/>
       <c r="O13" s="68" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="69">
@@ -36994,13 +36994,13 @@
       </c>
       <c r="B14" s="56"/>
       <c r="C14" s="3" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>1500</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>1501</v>
-      </c>
       <c r="E14" s="56" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="F14" s="56">
         <v>-2.7425999999999999E-2</v>
@@ -37022,7 +37022,7 @@
       <c r="M14" s="56"/>
       <c r="N14" s="69"/>
       <c r="O14" s="68" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="69">
@@ -37031,16 +37031,16 @@
       </c>
       <c r="B15" s="56"/>
       <c r="C15" s="3" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>1500</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>1501</v>
-      </c>
       <c r="E15" s="56" t="s">
+        <v>1513</v>
+      </c>
+      <c r="F15" s="56" t="s">
         <v>1514</v>
-      </c>
-      <c r="F15" s="56" t="s">
-        <v>1515</v>
       </c>
       <c r="G15" s="56">
         <v>109.322507</v>
@@ -37059,7 +37059,7 @@
       <c r="M15" s="56"/>
       <c r="N15" s="69"/>
       <c r="O15" s="68" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="69">
@@ -37068,13 +37068,13 @@
       </c>
       <c r="B16" s="56"/>
       <c r="C16" s="3" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>1500</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>1501</v>
-      </c>
       <c r="E16" s="56" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="F16" s="56">
         <v>-1.7652999999999999E-2</v>
@@ -37096,7 +37096,7 @@
       <c r="M16" s="56"/>
       <c r="N16" s="69"/>
       <c r="O16" s="68" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="69">
@@ -37105,13 +37105,13 @@
       </c>
       <c r="B17" s="57"/>
       <c r="C17" s="3" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D17" s="17" t="s">
         <v>1500</v>
       </c>
-      <c r="D17" s="17" t="s">
-        <v>1501</v>
-      </c>
       <c r="E17" s="57" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="F17" s="57">
         <v>2.2098199999999999E-3</v>
@@ -37133,7 +37133,7 @@
       <c r="M17" s="57"/>
       <c r="N17" s="70"/>
       <c r="O17" s="68" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="69">
@@ -37142,13 +37142,13 @@
       </c>
       <c r="B18" s="36"/>
       <c r="C18" s="3" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D18" s="9" t="s">
         <v>1500</v>
       </c>
-      <c r="D18" s="9" t="s">
-        <v>1501</v>
-      </c>
       <c r="E18" s="36" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="F18" s="36">
         <v>7.8245299999999997E-3</v>
@@ -37170,7 +37170,7 @@
       <c r="M18" s="36"/>
       <c r="N18" s="71"/>
       <c r="O18" s="68" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="69">
@@ -37179,13 +37179,13 @@
       </c>
       <c r="B19" s="36"/>
       <c r="C19" s="3" t="s">
+        <v>1518</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>1500</v>
+      </c>
+      <c r="E19" s="36" t="s">
         <v>1519</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>1501</v>
-      </c>
-      <c r="E19" s="36" t="s">
-        <v>1520</v>
       </c>
       <c r="F19" s="36">
         <v>-2.8417000000000001E-2</v>
@@ -37203,7 +37203,7 @@
       <c r="M19" s="36"/>
       <c r="N19" s="71"/>
       <c r="O19" s="68" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="69">
@@ -37212,13 +37212,13 @@
       </c>
       <c r="B20" s="58"/>
       <c r="C20" s="3" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="E20" s="58" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="F20" s="58">
         <v>-4.8384000000000003E-2</v>
@@ -37236,7 +37236,7 @@
       <c r="M20" s="58"/>
       <c r="N20" s="72"/>
       <c r="O20" s="68" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="69">
@@ -37245,13 +37245,13 @@
       </c>
       <c r="B21" s="36"/>
       <c r="C21" s="3" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="E21" s="36" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="F21" s="36">
         <v>3.849E-3</v>
@@ -37269,7 +37269,7 @@
       <c r="M21" s="36"/>
       <c r="N21" s="71"/>
       <c r="O21" s="68" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="69">
@@ -37278,13 +37278,13 @@
       </c>
       <c r="B22" s="29"/>
       <c r="C22" s="3" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="E22" s="36" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="F22" s="36">
         <v>7.8810000000000009E-3</v>
@@ -37302,7 +37302,7 @@
       <c r="M22" s="29"/>
       <c r="N22" s="73"/>
       <c r="O22" s="68" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
   </sheetData>
@@ -45971,6 +45971,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="K2:L2"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="K1:P1"/>
@@ -45987,8 +45989,6 @@
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="J2:J3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="K2:L2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -48693,11 +48693,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="R2:R3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="S1:S3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:B3"/>
@@ -48708,6 +48703,11 @@
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="E2:E3"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="R2:R3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="S1:S3"/>
     <mergeCell ref="K1:P1"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="M2:O2"/>
@@ -51025,7 +51025,7 @@
         <v>78</v>
       </c>
       <c r="I54" s="18" t="s">
-        <v>587</v>
+        <v>66</v>
       </c>
       <c r="J54" s="18" t="s">
         <v>588</v>
@@ -51034,7 +51034,7 @@
         <v>678</v>
       </c>
       <c r="L54" s="18" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="M54" s="18">
         <v>2</v>
@@ -51075,7 +51075,7 @@
         <v>78</v>
       </c>
       <c r="I55" s="18" t="s">
-        <v>587</v>
+        <v>66</v>
       </c>
       <c r="J55" s="18" t="s">
         <v>588</v>
@@ -51084,7 +51084,7 @@
         <v>678</v>
       </c>
       <c r="L55" s="18" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="M55" s="18">
         <v>2</v>
@@ -51125,7 +51125,7 @@
         <v>85</v>
       </c>
       <c r="I56" s="18" t="s">
-        <v>587</v>
+        <v>66</v>
       </c>
       <c r="J56" s="18" t="s">
         <v>588</v>
@@ -51134,7 +51134,7 @@
         <v>678</v>
       </c>
       <c r="L56" s="18" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="M56" s="18">
         <v>2</v>
@@ -51175,7 +51175,7 @@
         <v>88</v>
       </c>
       <c r="I57" s="18" t="s">
-        <v>587</v>
+        <v>66</v>
       </c>
       <c r="J57" s="18" t="s">
         <v>588</v>
@@ -51184,7 +51184,7 @@
         <v>678</v>
       </c>
       <c r="L57" s="18" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="M57" s="18">
         <v>2</v>
@@ -51225,7 +51225,7 @@
         <v>65</v>
       </c>
       <c r="I58" s="18" t="s">
-        <v>587</v>
+        <v>66</v>
       </c>
       <c r="J58" s="18" t="s">
         <v>588</v>
@@ -51234,7 +51234,7 @@
         <v>678</v>
       </c>
       <c r="L58" s="18" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="M58" s="18">
         <v>1</v>
@@ -51281,13 +51281,14 @@
     <col min="1" max="1" width="9.25" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.1640625" style="5"/>
     <col min="3" max="3" width="9.1640625" style="32"/>
-    <col min="4" max="5" width="9.1640625" style="5"/>
-    <col min="6" max="6" width="9.4140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" style="5"/>
+    <col min="5" max="5" width="10" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.33203125" style="5" bestFit="1" customWidth="1"/>
     <col min="8" max="11" width="9.1640625" style="5"/>
-    <col min="12" max="15" width="9.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10" style="5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.83203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="9.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.08203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.9140625" style="5" bestFit="1" customWidth="1"/>
     <col min="18" max="16384" width="9.1640625" style="5"/>
   </cols>
   <sheetData>
@@ -51671,11 +51672,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="P2:P3"/>
-    <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="R1:R3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="J1:O1"/>
@@ -51688,6 +51684,11 @@
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="P2:P3"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="R1:R3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -58241,7 +58242,7 @@
         <v>85</v>
       </c>
       <c r="I132" s="18" t="s">
-        <v>1026</v>
+        <v>66</v>
       </c>
       <c r="J132" s="18" t="s">
         <v>588</v>
@@ -58250,13 +58251,13 @@
         <v>678</v>
       </c>
       <c r="L132" s="18" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M132" s="18">
         <v>1</v>
       </c>
       <c r="N132" s="18" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="O132" s="18">
         <v>1976</v>
@@ -58276,7 +58277,7 @@
         <v>889</v>
       </c>
       <c r="D133" s="18" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="E133" s="18">
         <v>-1.11251812395429E-3</v>
@@ -58291,7 +58292,7 @@
         <v>85</v>
       </c>
       <c r="I133" s="18" t="s">
-        <v>1026</v>
+        <v>66</v>
       </c>
       <c r="J133" s="18" t="s">
         <v>588</v>
@@ -58300,13 +58301,13 @@
         <v>678</v>
       </c>
       <c r="L133" s="18" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="M133" s="18">
         <v>2</v>
       </c>
       <c r="N133" s="18" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="O133" s="18">
         <v>2014</v>
@@ -58326,7 +58327,7 @@
         <v>889</v>
       </c>
       <c r="D134" s="18" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="E134" s="18">
         <v>5.9328155122252203E-4</v>
@@ -58341,7 +58342,7 @@
         <v>85</v>
       </c>
       <c r="I134" s="18" t="s">
-        <v>1026</v>
+        <v>66</v>
       </c>
       <c r="J134" s="18" t="s">
         <v>588</v>
@@ -58350,13 +58351,13 @@
         <v>678</v>
       </c>
       <c r="L134" s="18" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="M134" s="18">
         <v>2</v>
       </c>
       <c r="N134" s="18" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="O134" s="18">
         <v>2015</v>
@@ -58376,7 +58377,7 @@
         <v>889</v>
       </c>
       <c r="D135" s="18" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="E135" s="18">
         <v>-1.53855570780006E-2</v>
@@ -58391,7 +58392,7 @@
         <v>85</v>
       </c>
       <c r="I135" s="18" t="s">
-        <v>1026</v>
+        <v>66</v>
       </c>
       <c r="J135" s="18" t="s">
         <v>588</v>
@@ -58400,13 +58401,13 @@
         <v>678</v>
       </c>
       <c r="L135" s="18" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="M135" s="18">
         <v>1</v>
       </c>
       <c r="N135" s="18" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="O135" s="18">
         <v>1982</v>
@@ -58426,7 +58427,7 @@
         <v>889</v>
       </c>
       <c r="D136" s="18" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="E136" s="18">
         <v>-1.52252799360201E-2</v>
@@ -58441,7 +58442,7 @@
         <v>85</v>
       </c>
       <c r="I136" s="18" t="s">
-        <v>1026</v>
+        <v>66</v>
       </c>
       <c r="J136" s="18" t="s">
         <v>588</v>
@@ -58456,7 +58457,7 @@
         <v>1</v>
       </c>
       <c r="N136" s="18" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="O136" s="18">
         <v>1982</v>
@@ -58476,7 +58477,7 @@
         <v>889</v>
       </c>
       <c r="D137" s="18" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="E137" s="18">
         <v>-1.18934774736666E-2</v>
@@ -58491,7 +58492,7 @@
         <v>85</v>
       </c>
       <c r="I137" s="18" t="s">
-        <v>1026</v>
+        <v>66</v>
       </c>
       <c r="J137" s="18" t="s">
         <v>588</v>
@@ -58500,13 +58501,13 @@
         <v>678</v>
       </c>
       <c r="L137" s="18" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="M137" s="18">
         <v>1</v>
       </c>
       <c r="N137" s="18" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="O137" s="18">
         <v>1982</v>
@@ -58526,7 +58527,7 @@
         <v>889</v>
       </c>
       <c r="D138" s="18" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="E138" s="18">
         <v>-1.2782870838480599E-2</v>
@@ -58541,7 +58542,7 @@
         <v>85</v>
       </c>
       <c r="I138" s="18" t="s">
-        <v>1026</v>
+        <v>66</v>
       </c>
       <c r="J138" s="18" t="s">
         <v>588</v>
@@ -58550,13 +58551,13 @@
         <v>678</v>
       </c>
       <c r="L138" s="18" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="M138" s="18">
         <v>2</v>
       </c>
       <c r="N138" s="18" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="O138" s="18">
         <v>2019</v>
@@ -58576,7 +58577,7 @@
         <v>889</v>
       </c>
       <c r="D139" s="18" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="E139" s="18">
         <v>-2.8114744654826802E-3</v>
@@ -58591,7 +58592,7 @@
         <v>85</v>
       </c>
       <c r="I139" s="18" t="s">
-        <v>1026</v>
+        <v>66</v>
       </c>
       <c r="J139" s="18" t="s">
         <v>588</v>
@@ -58600,13 +58601,13 @@
         <v>678</v>
       </c>
       <c r="L139" s="18" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="M139" s="18">
         <v>1</v>
       </c>
       <c r="N139" s="18" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="O139" s="18">
         <v>1984</v>
@@ -58626,7 +58627,7 @@
         <v>889</v>
       </c>
       <c r="D140" s="18" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="E140" s="18">
         <v>-1.65668824016444E-2</v>
@@ -58641,7 +58642,7 @@
         <v>85</v>
       </c>
       <c r="I140" s="18" t="s">
-        <v>1026</v>
+        <v>66</v>
       </c>
       <c r="J140" s="18" t="s">
         <v>588</v>
@@ -58650,13 +58651,13 @@
         <v>678</v>
       </c>
       <c r="L140" s="18" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="M140" s="18">
         <v>1</v>
       </c>
       <c r="N140" s="18" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="O140" s="18">
         <v>1985</v>
@@ -58676,7 +58677,7 @@
         <v>889</v>
       </c>
       <c r="D141" s="18" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="E141" s="18">
         <v>1.7953317331205101E-2</v>
@@ -58691,7 +58692,7 @@
         <v>85</v>
       </c>
       <c r="I141" s="18" t="s">
-        <v>1026</v>
+        <v>66</v>
       </c>
       <c r="J141" s="18" t="s">
         <v>588</v>
@@ -58700,13 +58701,13 @@
         <v>678</v>
       </c>
       <c r="L141" s="18" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="M141" s="18">
         <v>2</v>
       </c>
       <c r="N141" s="18" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="O141" s="18">
         <v>2016</v>
@@ -58726,7 +58727,7 @@
         <v>889</v>
       </c>
       <c r="D142" s="18" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="E142" s="18">
         <v>-1.30550642755665E-2</v>
@@ -58741,7 +58742,7 @@
         <v>85</v>
       </c>
       <c r="I142" s="18" t="s">
-        <v>1026</v>
+        <v>66</v>
       </c>
       <c r="J142" s="18" t="s">
         <v>588</v>
@@ -58750,13 +58751,13 @@
         <v>678</v>
       </c>
       <c r="L142" s="18" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="M142" s="18">
         <v>1</v>
       </c>
       <c r="N142" s="18" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="O142" s="18">
         <v>1985</v>
@@ -58776,7 +58777,7 @@
         <v>889</v>
       </c>
       <c r="D143" s="18" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="E143" s="18">
         <v>-1.2734550876353E-2</v>
@@ -58791,7 +58792,7 @@
         <v>85</v>
       </c>
       <c r="I143" s="18" t="s">
-        <v>1026</v>
+        <v>66</v>
       </c>
       <c r="J143" s="18" t="s">
         <v>588</v>
@@ -58800,13 +58801,13 @@
         <v>678</v>
       </c>
       <c r="L143" s="18" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="M143" s="18">
         <v>1</v>
       </c>
       <c r="N143" s="18" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="O143" s="18">
         <v>1987</v>
@@ -58826,7 +58827,7 @@
         <v>959</v>
       </c>
       <c r="D144" s="18" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="E144" s="18">
         <v>-2.4297134409067998E-3</v>
@@ -58841,7 +58842,7 @@
         <v>85</v>
       </c>
       <c r="I144" s="18" t="s">
-        <v>1026</v>
+        <v>66</v>
       </c>
       <c r="J144" s="18" t="s">
         <v>588</v>
@@ -58850,13 +58851,13 @@
         <v>678</v>
       </c>
       <c r="L144" s="18" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="M144" s="18">
         <v>2</v>
       </c>
       <c r="N144" s="18" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="O144" s="18">
         <v>2010</v>
@@ -58876,7 +58877,7 @@
         <v>959</v>
       </c>
       <c r="D145" s="18" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="E145" s="18">
         <v>1.7953317331205101E-2</v>
@@ -58891,7 +58892,7 @@
         <v>85</v>
       </c>
       <c r="I145" s="18" t="s">
-        <v>1026</v>
+        <v>66</v>
       </c>
       <c r="J145" s="18" t="s">
         <v>588</v>
@@ -58900,7 +58901,7 @@
         <v>678</v>
       </c>
       <c r="L145" s="18" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="M145" s="18">
         <v>2</v>
@@ -58926,7 +58927,7 @@
         <v>959</v>
       </c>
       <c r="D146" s="18" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="E146" s="18">
         <v>-1.56942708718813E-2</v>
@@ -58941,7 +58942,7 @@
         <v>85</v>
       </c>
       <c r="I146" s="18" t="s">
-        <v>1026</v>
+        <v>66</v>
       </c>
       <c r="J146" s="18" t="s">
         <v>588</v>
@@ -58950,13 +58951,13 @@
         <v>678</v>
       </c>
       <c r="L146" s="18" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="M146" s="18">
         <v>2</v>
       </c>
       <c r="N146" s="18" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="O146" s="18">
         <v>2012</v>
@@ -58976,7 +58977,7 @@
         <v>889</v>
       </c>
       <c r="D147" s="18" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="E147" s="18">
         <v>1.0328113798238701E-2</v>
@@ -58988,10 +58989,10 @@
         <v>1025</v>
       </c>
       <c r="H147" s="18" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="I147" s="18" t="s">
-        <v>1026</v>
+        <v>66</v>
       </c>
       <c r="J147" s="18" t="s">
         <v>588</v>
@@ -59000,7 +59001,7 @@
         <v>678</v>
       </c>
       <c r="L147" s="18" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="M147" s="18">
         <v>1</v>
@@ -59026,7 +59027,7 @@
         <v>889</v>
       </c>
       <c r="D148" s="18" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="E148" s="18">
         <v>5.4449597285002298E-3</v>
@@ -59038,10 +59039,10 @@
         <v>1025</v>
       </c>
       <c r="H148" s="18" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="I148" s="18" t="s">
-        <v>1026</v>
+        <v>66</v>
       </c>
       <c r="J148" s="18" t="s">
         <v>588</v>
@@ -59050,7 +59051,7 @@
         <v>678</v>
       </c>
       <c r="L148" s="18" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="M148" s="18">
         <v>2</v>
@@ -59076,7 +59077,7 @@
         <v>889</v>
       </c>
       <c r="D149" s="18" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="E149" s="18">
         <v>7.0290885124097797E-3</v>
@@ -59088,10 +59089,10 @@
         <v>1025</v>
       </c>
       <c r="H149" s="18" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="I149" s="18" t="s">
-        <v>1026</v>
+        <v>66</v>
       </c>
       <c r="J149" s="18" t="s">
         <v>588</v>
@@ -59100,7 +59101,7 @@
         <v>678</v>
       </c>
       <c r="L149" s="18" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="M149" s="18">
         <v>1</v>
@@ -59126,7 +59127,7 @@
         <v>889</v>
       </c>
       <c r="D150" s="18" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="E150" s="18">
         <v>2.6456347138964602E-3</v>
@@ -59138,10 +59139,10 @@
         <v>1025</v>
       </c>
       <c r="H150" s="18" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="I150" s="18" t="s">
-        <v>1026</v>
+        <v>66</v>
       </c>
       <c r="J150" s="18" t="s">
         <v>588</v>
@@ -59150,7 +59151,7 @@
         <v>678</v>
       </c>
       <c r="L150" s="18" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="M150" s="18">
         <v>1</v>
@@ -59176,7 +59177,7 @@
         <v>889</v>
       </c>
       <c r="D151" s="18" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="E151" s="18">
         <v>7.5333021856917697E-3</v>
@@ -59188,10 +59189,10 @@
         <v>1025</v>
       </c>
       <c r="H151" s="18" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="I151" s="18" t="s">
-        <v>1026</v>
+        <v>66</v>
       </c>
       <c r="J151" s="18" t="s">
         <v>588</v>
@@ -59200,7 +59201,7 @@
         <v>678</v>
       </c>
       <c r="L151" s="18" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="M151" s="18">
         <v>2</v>
@@ -59226,7 +59227,7 @@
         <v>959</v>
       </c>
       <c r="D152" s="18" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="E152" s="18">
         <v>9.4162177347996701E-3</v>
@@ -59238,10 +59239,10 @@
         <v>1025</v>
       </c>
       <c r="H152" s="18" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="I152" s="18" t="s">
-        <v>1026</v>
+        <v>66</v>
       </c>
       <c r="J152" s="18" t="s">
         <v>588</v>
@@ -59250,7 +59251,7 @@
         <v>678</v>
       </c>
       <c r="L152" s="18" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="M152" s="18">
         <v>2</v>
@@ -59276,7 +59277,7 @@
         <v>959</v>
       </c>
       <c r="D153" s="18" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="E153" s="18">
         <v>8.0120884761362299E-3</v>
@@ -59288,10 +59289,10 @@
         <v>1025</v>
       </c>
       <c r="H153" s="18" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="I153" s="18" t="s">
-        <v>1026</v>
+        <v>66</v>
       </c>
       <c r="J153" s="18" t="s">
         <v>588</v>
@@ -59300,13 +59301,13 @@
         <v>678</v>
       </c>
       <c r="L153" s="18" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="M153" s="18">
         <v>2</v>
       </c>
       <c r="N153" s="18" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="O153" s="18">
         <v>2011</v>
@@ -59326,7 +59327,7 @@
         <v>992</v>
       </c>
       <c r="D154" s="18" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="E154" s="18">
         <v>2.3029908385521999E-3</v>
@@ -59338,10 +59339,10 @@
         <v>1025</v>
       </c>
       <c r="H154" s="18" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="I154" s="18" t="s">
-        <v>1026</v>
+        <v>66</v>
       </c>
       <c r="J154" s="18" t="s">
         <v>588</v>
@@ -59350,7 +59351,7 @@
         <v>678</v>
       </c>
       <c r="L154" s="18" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="M154" s="18">
         <v>2</v>
@@ -59376,7 +59377,7 @@
         <v>992</v>
       </c>
       <c r="D155" s="18" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="E155" s="18">
         <v>1.53061576721314E-2</v>
@@ -59388,10 +59389,10 @@
         <v>1025</v>
       </c>
       <c r="H155" s="18" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="I155" s="18" t="s">
-        <v>1026</v>
+        <v>66</v>
       </c>
       <c r="J155" s="18" t="s">
         <v>588</v>
@@ -59400,7 +59401,7 @@
         <v>678</v>
       </c>
       <c r="L155" s="18" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="M155" s="18">
         <v>2</v>
@@ -59426,7 +59427,7 @@
         <v>789</v>
       </c>
       <c r="D156" s="18" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E156" s="18">
         <v>5.4410800000000002E-2</v>
@@ -59441,13 +59442,13 @@
         <v>42</v>
       </c>
       <c r="I156" s="18" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="J156" s="18" t="s">
         <v>588</v>
       </c>
       <c r="K156" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L156" s="18"/>
       <c r="M156" s="18">
@@ -59474,7 +59475,7 @@
         <v>789</v>
       </c>
       <c r="D157" s="18" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="E157" s="18">
         <v>4.6882E-2</v>
@@ -59489,13 +59490,13 @@
         <v>54</v>
       </c>
       <c r="I157" s="18" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="J157" s="18" t="s">
         <v>588</v>
       </c>
       <c r="K157" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L157" s="18"/>
       <c r="M157" s="18">
@@ -59520,7 +59521,7 @@
         <v>789</v>
       </c>
       <c r="D158" s="18" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="E158" s="18">
         <v>3.1699999999999999E-2</v>
@@ -59530,7 +59531,7 @@
       </c>
       <c r="G158" s="18"/>
       <c r="H158" s="18" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="I158" s="18" t="s">
         <v>69</v>
@@ -59539,7 +59540,7 @@
         <v>588</v>
       </c>
       <c r="K158" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L158" s="18"/>
       <c r="M158" s="18">
@@ -59562,7 +59563,7 @@
         <v>789</v>
       </c>
       <c r="D159" s="18" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="E159" s="18">
         <v>1.4200000000000001E-2</v>
@@ -59572,7 +59573,7 @@
       </c>
       <c r="G159" s="18"/>
       <c r="H159" s="18" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="I159" s="18" t="s">
         <v>58</v>
@@ -59581,7 +59582,7 @@
         <v>588</v>
       </c>
       <c r="K159" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L159" s="18"/>
       <c r="M159" s="18">
@@ -59604,7 +59605,7 @@
         <v>789</v>
       </c>
       <c r="D160" s="18" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="E160" s="18"/>
       <c r="F160" s="18"/>
@@ -59619,7 +59620,7 @@
         <v>588</v>
       </c>
       <c r="K160" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L160" s="18"/>
       <c r="M160" s="18">
@@ -59642,7 +59643,7 @@
         <v>789</v>
       </c>
       <c r="D161" s="18" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="E161" s="18">
         <v>3.3470000000000001E-3</v>
@@ -59661,7 +59662,7 @@
         <v>588</v>
       </c>
       <c r="K161" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L161" s="18"/>
       <c r="M161" s="18">
@@ -59684,7 +59685,7 @@
         <v>889</v>
       </c>
       <c r="D162" s="18" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="E162" s="18">
         <v>4.4699999999999997E-2</v>
@@ -59703,7 +59704,7 @@
         <v>588</v>
       </c>
       <c r="K162" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L162" s="18"/>
       <c r="M162" s="18">
@@ -59726,7 +59727,7 @@
         <v>889</v>
       </c>
       <c r="D163" s="18" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="E163" s="18">
         <v>4.2500000000000003E-2</v>
@@ -59745,7 +59746,7 @@
         <v>588</v>
       </c>
       <c r="K163" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L163" s="18"/>
       <c r="M163" s="18">
@@ -59768,7 +59769,7 @@
         <v>889</v>
       </c>
       <c r="D164" s="18" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="E164" s="18">
         <v>3.5900000000000001E-2</v>
@@ -59787,7 +59788,7 @@
         <v>588</v>
       </c>
       <c r="K164" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L164" s="18"/>
       <c r="M164" s="18">
@@ -59810,7 +59811,7 @@
         <v>889</v>
       </c>
       <c r="D165" s="18" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E165" s="18">
         <v>3.7999999999999999E-2</v>
@@ -59829,7 +59830,7 @@
         <v>588</v>
       </c>
       <c r="K165" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L165" s="18"/>
       <c r="M165" s="18">
@@ -59852,7 +59853,7 @@
         <v>889</v>
       </c>
       <c r="D166" s="18" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="E166" s="18">
         <v>5.3600000000000002E-2</v>
@@ -59871,7 +59872,7 @@
         <v>588</v>
       </c>
       <c r="K166" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L166" s="18"/>
       <c r="M166" s="18">
@@ -59894,7 +59895,7 @@
         <v>889</v>
       </c>
       <c r="D167" s="18" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="E167" s="18">
         <v>5.4100000000000002E-2</v>
@@ -59913,7 +59914,7 @@
         <v>588</v>
       </c>
       <c r="K167" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L167" s="18"/>
       <c r="M167" s="18">
@@ -59936,7 +59937,7 @@
         <v>889</v>
       </c>
       <c r="D168" s="18" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="E168" s="18">
         <v>5.8099999999999999E-2</v>
@@ -59955,7 +59956,7 @@
         <v>588</v>
       </c>
       <c r="K168" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L168" s="18"/>
       <c r="M168" s="18">
@@ -59978,7 +59979,7 @@
         <v>889</v>
       </c>
       <c r="D169" s="18" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="E169" s="18">
         <v>5.1700000000000003E-2</v>
@@ -59997,7 +59998,7 @@
         <v>588</v>
       </c>
       <c r="K169" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L169" s="18"/>
       <c r="M169" s="18">
@@ -60020,7 +60021,7 @@
         <v>889</v>
       </c>
       <c r="D170" s="18" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="E170" s="18">
         <v>3.8300000000000001E-2</v>
@@ -60039,7 +60040,7 @@
         <v>588</v>
       </c>
       <c r="K170" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L170" s="18"/>
       <c r="M170" s="18">
@@ -60062,7 +60063,7 @@
         <v>889</v>
       </c>
       <c r="D171" s="18" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="E171" s="18">
         <v>3.4599999999999999E-2</v>
@@ -60081,7 +60082,7 @@
         <v>588</v>
       </c>
       <c r="K171" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L171" s="18"/>
       <c r="M171" s="18">
@@ -60104,7 +60105,7 @@
         <v>889</v>
       </c>
       <c r="D172" s="18" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="E172" s="18">
         <v>4.9500000000000002E-2</v>
@@ -60123,7 +60124,7 @@
         <v>588</v>
       </c>
       <c r="K172" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L172" s="18"/>
       <c r="M172" s="18">
@@ -60146,7 +60147,7 @@
         <v>889</v>
       </c>
       <c r="D173" s="18" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="E173" s="18">
         <v>4.9200000000000001E-2</v>
@@ -60165,7 +60166,7 @@
         <v>588</v>
       </c>
       <c r="K173" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L173" s="18"/>
       <c r="M173" s="18">
@@ -60188,7 +60189,7 @@
         <v>889</v>
       </c>
       <c r="D174" s="18" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="E174" s="18">
         <v>5.8999999999999997E-2</v>
@@ -60198,7 +60199,7 @@
       </c>
       <c r="G174" s="18"/>
       <c r="H174" s="18" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="I174" s="18" t="s">
         <v>43</v>
@@ -60207,7 +60208,7 @@
         <v>588</v>
       </c>
       <c r="K174" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L174" s="18"/>
       <c r="M174" s="18">
@@ -60230,7 +60231,7 @@
         <v>889</v>
       </c>
       <c r="D175" s="18" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="E175" s="18">
         <v>6.4399999999999999E-2</v>
@@ -60249,7 +60250,7 @@
         <v>588</v>
       </c>
       <c r="K175" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L175" s="18"/>
       <c r="M175" s="18">
@@ -60272,7 +60273,7 @@
         <v>889</v>
       </c>
       <c r="D176" s="18" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="E176" s="18">
         <v>3.1675000000000002E-2</v>
@@ -60291,7 +60292,7 @@
         <v>588</v>
       </c>
       <c r="K176" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L176" s="18"/>
       <c r="M176" s="18">
@@ -60314,7 +60315,7 @@
         <v>889</v>
       </c>
       <c r="D177" s="18" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="E177" s="18">
         <v>4.07E-2</v>
@@ -60333,7 +60334,7 @@
         <v>588</v>
       </c>
       <c r="K177" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L177" s="18"/>
       <c r="M177" s="18">
@@ -60356,7 +60357,7 @@
         <v>889</v>
       </c>
       <c r="D178" s="18" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="E178" s="18">
         <v>2.6200000000000001E-2</v>
@@ -60366,7 +60367,7 @@
       </c>
       <c r="G178" s="18"/>
       <c r="H178" s="18" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="I178" s="18" t="s">
         <v>69</v>
@@ -60375,7 +60376,7 @@
         <v>588</v>
       </c>
       <c r="K178" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L178" s="18"/>
       <c r="M178" s="18">
@@ -60398,7 +60399,7 @@
         <v>889</v>
       </c>
       <c r="D179" s="18" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="E179" s="18">
         <v>2.904E-2</v>
@@ -60417,7 +60418,7 @@
         <v>588</v>
       </c>
       <c r="K179" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L179" s="18"/>
       <c r="M179" s="18">
@@ -60440,7 +60441,7 @@
         <v>889</v>
       </c>
       <c r="D180" s="18" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="E180" s="18">
         <v>4.2299999999999997E-2</v>
@@ -60459,7 +60460,7 @@
         <v>588</v>
       </c>
       <c r="K180" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L180" s="18"/>
       <c r="M180" s="18">
@@ -60482,7 +60483,7 @@
         <v>889</v>
       </c>
       <c r="D181" s="18" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="E181" s="18">
         <v>2.9399999999999999E-2</v>
@@ -60501,7 +60502,7 @@
         <v>588</v>
       </c>
       <c r="K181" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L181" s="18"/>
       <c r="M181" s="18">
@@ -60524,7 +60525,7 @@
         <v>889</v>
       </c>
       <c r="D182" s="18" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="E182" s="18">
         <v>6.1223300000000001E-2</v>
@@ -60534,7 +60535,7 @@
       </c>
       <c r="G182" s="18"/>
       <c r="H182" s="18" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="I182" s="18" t="s">
         <v>69</v>
@@ -60543,7 +60544,7 @@
         <v>588</v>
       </c>
       <c r="K182" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L182" s="18"/>
       <c r="M182" s="18">
@@ -60566,7 +60567,7 @@
         <v>889</v>
       </c>
       <c r="D183" s="18" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="E183" s="18">
         <v>4.9578299999999999E-2</v>
@@ -60576,7 +60577,7 @@
       </c>
       <c r="G183" s="18"/>
       <c r="H183" s="18" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="I183" s="18" t="s">
         <v>69</v>
@@ -60585,7 +60586,7 @@
         <v>588</v>
       </c>
       <c r="K183" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L183" s="18"/>
       <c r="M183" s="18">
@@ -60608,7 +60609,7 @@
         <v>889</v>
       </c>
       <c r="D184" s="18" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="E184" s="18">
         <v>3.4535000000000003E-2</v>
@@ -60618,7 +60619,7 @@
       </c>
       <c r="G184" s="18"/>
       <c r="H184" s="18" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="I184" s="18" t="s">
         <v>69</v>
@@ -60627,7 +60628,7 @@
         <v>588</v>
       </c>
       <c r="K184" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L184" s="18"/>
       <c r="M184" s="18">
@@ -60650,7 +60651,7 @@
         <v>889</v>
       </c>
       <c r="D185" s="18" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="E185" s="18">
         <v>3.2671699999999998E-2</v>
@@ -60660,7 +60661,7 @@
       </c>
       <c r="G185" s="18"/>
       <c r="H185" s="18" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="I185" s="18" t="s">
         <v>69</v>
@@ -60669,7 +60670,7 @@
         <v>588</v>
       </c>
       <c r="K185" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L185" s="18"/>
       <c r="M185" s="18">
@@ -60692,7 +60693,7 @@
         <v>889</v>
       </c>
       <c r="D186" s="18" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="E186" s="18">
         <v>2.5999999999999999E-2</v>
@@ -60711,7 +60712,7 @@
         <v>588</v>
       </c>
       <c r="K186" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L186" s="18"/>
       <c r="M186" s="18">
@@ -60734,7 +60735,7 @@
         <v>889</v>
       </c>
       <c r="D187" s="18" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="E187" s="18">
         <v>2.3800000000000002E-2</v>
@@ -60744,7 +60745,7 @@
       </c>
       <c r="G187" s="18"/>
       <c r="H187" s="18" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="I187" s="18" t="s">
         <v>69</v>
@@ -60753,7 +60754,7 @@
         <v>588</v>
       </c>
       <c r="K187" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L187" s="18"/>
       <c r="M187" s="18">
@@ -60776,7 +60777,7 @@
         <v>889</v>
       </c>
       <c r="D188" s="18" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="E188" s="18">
         <v>4.1988299999999999E-2</v>
@@ -60786,7 +60787,7 @@
       </c>
       <c r="G188" s="18"/>
       <c r="H188" s="18" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="I188" s="18" t="s">
         <v>69</v>
@@ -60795,7 +60796,7 @@
         <v>588</v>
       </c>
       <c r="K188" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L188" s="18"/>
       <c r="M188" s="18">
@@ -60818,7 +60819,7 @@
         <v>889</v>
       </c>
       <c r="D189" s="18" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E189" s="18">
         <v>2.7099999999999999E-2</v>
@@ -60828,7 +60829,7 @@
       </c>
       <c r="G189" s="18"/>
       <c r="H189" s="18" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="I189" s="18" t="s">
         <v>69</v>
@@ -60837,7 +60838,7 @@
         <v>588</v>
       </c>
       <c r="K189" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L189" s="18"/>
       <c r="M189" s="18">
@@ -60860,7 +60861,7 @@
         <v>889</v>
       </c>
       <c r="D190" s="18" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="E190" s="18">
         <v>2.56283E-2</v>
@@ -60870,7 +60871,7 @@
       </c>
       <c r="G190" s="18"/>
       <c r="H190" s="18" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="I190" s="18" t="s">
         <v>69</v>
@@ -60879,7 +60880,7 @@
         <v>588</v>
       </c>
       <c r="K190" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L190" s="18"/>
       <c r="M190" s="18">
@@ -60902,7 +60903,7 @@
         <v>889</v>
       </c>
       <c r="D191" s="18" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="E191" s="18">
         <v>3.8399999999999997E-2</v>
@@ -60912,7 +60913,7 @@
       </c>
       <c r="G191" s="18"/>
       <c r="H191" s="18" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="I191" s="18" t="s">
         <v>69</v>
@@ -60921,7 +60922,7 @@
         <v>588</v>
       </c>
       <c r="K191" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L191" s="18"/>
       <c r="M191" s="18">
@@ -60944,7 +60945,7 @@
         <v>889</v>
       </c>
       <c r="D192" s="18" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E192" s="18">
         <v>2.6006600000000001E-2</v>
@@ -60954,7 +60955,7 @@
       </c>
       <c r="G192" s="18"/>
       <c r="H192" s="18" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="I192" s="18" t="s">
         <v>69</v>
@@ -60963,7 +60964,7 @@
         <v>588</v>
       </c>
       <c r="K192" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L192" s="18"/>
       <c r="M192" s="18">
@@ -60986,7 +60987,7 @@
         <v>889</v>
       </c>
       <c r="D193" s="18" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="E193" s="18">
         <v>2.3968300000000001E-2</v>
@@ -61005,7 +61006,7 @@
         <v>588</v>
       </c>
       <c r="K193" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L193" s="18"/>
       <c r="M193" s="18">
@@ -61028,7 +61029,7 @@
         <v>889</v>
       </c>
       <c r="D194" s="18" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="E194" s="18">
         <v>3.0865799999999999E-2</v>
@@ -61038,7 +61039,7 @@
       </c>
       <c r="G194" s="18"/>
       <c r="H194" s="18" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="I194" s="18" t="s">
         <v>69</v>
@@ -61047,7 +61048,7 @@
         <v>588</v>
       </c>
       <c r="K194" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L194" s="18"/>
       <c r="M194" s="18">
@@ -61070,7 +61071,7 @@
         <v>889</v>
       </c>
       <c r="D195" s="18" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="E195" s="18">
         <v>2.3435000000000001E-2</v>
@@ -61080,7 +61081,7 @@
       </c>
       <c r="G195" s="18"/>
       <c r="H195" s="18" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="I195" s="18" t="s">
         <v>69</v>
@@ -61089,7 +61090,7 @@
         <v>588</v>
       </c>
       <c r="K195" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L195" s="18"/>
       <c r="M195" s="18">
@@ -61112,7 +61113,7 @@
         <v>889</v>
       </c>
       <c r="D196" s="18" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="E196" s="18">
         <v>2.75E-2</v>
@@ -61122,7 +61123,7 @@
       </c>
       <c r="G196" s="18"/>
       <c r="H196" s="18" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="I196" s="18" t="s">
         <v>69</v>
@@ -61131,7 +61132,7 @@
         <v>588</v>
       </c>
       <c r="K196" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L196" s="18"/>
       <c r="M196" s="18">
@@ -61154,7 +61155,7 @@
         <v>889</v>
       </c>
       <c r="D197" s="18" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="E197" s="18">
         <v>1.0185E-2</v>
@@ -61173,7 +61174,7 @@
         <v>588</v>
       </c>
       <c r="K197" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L197" s="18"/>
       <c r="M197" s="18">
@@ -61196,7 +61197,7 @@
         <v>889</v>
       </c>
       <c r="D198" s="18" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="E198" s="18">
         <v>6.3E-3</v>
@@ -61215,7 +61216,7 @@
         <v>588</v>
       </c>
       <c r="K198" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L198" s="18"/>
       <c r="M198" s="18">
@@ -61238,7 +61239,7 @@
         <v>889</v>
       </c>
       <c r="D199" s="18" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="E199" s="18">
         <v>2.09483E-2</v>
@@ -61257,7 +61258,7 @@
         <v>588</v>
       </c>
       <c r="K199" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L199" s="18"/>
       <c r="M199" s="18">
@@ -61280,7 +61281,7 @@
         <v>889</v>
       </c>
       <c r="D200" s="18" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="E200" s="18">
         <v>3.7699999999999997E-2</v>
@@ -61299,7 +61300,7 @@
         <v>588</v>
       </c>
       <c r="K200" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L200" s="18"/>
       <c r="M200" s="18">
@@ -61322,7 +61323,7 @@
         <v>889</v>
       </c>
       <c r="D201" s="18" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="E201" s="18">
         <v>2.3734999999999999E-2</v>
@@ -61341,7 +61342,7 @@
         <v>588</v>
       </c>
       <c r="K201" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L201" s="18"/>
       <c r="M201" s="18">
@@ -61364,7 +61365,7 @@
         <v>889</v>
       </c>
       <c r="D202" s="18" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="E202" s="18">
         <v>1.789E-2</v>
@@ -61383,7 +61384,7 @@
         <v>588</v>
       </c>
       <c r="K202" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L202" s="18"/>
       <c r="M202" s="18">
@@ -61406,7 +61407,7 @@
         <v>889</v>
       </c>
       <c r="D203" s="18" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E203" s="18">
         <v>1.7126700000000002E-2</v>
@@ -61425,7 +61426,7 @@
         <v>588</v>
       </c>
       <c r="K203" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L203" s="18"/>
       <c r="M203" s="18">
@@ -61448,7 +61449,7 @@
         <v>889</v>
       </c>
       <c r="D204" s="18" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E204" s="18">
         <v>1.4E-2</v>
@@ -61467,7 +61468,7 @@
         <v>588</v>
       </c>
       <c r="K204" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L204" s="18"/>
       <c r="M204" s="18">
@@ -61490,7 +61491,7 @@
         <v>889</v>
       </c>
       <c r="D205" s="18" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="E205" s="18">
         <v>1.7338300000000001E-2</v>
@@ -61509,7 +61510,7 @@
         <v>588</v>
       </c>
       <c r="K205" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L205" s="18"/>
       <c r="M205" s="18">
@@ -61532,7 +61533,7 @@
         <v>889</v>
       </c>
       <c r="D206" s="18" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="E206" s="18">
         <v>1.8714999999999999E-2</v>
@@ -61551,7 +61552,7 @@
         <v>588</v>
       </c>
       <c r="K206" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L206" s="18"/>
       <c r="M206" s="18">
@@ -61574,7 +61575,7 @@
         <v>889</v>
       </c>
       <c r="D207" s="18" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E207" s="18">
         <v>6.6950000000000004E-3</v>
@@ -61593,7 +61594,7 @@
         <v>588</v>
       </c>
       <c r="K207" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L207" s="18"/>
       <c r="M207" s="18">
@@ -61616,7 +61617,7 @@
         <v>889</v>
       </c>
       <c r="D208" s="18" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="E208" s="18">
         <v>1.0416699999999999E-2</v>
@@ -61635,7 +61636,7 @@
         <v>588</v>
       </c>
       <c r="K208" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L208" s="18"/>
       <c r="M208" s="18">
@@ -61658,7 +61659,7 @@
         <v>889</v>
       </c>
       <c r="D209" s="18" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="E209" s="18">
         <v>1.0800000000000001E-2</v>
@@ -61677,7 +61678,7 @@
         <v>588</v>
       </c>
       <c r="K209" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L209" s="18"/>
       <c r="M209" s="18">
@@ -61700,7 +61701,7 @@
         <v>889</v>
       </c>
       <c r="D210" s="18" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E210" s="18">
         <v>6.0000000000000001E-3</v>
@@ -61719,7 +61720,7 @@
         <v>588</v>
       </c>
       <c r="K210" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L210" s="18"/>
       <c r="M210" s="18">
@@ -61742,7 +61743,7 @@
         <v>889</v>
       </c>
       <c r="D211" s="18" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="E211" s="18">
         <v>7.2150000000000001E-3</v>
@@ -61761,7 +61762,7 @@
         <v>588</v>
       </c>
       <c r="K211" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L211" s="18"/>
       <c r="M211" s="18">
@@ -61784,7 +61785,7 @@
         <v>889</v>
       </c>
       <c r="D212" s="18" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="E212" s="18">
         <v>5.9033000000000002E-3</v>
@@ -61803,7 +61804,7 @@
         <v>588</v>
       </c>
       <c r="K212" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L212" s="18"/>
       <c r="M212" s="18">
@@ -61826,7 +61827,7 @@
         <v>889</v>
       </c>
       <c r="D213" s="18" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="E213" s="18">
         <v>6.5732999999999998E-3</v>
@@ -61845,7 +61846,7 @@
         <v>588</v>
       </c>
       <c r="K213" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L213" s="18"/>
       <c r="M213" s="18">
@@ -61868,7 +61869,7 @@
         <v>889</v>
       </c>
       <c r="D214" s="18" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="E214" s="18">
         <v>6.4000000000000003E-3</v>
@@ -61887,7 +61888,7 @@
         <v>588</v>
       </c>
       <c r="K214" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L214" s="18"/>
       <c r="M214" s="18">
@@ -61910,7 +61911,7 @@
         <v>889</v>
       </c>
       <c r="D215" s="18" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="E215" s="18">
         <v>6.4999999999999997E-3</v>
@@ -61929,7 +61930,7 @@
         <v>588</v>
       </c>
       <c r="K215" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L215" s="18"/>
       <c r="M215" s="18">
@@ -61952,7 +61953,7 @@
         <v>889</v>
       </c>
       <c r="D216" s="18" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="E216" s="18">
         <v>2.4211699999999999E-2</v>
@@ -61971,7 +61972,7 @@
         <v>588</v>
       </c>
       <c r="K216" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L216" s="18"/>
       <c r="M216" s="18">
@@ -61994,7 +61995,7 @@
         <v>889</v>
       </c>
       <c r="D217" s="18" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="E217" s="18">
         <v>2.0371E-2</v>
@@ -62013,7 +62014,7 @@
         <v>588</v>
       </c>
       <c r="K217" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L217" s="18"/>
       <c r="M217" s="18">
@@ -62036,7 +62037,7 @@
         <v>889</v>
       </c>
       <c r="D218" s="18" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="E218" s="18">
         <v>1.18E-2</v>
@@ -62055,7 +62056,7 @@
         <v>588</v>
       </c>
       <c r="K218" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L218" s="18"/>
       <c r="M218" s="18">
@@ -62078,7 +62079,7 @@
         <v>889</v>
       </c>
       <c r="D219" s="18" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="E219" s="18">
         <v>1.89E-2</v>
@@ -62097,7 +62098,7 @@
         <v>588</v>
       </c>
       <c r="K219" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L219" s="18"/>
       <c r="M219" s="18">
@@ -62120,7 +62121,7 @@
         <v>889</v>
       </c>
       <c r="D220" s="18" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="E220" s="18">
         <v>4.0200000000000001E-5</v>
@@ -62139,7 +62140,7 @@
         <v>588</v>
       </c>
       <c r="K220" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L220" s="18"/>
       <c r="M220" s="18">
@@ -62162,7 +62163,7 @@
         <v>889</v>
       </c>
       <c r="D221" s="18" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="E221" s="18">
         <v>7.1999999999999998E-3</v>
@@ -62181,7 +62182,7 @@
         <v>588</v>
       </c>
       <c r="K221" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L221" s="18"/>
       <c r="M221" s="18">
@@ -62204,7 +62205,7 @@
         <v>889</v>
       </c>
       <c r="D222" s="18" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="E222" s="18">
         <v>1.14E-2</v>
@@ -62223,7 +62224,7 @@
         <v>588</v>
       </c>
       <c r="K222" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L222" s="18"/>
       <c r="M222" s="18">
@@ -62246,7 +62247,7 @@
         <v>889</v>
       </c>
       <c r="D223" s="18" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="E223" s="18">
         <v>7.1000000000000004E-3</v>
@@ -62265,7 +62266,7 @@
         <v>588</v>
       </c>
       <c r="K223" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L223" s="18"/>
       <c r="M223" s="18">
@@ -62288,7 +62289,7 @@
         <v>889</v>
       </c>
       <c r="D224" s="18" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="E224" s="18">
         <v>6.9999999999999999E-4</v>
@@ -62307,7 +62308,7 @@
         <v>588</v>
       </c>
       <c r="K224" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L224" s="18"/>
       <c r="M224" s="18">
@@ -62330,7 +62331,7 @@
         <v>889</v>
       </c>
       <c r="D225" s="18" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="E225" s="18">
         <v>1.54E-2</v>
@@ -62349,7 +62350,7 @@
         <v>588</v>
       </c>
       <c r="K225" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L225" s="18"/>
       <c r="M225" s="18">
@@ -62372,7 +62373,7 @@
         <v>889</v>
       </c>
       <c r="D226" s="18" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="E226" s="18">
         <v>8.3000000000000001E-3</v>
@@ -62391,7 +62392,7 @@
         <v>588</v>
       </c>
       <c r="K226" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L226" s="18"/>
       <c r="M226" s="18">
@@ -62414,7 +62415,7 @@
         <v>889</v>
       </c>
       <c r="D227" s="18" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="E227" s="18">
         <v>1.1299999999999999E-2</v>
@@ -62433,7 +62434,7 @@
         <v>588</v>
       </c>
       <c r="K227" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L227" s="18"/>
       <c r="M227" s="18">
@@ -62456,7 +62457,7 @@
         <v>889</v>
       </c>
       <c r="D228" s="18" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="E228" s="18">
         <v>1.5299999999999999E-2</v>
@@ -62475,7 +62476,7 @@
         <v>588</v>
       </c>
       <c r="K228" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L228" s="18"/>
       <c r="M228" s="18">
@@ -62498,7 +62499,7 @@
         <v>889</v>
       </c>
       <c r="D229" s="18" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="E229" s="18">
         <v>1.5100000000000001E-2</v>
@@ -62517,7 +62518,7 @@
         <v>588</v>
       </c>
       <c r="K229" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L229" s="18"/>
       <c r="M229" s="18">
@@ -62540,7 +62541,7 @@
         <v>889</v>
       </c>
       <c r="D230" s="18" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="E230" s="18">
         <v>1.1900000000000001E-2</v>
@@ -62559,7 +62560,7 @@
         <v>588</v>
       </c>
       <c r="K230" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L230" s="18"/>
       <c r="M230" s="18">
@@ -62582,7 +62583,7 @@
         <v>889</v>
       </c>
       <c r="D231" s="18" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="E231" s="18">
         <v>7.4000000000000003E-3</v>
@@ -62601,7 +62602,7 @@
         <v>588</v>
       </c>
       <c r="K231" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L231" s="18"/>
       <c r="M231" s="18">
@@ -62624,7 +62625,7 @@
         <v>889</v>
       </c>
       <c r="D232" s="18" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="E232" s="18">
         <v>1.2500000000000001E-2</v>
@@ -62643,7 +62644,7 @@
         <v>588</v>
       </c>
       <c r="K232" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L232" s="18"/>
       <c r="M232" s="18">
@@ -62666,7 +62667,7 @@
         <v>889</v>
       </c>
       <c r="D233" s="18" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="E233" s="18">
         <v>2.8999999999999998E-3</v>
@@ -62685,7 +62686,7 @@
         <v>588</v>
       </c>
       <c r="K233" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L233" s="18"/>
       <c r="M233" s="18">
@@ -62708,7 +62709,7 @@
         <v>889</v>
       </c>
       <c r="D234" s="18" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="E234" s="18">
         <v>1.2500000000000001E-2</v>
@@ -62727,7 +62728,7 @@
         <v>588</v>
       </c>
       <c r="K234" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L234" s="18"/>
       <c r="M234" s="18">
@@ -62750,7 +62751,7 @@
         <v>889</v>
       </c>
       <c r="D235" s="18" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="E235" s="18">
         <v>5.3E-3</v>
@@ -62769,7 +62770,7 @@
         <v>588</v>
       </c>
       <c r="K235" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L235" s="18"/>
       <c r="M235" s="18">
@@ -62792,7 +62793,7 @@
         <v>889</v>
       </c>
       <c r="D236" s="18" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="E236" s="18">
         <v>2.8E-3</v>
@@ -62811,7 +62812,7 @@
         <v>588</v>
       </c>
       <c r="K236" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L236" s="18"/>
       <c r="M236" s="18">
@@ -62834,7 +62835,7 @@
         <v>889</v>
       </c>
       <c r="D237" s="18" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="E237" s="18">
         <v>2.5999999999999999E-3</v>
@@ -62853,7 +62854,7 @@
         <v>588</v>
       </c>
       <c r="K237" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L237" s="18"/>
       <c r="M237" s="18">
@@ -62876,7 +62877,7 @@
         <v>889</v>
       </c>
       <c r="D238" s="18" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="E238" s="18">
         <v>6.8999999999999999E-3</v>
@@ -62895,7 +62896,7 @@
         <v>588</v>
       </c>
       <c r="K238" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L238" s="18"/>
       <c r="M238" s="18">
@@ -62918,7 +62919,7 @@
         <v>889</v>
       </c>
       <c r="D239" s="18" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="E239" s="18">
         <v>7.7000000000000002E-3</v>
@@ -62937,7 +62938,7 @@
         <v>588</v>
       </c>
       <c r="K239" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L239" s="18"/>
       <c r="M239" s="18">
@@ -62960,7 +62961,7 @@
         <v>889</v>
       </c>
       <c r="D240" s="18" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="E240" s="18">
         <v>6.1000000000000004E-3</v>
@@ -62979,7 +62980,7 @@
         <v>588</v>
       </c>
       <c r="K240" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L240" s="18"/>
       <c r="M240" s="18">
@@ -63002,7 +63003,7 @@
         <v>889</v>
       </c>
       <c r="D241" s="18" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="E241" s="18">
         <v>1.6500000000000001E-2</v>
@@ -63021,7 +63022,7 @@
         <v>588</v>
       </c>
       <c r="K241" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L241" s="18"/>
       <c r="M241" s="18">
@@ -63044,7 +63045,7 @@
         <v>889</v>
       </c>
       <c r="D242" s="18" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="E242" s="18">
         <v>1.7999999999999999E-2</v>
@@ -63063,7 +63064,7 @@
         <v>588</v>
       </c>
       <c r="K242" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L242" s="18"/>
       <c r="M242" s="18">
@@ -63086,7 +63087,7 @@
         <v>889</v>
       </c>
       <c r="D243" s="18" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="E243" s="18">
         <v>1.43E-2</v>
@@ -63105,7 +63106,7 @@
         <v>588</v>
       </c>
       <c r="K243" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L243" s="18"/>
       <c r="M243" s="18">
@@ -63128,7 +63129,7 @@
         <v>889</v>
       </c>
       <c r="D244" s="18" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="E244" s="18">
         <v>5.1999999999999998E-3</v>
@@ -63147,7 +63148,7 @@
         <v>588</v>
       </c>
       <c r="K244" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L244" s="18"/>
       <c r="M244" s="18">
@@ -63170,7 +63171,7 @@
         <v>889</v>
       </c>
       <c r="D245" s="18" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="E245" s="18">
         <v>5.0000000000000001E-3</v>
@@ -63189,7 +63190,7 @@
         <v>588</v>
       </c>
       <c r="K245" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L245" s="18"/>
       <c r="M245" s="18">
@@ -63212,7 +63213,7 @@
         <v>889</v>
       </c>
       <c r="D246" s="18" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="E246" s="18">
         <v>1.21E-2</v>
@@ -63231,7 +63232,7 @@
         <v>588</v>
       </c>
       <c r="K246" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L246" s="18"/>
       <c r="M246" s="18">
@@ -63254,7 +63255,7 @@
         <v>889</v>
       </c>
       <c r="D247" s="18" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="E247" s="18">
         <v>1.3100000000000001E-2</v>
@@ -63273,7 +63274,7 @@
         <v>588</v>
       </c>
       <c r="K247" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L247" s="18"/>
       <c r="M247" s="18">
@@ -63296,7 +63297,7 @@
         <v>889</v>
       </c>
       <c r="D248" s="18" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="E248" s="18">
         <v>6.2820000000000003E-3</v>
@@ -63315,7 +63316,7 @@
         <v>588</v>
       </c>
       <c r="K248" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L248" s="18"/>
       <c r="M248" s="18">
@@ -63338,7 +63339,7 @@
         <v>889</v>
       </c>
       <c r="D249" s="18" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="E249" s="18">
         <v>2.5499999999999998E-2</v>
@@ -63357,7 +63358,7 @@
         <v>588</v>
       </c>
       <c r="K249" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L249" s="18"/>
       <c r="M249" s="18">
@@ -63380,7 +63381,7 @@
         <v>889</v>
       </c>
       <c r="D250" s="18" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="E250" s="18">
         <v>2.3099999999999999E-2</v>
@@ -63399,7 +63400,7 @@
         <v>588</v>
       </c>
       <c r="K250" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L250" s="18"/>
       <c r="M250" s="18">
@@ -63422,7 +63423,7 @@
         <v>889</v>
       </c>
       <c r="D251" s="18" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="E251" s="18">
         <v>2.1999999999999999E-2</v>
@@ -63441,7 +63442,7 @@
         <v>588</v>
       </c>
       <c r="K251" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L251" s="18"/>
       <c r="M251" s="18">
@@ -63464,7 +63465,7 @@
         <v>889</v>
       </c>
       <c r="D252" s="18" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="E252" s="18">
         <v>1.9300000000000001E-2</v>
@@ -63483,7 +63484,7 @@
         <v>588</v>
       </c>
       <c r="K252" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L252" s="18"/>
       <c r="M252" s="18">
@@ -63506,7 +63507,7 @@
         <v>889</v>
       </c>
       <c r="D253" s="18" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="E253" s="18">
         <v>3.8199999999999998E-2</v>
@@ -63525,7 +63526,7 @@
         <v>588</v>
       </c>
       <c r="K253" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L253" s="18"/>
       <c r="M253" s="18">
@@ -63548,7 +63549,7 @@
         <v>889</v>
       </c>
       <c r="D254" s="18" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="E254" s="18">
         <v>3.4599999999999999E-2</v>
@@ -63567,7 +63568,7 @@
         <v>588</v>
       </c>
       <c r="K254" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L254" s="18"/>
       <c r="M254" s="18">
@@ -63590,7 +63591,7 @@
         <v>889</v>
       </c>
       <c r="D255" s="18" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="E255" s="18">
         <v>2.3599999999999999E-2</v>
@@ -63609,7 +63610,7 @@
         <v>588</v>
       </c>
       <c r="K255" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L255" s="18"/>
       <c r="M255" s="18">
@@ -63632,7 +63633,7 @@
         <v>889</v>
       </c>
       <c r="D256" s="18" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="E256" s="18">
         <v>3.0800000000000001E-2</v>
@@ -63651,7 +63652,7 @@
         <v>588</v>
       </c>
       <c r="K256" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L256" s="18"/>
       <c r="M256" s="18">
@@ -63674,7 +63675,7 @@
         <v>889</v>
       </c>
       <c r="D257" s="18" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="E257" s="18">
         <v>3.7900000000000003E-2</v>
@@ -63693,7 +63694,7 @@
         <v>588</v>
       </c>
       <c r="K257" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L257" s="18"/>
       <c r="M257" s="18">
@@ -63716,7 +63717,7 @@
         <v>889</v>
       </c>
       <c r="D258" s="18" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E258" s="18">
         <v>3.2000000000000001E-2</v>
@@ -63735,7 +63736,7 @@
         <v>588</v>
       </c>
       <c r="K258" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L258" s="18"/>
       <c r="M258" s="18">
@@ -63758,7 +63759,7 @@
         <v>889</v>
       </c>
       <c r="D259" s="18" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="E259" s="18">
         <v>2.4299999999999999E-2</v>
@@ -63777,7 +63778,7 @@
         <v>588</v>
       </c>
       <c r="K259" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L259" s="18"/>
       <c r="M259" s="18">
@@ -63800,7 +63801,7 @@
         <v>889</v>
       </c>
       <c r="D260" s="18" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="E260" s="18">
         <v>3.8899999999999997E-2</v>
@@ -63819,7 +63820,7 @@
         <v>588</v>
       </c>
       <c r="K260" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L260" s="18"/>
       <c r="M260" s="18">
@@ -63842,7 +63843,7 @@
         <v>889</v>
       </c>
       <c r="D261" s="18" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="E261" s="18">
         <v>5.16E-2</v>
@@ -63861,7 +63862,7 @@
         <v>588</v>
       </c>
       <c r="K261" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L261" s="18"/>
       <c r="M261" s="18">
@@ -63884,7 +63885,7 @@
         <v>889</v>
       </c>
       <c r="D262" s="18" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="E262" s="18">
         <v>4.6699999999999998E-2</v>
@@ -63903,7 +63904,7 @@
         <v>588</v>
       </c>
       <c r="K262" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L262" s="18"/>
       <c r="M262" s="18">
@@ -63926,7 +63927,7 @@
         <v>889</v>
       </c>
       <c r="D263" s="18" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="E263" s="18">
         <v>2.7099999999999999E-2</v>
@@ -63945,7 +63946,7 @@
         <v>588</v>
       </c>
       <c r="K263" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L263" s="18"/>
       <c r="M263" s="18">
@@ -63968,7 +63969,7 @@
         <v>889</v>
       </c>
       <c r="D264" s="18" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="E264" s="18">
         <v>0.06</v>
@@ -63987,7 +63988,7 @@
         <v>588</v>
       </c>
       <c r="K264" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L264" s="18"/>
       <c r="M264" s="18">
@@ -64010,7 +64011,7 @@
         <v>889</v>
       </c>
       <c r="D265" s="18" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="E265" s="18">
         <v>2.4299999999999999E-2</v>
@@ -64029,7 +64030,7 @@
         <v>588</v>
       </c>
       <c r="K265" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L265" s="18"/>
       <c r="M265" s="18">
@@ -64052,7 +64053,7 @@
         <v>889</v>
       </c>
       <c r="D266" s="18" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="E266" s="18">
         <v>3.49E-2</v>
@@ -64071,7 +64072,7 @@
         <v>588</v>
       </c>
       <c r="K266" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L266" s="18"/>
       <c r="M266" s="18">
@@ -64094,7 +64095,7 @@
         <v>889</v>
       </c>
       <c r="D267" s="18" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="E267" s="18">
         <v>5.0200000000000002E-2</v>
@@ -64113,7 +64114,7 @@
         <v>588</v>
       </c>
       <c r="K267" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L267" s="18"/>
       <c r="M267" s="18">
@@ -64136,7 +64137,7 @@
         <v>889</v>
       </c>
       <c r="D268" s="18" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="E268" s="18">
         <v>5.9799999999999999E-2</v>
@@ -64155,7 +64156,7 @@
         <v>588</v>
       </c>
       <c r="K268" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L268" s="18"/>
       <c r="M268" s="18">
@@ -64178,7 +64179,7 @@
         <v>889</v>
       </c>
       <c r="D269" s="18" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="E269" s="18">
         <v>0.05</v>
@@ -64197,7 +64198,7 @@
         <v>588</v>
       </c>
       <c r="K269" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L269" s="18"/>
       <c r="M269" s="18">
@@ -64220,7 +64221,7 @@
         <v>889</v>
       </c>
       <c r="D270" s="18" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="E270" s="18">
         <v>7.0999999999999994E-2</v>
@@ -64239,7 +64240,7 @@
         <v>588</v>
       </c>
       <c r="K270" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L270" s="18"/>
       <c r="M270" s="18">
@@ -64262,7 +64263,7 @@
         <v>889</v>
       </c>
       <c r="D271" s="18" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="E271" s="18">
         <v>4.9299999999999997E-2</v>
@@ -64281,7 +64282,7 @@
         <v>588</v>
       </c>
       <c r="K271" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L271" s="18"/>
       <c r="M271" s="18">
@@ -64304,7 +64305,7 @@
         <v>889</v>
       </c>
       <c r="D272" s="18" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="E272" s="18">
         <v>0.06</v>
@@ -64323,7 +64324,7 @@
         <v>588</v>
       </c>
       <c r="K272" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L272" s="18"/>
       <c r="M272" s="18">
@@ -64346,7 +64347,7 @@
         <v>889</v>
       </c>
       <c r="D273" s="18" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="E273" s="18">
         <v>7.7817999999999998E-2</v>
@@ -64365,7 +64366,7 @@
         <v>588</v>
       </c>
       <c r="K273" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L273" s="18"/>
       <c r="M273" s="18">
@@ -64388,7 +64389,7 @@
         <v>889</v>
       </c>
       <c r="D274" s="18" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="E274" s="18">
         <v>5.8200000000000002E-2</v>
@@ -64407,7 +64408,7 @@
         <v>588</v>
       </c>
       <c r="K274" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L274" s="18"/>
       <c r="M274" s="18">
@@ -64430,7 +64431,7 @@
         <v>889</v>
       </c>
       <c r="D275" s="18" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="E275" s="18"/>
       <c r="F275" s="18"/>
@@ -64462,7 +64463,7 @@
         <v>959</v>
       </c>
       <c r="D276" s="18" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="E276" s="18">
         <v>3.7400000000000003E-2</v>
@@ -64481,7 +64482,7 @@
         <v>588</v>
       </c>
       <c r="K276" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L276" s="18"/>
       <c r="M276" s="18">
@@ -64504,7 +64505,7 @@
         <v>959</v>
       </c>
       <c r="D277" s="18" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="E277" s="18">
         <v>3.7900000000000003E-2</v>
@@ -64523,7 +64524,7 @@
         <v>588</v>
       </c>
       <c r="K277" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L277" s="18"/>
       <c r="M277" s="18">
@@ -64546,7 +64547,7 @@
         <v>959</v>
       </c>
       <c r="D278" s="18" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="E278" s="18">
         <v>4.8500000000000001E-2</v>
@@ -64565,7 +64566,7 @@
         <v>588</v>
       </c>
       <c r="K278" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L278" s="18"/>
       <c r="M278" s="18">
@@ -64588,7 +64589,7 @@
         <v>959</v>
       </c>
       <c r="D279" s="18" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="E279" s="18">
         <v>5.8299999999999998E-2</v>
@@ -64607,7 +64608,7 @@
         <v>588</v>
       </c>
       <c r="K279" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L279" s="18"/>
       <c r="M279" s="18">
@@ -64630,7 +64631,7 @@
         <v>959</v>
       </c>
       <c r="D280" s="18" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="E280" s="18">
         <v>3.5999999999999997E-2</v>
@@ -64649,7 +64650,7 @@
         <v>588</v>
       </c>
       <c r="K280" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L280" s="18"/>
       <c r="M280" s="18">
@@ -64672,7 +64673,7 @@
         <v>959</v>
       </c>
       <c r="D281" s="18" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="E281" s="18">
         <v>4.1700000000000001E-2</v>
@@ -64691,7 +64692,7 @@
         <v>588</v>
       </c>
       <c r="K281" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L281" s="18"/>
       <c r="M281" s="18">
@@ -64714,7 +64715,7 @@
         <v>959</v>
       </c>
       <c r="D282" s="18" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E282" s="18">
         <v>5.5800000000000002E-2</v>
@@ -64733,7 +64734,7 @@
         <v>588</v>
       </c>
       <c r="K282" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L282" s="18"/>
       <c r="M282" s="18">
@@ -64756,7 +64757,7 @@
         <v>959</v>
       </c>
       <c r="D283" s="18" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E283" s="18">
         <v>4.0500000000000001E-2</v>
@@ -64775,7 +64776,7 @@
         <v>588</v>
       </c>
       <c r="K283" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L283" s="18"/>
       <c r="M283" s="18">
@@ -64798,7 +64799,7 @@
         <v>959</v>
       </c>
       <c r="D284" s="18" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="E284" s="18">
         <v>5.0180000000000002E-2</v>
@@ -64817,7 +64818,7 @@
         <v>588</v>
       </c>
       <c r="K284" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L284" s="18"/>
       <c r="M284" s="18">
@@ -64840,7 +64841,7 @@
         <v>959</v>
       </c>
       <c r="D285" s="18" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="E285" s="18">
         <v>2.5116699999999999E-2</v>
@@ -64850,7 +64851,7 @@
       </c>
       <c r="G285" s="18"/>
       <c r="H285" s="18" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="I285" s="18" t="s">
         <v>69</v>
@@ -64859,7 +64860,7 @@
         <v>588</v>
       </c>
       <c r="K285" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L285" s="18"/>
       <c r="M285" s="18">
@@ -64882,7 +64883,7 @@
         <v>959</v>
       </c>
       <c r="D286" s="18" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="E286" s="18">
         <v>3.0099999999999998E-2</v>
@@ -64901,7 +64902,7 @@
         <v>588</v>
       </c>
       <c r="K286" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L286" s="18"/>
       <c r="M286" s="18">
@@ -64924,7 +64925,7 @@
         <v>959</v>
       </c>
       <c r="D287" s="18" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="E287" s="18">
         <v>1.9356700000000001E-2</v>
@@ -64943,7 +64944,7 @@
         <v>588</v>
       </c>
       <c r="K287" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L287" s="18"/>
       <c r="M287" s="18">
@@ -64966,7 +64967,7 @@
         <v>959</v>
       </c>
       <c r="D288" s="18" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="E288" s="18">
         <v>1.2555E-2</v>
@@ -64985,7 +64986,7 @@
         <v>588</v>
       </c>
       <c r="K288" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L288" s="18"/>
       <c r="M288" s="18">
@@ -65008,7 +65009,7 @@
         <v>959</v>
       </c>
       <c r="D289" s="18" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="E289" s="18">
         <v>1.5903299999999999E-2</v>
@@ -65027,7 +65028,7 @@
         <v>588</v>
       </c>
       <c r="K289" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L289" s="18"/>
       <c r="M289" s="18">
@@ -65050,7 +65051,7 @@
         <v>959</v>
       </c>
       <c r="D290" s="18" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="E290" s="18">
         <v>2.53E-2</v>
@@ -65069,7 +65070,7 @@
         <v>588</v>
       </c>
       <c r="K290" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L290" s="18"/>
       <c r="M290" s="18">
@@ -65092,7 +65093,7 @@
         <v>959</v>
       </c>
       <c r="D291" s="18" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="E291" s="18">
         <v>1.84E-2</v>
@@ -65111,7 +65112,7 @@
         <v>588</v>
       </c>
       <c r="K291" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L291" s="18"/>
       <c r="M291" s="18">
@@ -65134,7 +65135,7 @@
         <v>959</v>
       </c>
       <c r="D292" s="18" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="E292" s="18">
         <v>7.9000000000000008E-3</v>
@@ -65153,7 +65154,7 @@
         <v>588</v>
       </c>
       <c r="K292" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L292" s="18"/>
       <c r="M292" s="18">
@@ -65176,7 +65177,7 @@
         <v>959</v>
       </c>
       <c r="D293" s="18" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="E293" s="18">
         <v>3.0999999999999999E-3</v>
@@ -65195,7 +65196,7 @@
         <v>588</v>
       </c>
       <c r="K293" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L293" s="18"/>
       <c r="M293" s="18">
@@ -65218,7 +65219,7 @@
         <v>959</v>
       </c>
       <c r="D294" s="18" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="E294" s="18">
         <v>0.01</v>
@@ -65237,7 +65238,7 @@
         <v>588</v>
       </c>
       <c r="K294" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L294" s="18"/>
       <c r="M294" s="18">
@@ -65260,7 +65261,7 @@
         <v>959</v>
       </c>
       <c r="D295" s="18" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="E295" s="18">
         <v>1.5699999999999999E-2</v>
@@ -65279,7 +65280,7 @@
         <v>588</v>
       </c>
       <c r="K295" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L295" s="18"/>
       <c r="M295" s="18">
@@ -65302,7 +65303,7 @@
         <v>959</v>
       </c>
       <c r="D296" s="18" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="E296" s="18">
         <v>1.8100000000000002E-2</v>
@@ -65321,7 +65322,7 @@
         <v>588</v>
       </c>
       <c r="K296" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L296" s="18"/>
       <c r="M296" s="18">
@@ -65344,7 +65345,7 @@
         <v>959</v>
       </c>
       <c r="D297" s="18" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="E297" s="18">
         <v>9.1999999999999998E-3</v>
@@ -65363,7 +65364,7 @@
         <v>588</v>
       </c>
       <c r="K297" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L297" s="18"/>
       <c r="M297" s="18">
@@ -65386,7 +65387,7 @@
         <v>959</v>
       </c>
       <c r="D298" s="18" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="E298" s="18">
         <v>8.2000000000000007E-3</v>
@@ -65405,7 +65406,7 @@
         <v>588</v>
       </c>
       <c r="K298" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L298" s="18"/>
       <c r="M298" s="18">
@@ -65428,7 +65429,7 @@
         <v>959</v>
       </c>
       <c r="D299" s="18" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="E299" s="18">
         <v>2.6200000000000001E-2</v>
@@ -65447,7 +65448,7 @@
         <v>588</v>
       </c>
       <c r="K299" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L299" s="18"/>
       <c r="M299" s="18">
@@ -65470,7 +65471,7 @@
         <v>959</v>
       </c>
       <c r="D300" s="18" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="E300" s="18">
         <v>5.3100000000000001E-2</v>
@@ -65489,7 +65490,7 @@
         <v>588</v>
       </c>
       <c r="K300" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L300" s="18"/>
       <c r="M300" s="18">
@@ -65512,7 +65513,7 @@
         <v>959</v>
       </c>
       <c r="D301" s="18" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="E301" s="18">
         <v>2.4199999999999999E-2</v>
@@ -65531,7 +65532,7 @@
         <v>588</v>
       </c>
       <c r="K301" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L301" s="18"/>
       <c r="M301" s="18">
@@ -65554,7 +65555,7 @@
         <v>959</v>
       </c>
       <c r="D302" s="18" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="E302" s="18">
         <v>3.9E-2</v>
@@ -65573,7 +65574,7 @@
         <v>588</v>
       </c>
       <c r="K302" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L302" s="18"/>
       <c r="M302" s="18">
@@ -65596,7 +65597,7 @@
         <v>959</v>
       </c>
       <c r="D303" s="18" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="E303" s="18">
         <v>7.8700000000000006E-2</v>
@@ -65615,7 +65616,7 @@
         <v>588</v>
       </c>
       <c r="K303" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L303" s="18"/>
       <c r="M303" s="18">
@@ -65638,7 +65639,7 @@
         <v>992</v>
       </c>
       <c r="D304" s="18" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="E304" s="18">
         <v>4.2368999999999997E-2</v>
@@ -65657,7 +65658,7 @@
         <v>588</v>
       </c>
       <c r="K304" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L304" s="18"/>
       <c r="M304" s="18">
@@ -65680,7 +65681,7 @@
         <v>992</v>
       </c>
       <c r="D305" s="18" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="E305" s="18">
         <v>5.8400000000000001E-2</v>
@@ -65699,7 +65700,7 @@
         <v>588</v>
       </c>
       <c r="K305" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L305" s="18"/>
       <c r="M305" s="18">
@@ -65722,7 +65723,7 @@
         <v>992</v>
       </c>
       <c r="D306" s="18" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="E306" s="18">
         <v>3.6600000000000001E-2</v>
@@ -65741,7 +65742,7 @@
         <v>588</v>
       </c>
       <c r="K306" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L306" s="18"/>
       <c r="M306" s="18">
@@ -65764,7 +65765,7 @@
         <v>992</v>
       </c>
       <c r="D307" s="18" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="E307" s="18">
         <v>4.5400000000000003E-2</v>
@@ -65783,7 +65784,7 @@
         <v>588</v>
       </c>
       <c r="K307" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L307" s="18"/>
       <c r="M307" s="18">
@@ -65806,7 +65807,7 @@
         <v>992</v>
       </c>
       <c r="D308" s="18" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="E308" s="18">
         <v>3.95E-2</v>
@@ -65825,7 +65826,7 @@
         <v>588</v>
       </c>
       <c r="K308" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L308" s="18"/>
       <c r="M308" s="18">
@@ -65848,7 +65849,7 @@
         <v>992</v>
       </c>
       <c r="D309" s="18" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="E309" s="18">
         <v>4.9599999999999998E-2</v>
@@ -65867,7 +65868,7 @@
         <v>588</v>
       </c>
       <c r="K309" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L309" s="18"/>
       <c r="M309" s="18">
@@ -65890,7 +65891,7 @@
         <v>992</v>
       </c>
       <c r="D310" s="18" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="E310" s="18">
         <v>1.4800000000000001E-2</v>
@@ -65909,7 +65910,7 @@
         <v>588</v>
       </c>
       <c r="K310" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L310" s="18"/>
       <c r="M310" s="18">
@@ -65932,7 +65933,7 @@
         <v>992</v>
       </c>
       <c r="D311" s="18" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="E311" s="18">
         <v>1.54E-2</v>
@@ -65951,7 +65952,7 @@
         <v>588</v>
       </c>
       <c r="K311" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L311" s="18"/>
       <c r="M311" s="18">
@@ -65974,7 +65975,7 @@
         <v>992</v>
       </c>
       <c r="D312" s="18" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="E312" s="18">
         <v>1.1299999999999999E-2</v>
@@ -65993,7 +65994,7 @@
         <v>588</v>
       </c>
       <c r="K312" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L312" s="18"/>
       <c r="M312" s="18">
@@ -66016,7 +66017,7 @@
         <v>992</v>
       </c>
       <c r="D313" s="18" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="E313" s="18">
         <v>2.0000000000000001E-4</v>
@@ -66035,7 +66036,7 @@
         <v>588</v>
       </c>
       <c r="K313" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L313" s="18"/>
       <c r="M313" s="18">
@@ -66058,7 +66059,7 @@
         <v>992</v>
       </c>
       <c r="D314" s="18" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E314" s="18">
         <v>3.3700000000000001E-2</v>
@@ -66077,7 +66078,7 @@
         <v>588</v>
       </c>
       <c r="K314" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L314" s="18"/>
       <c r="M314" s="18">
@@ -66100,7 +66101,7 @@
         <v>992</v>
       </c>
       <c r="D315" s="18" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="E315" s="18">
         <v>3.3099999999999997E-2</v>
@@ -66119,7 +66120,7 @@
         <v>588</v>
       </c>
       <c r="K315" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L315" s="18"/>
       <c r="M315" s="18">
@@ -66142,7 +66143,7 @@
         <v>992</v>
       </c>
       <c r="D316" s="18" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="E316" s="18">
         <v>5.1299999999999998E-2</v>
@@ -66161,7 +66162,7 @@
         <v>588</v>
       </c>
       <c r="K316" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L316" s="18"/>
       <c r="M316" s="18">
@@ -66184,7 +66185,7 @@
         <v>992</v>
       </c>
       <c r="D317" s="18" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="E317" s="18">
         <v>7.8700000000000006E-2</v>
@@ -66203,7 +66204,7 @@
         <v>588</v>
       </c>
       <c r="K317" s="18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="L317" s="18"/>
       <c r="M317" s="18">
@@ -66218,6 +66219,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="I1:I317"/>
   <mergeCells count="15">
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:I1"/>
@@ -66283,11 +66285,11 @@
       </c>
       <c r="Q1" s="85"/>
       <c r="R1" s="75" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="S1" s="75"/>
       <c r="T1" s="75" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="U1" s="75"/>
       <c r="V1" s="75" t="s">
@@ -66339,16 +66341,16 @@
         <v>18</v>
       </c>
       <c r="R2" s="75" t="s">
+        <v>1253</v>
+      </c>
+      <c r="S2" s="75" t="s">
         <v>1254</v>
       </c>
-      <c r="S2" s="75" t="s">
+      <c r="T2" s="75" t="s">
+        <v>1253</v>
+      </c>
+      <c r="U2" s="75" t="s">
         <v>1255</v>
-      </c>
-      <c r="T2" s="75" t="s">
-        <v>1254</v>
-      </c>
-      <c r="U2" s="75" t="s">
-        <v>1256</v>
       </c>
       <c r="V2" s="75"/>
     </row>
@@ -66394,10 +66396,10 @@
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="8" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>1257</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>1258</v>
       </c>
       <c r="E4" s="28">
         <v>-3.7306023283371598E-2</v>
@@ -66406,7 +66408,7 @@
         <v>109.329478725182</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="H4" s="9" t="s">
         <v>28</v>
@@ -66421,7 +66423,7 @@
         <v>678</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="M4" s="9">
         <v>8</v>
@@ -66448,10 +66450,10 @@
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="8" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="E5" s="28">
         <v>-1.95937331633412E-2</v>
@@ -66475,7 +66477,7 @@
         <v>678</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="M5" s="9">
         <v>4</v>
@@ -66502,10 +66504,10 @@
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="8" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>1263</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>1264</v>
       </c>
       <c r="E6" s="28">
         <v>-3.9292421453211303E-2</v>
@@ -66529,7 +66531,7 @@
         <v>678</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="M6" s="9">
         <v>2</v>
@@ -66556,10 +66558,10 @@
       </c>
       <c r="B7" s="9"/>
       <c r="C7" s="8" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="E7" s="28">
         <v>-2.4664565600741799E-2</v>
@@ -66583,7 +66585,7 @@
         <v>678</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="M7" s="9">
         <v>2</v>
@@ -66592,7 +66594,7 @@
         <v>730</v>
       </c>
       <c r="O7" s="9" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="P7" s="9"/>
       <c r="Q7" s="9"/>
@@ -66610,10 +66612,10 @@
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="8" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="E8" s="28">
         <v>-2.5131079011639499E-2</v>
@@ -66637,7 +66639,7 @@
         <v>678</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="M8" s="9">
         <v>2</v>
@@ -66646,7 +66648,7 @@
         <v>730</v>
       </c>
       <c r="O8" s="9" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="P8" s="9"/>
       <c r="Q8" s="9"/>
@@ -66664,10 +66666,10 @@
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="8" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="E9" s="28">
         <v>-5.09894079828545E-2</v>
@@ -66691,7 +66693,7 @@
         <v>678</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="M9" s="9">
         <v>2</v>
@@ -66718,10 +66720,10 @@
       </c>
       <c r="B10" s="18"/>
       <c r="C10" s="8" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="E10" s="18">
         <v>-1.3611111111111109E-3</v>
@@ -66730,7 +66732,7 @@
         <v>109.33280555555559</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="H10" s="9" t="s">
         <v>78</v>
@@ -66763,7 +66765,7 @@
       <c r="T10" s="9"/>
       <c r="U10" s="9"/>
       <c r="V10" s="18" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="11" spans="1:22" ht="23">
@@ -66772,10 +66774,10 @@
       </c>
       <c r="B11" s="18"/>
       <c r="C11" s="8" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="E11" s="18">
         <v>5.681368E-3</v>
@@ -66784,7 +66786,7 @@
         <v>109.3097629</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>65</v>
@@ -66796,7 +66798,7 @@
         <v>588</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="L11" s="9">
         <v>386.5</v>
@@ -66813,11 +66815,11 @@
       <c r="R11" s="9"/>
       <c r="S11" s="9"/>
       <c r="T11" s="9" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="U11" s="9"/>
       <c r="V11" s="18" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="12" spans="1:22" ht="34.5">
@@ -66826,10 +66828,10 @@
       </c>
       <c r="B12" s="18"/>
       <c r="C12" s="8" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="E12" s="18">
         <v>-1.6083333333333331E-2</v>
@@ -66838,7 +66840,7 @@
         <v>109.3486944444444</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="H12" s="9" t="s">
         <v>88</v>
@@ -66871,7 +66873,7 @@
       <c r="T12" s="9"/>
       <c r="U12" s="9"/>
       <c r="V12" s="18" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="34.5">
@@ -66880,10 +66882,10 @@
       </c>
       <c r="B13" s="9"/>
       <c r="C13" s="8" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="E13" s="18">
         <v>-1.4874999999999999E-2</v>
@@ -66892,7 +66894,7 @@
         <v>109.3546083333333</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>85</v>
@@ -66925,7 +66927,7 @@
       <c r="T13" s="9"/>
       <c r="U13" s="9"/>
       <c r="V13" s="18" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="14" spans="1:22" ht="23">
@@ -66934,10 +66936,10 @@
       </c>
       <c r="B14" s="18"/>
       <c r="C14" s="8" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E14" s="18">
         <v>-2.472222222222222E-3</v>
@@ -66946,7 +66948,7 @@
         <v>109.36341666666669</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>85</v>
@@ -66979,7 +66981,7 @@
       <c r="T14" s="9"/>
       <c r="U14" s="9"/>
       <c r="V14" s="18" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="15" spans="1:22" ht="23">
@@ -66988,10 +66990,10 @@
       </c>
       <c r="B15" s="18"/>
       <c r="C15" s="8" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="E15" s="18">
         <v>-4.5275000000000003E-2</v>
@@ -67000,7 +67002,7 @@
         <v>109.3667972222222</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="H15" s="9" t="s">
         <v>68</v>
@@ -67029,11 +67031,11 @@
       <c r="R15" s="9"/>
       <c r="S15" s="9"/>
       <c r="T15" s="9" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="U15" s="9"/>
       <c r="V15" s="18" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="16" spans="1:22" ht="23">
@@ -67042,10 +67044,10 @@
       </c>
       <c r="B16" s="18"/>
       <c r="C16" s="8" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="E16" s="18">
         <v>-5.4226999999999997E-2</v>
@@ -67054,10 +67056,10 @@
         <v>109.372108</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="I16" s="9" t="s">
         <v>69</v>
@@ -67083,11 +67085,11 @@
       <c r="R16" s="9"/>
       <c r="S16" s="9"/>
       <c r="T16" s="9" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="U16" s="9"/>
       <c r="V16" s="18" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="34.5">
@@ -67096,10 +67098,10 @@
       </c>
       <c r="B17" s="9"/>
       <c r="C17" s="8" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="E17" s="18">
         <v>-4.3363888888888889E-2</v>
@@ -67108,10 +67110,10 @@
         <v>109.3606972222222</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="I17" s="9" t="s">
         <v>69</v>
@@ -67120,7 +67122,7 @@
         <v>588</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="L17" s="9">
         <v>325</v>
@@ -67137,11 +67139,11 @@
       <c r="R17" s="9"/>
       <c r="S17" s="9"/>
       <c r="T17" s="9" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="U17" s="9"/>
       <c r="V17" s="18" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="18" spans="1:22" ht="34.5">
@@ -67150,10 +67152,10 @@
       </c>
       <c r="B18" s="18"/>
       <c r="C18" s="8" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="E18" s="18">
         <v>-3.6080555555555553E-2</v>
@@ -67162,10 +67164,10 @@
         <v>109.3525305555555</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="I18" s="9" t="s">
         <v>69</v>
@@ -67174,7 +67176,7 @@
         <v>588</v>
       </c>
       <c r="K18" s="9" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="L18" s="9">
         <v>252</v>
@@ -67191,11 +67193,11 @@
       <c r="R18" s="9"/>
       <c r="S18" s="9"/>
       <c r="T18" s="9" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="U18" s="9"/>
       <c r="V18" s="18" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="19" spans="1:22" ht="34.5">
@@ -67204,10 +67206,10 @@
       </c>
       <c r="B19" s="18"/>
       <c r="C19" s="8" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="E19" s="18">
         <v>-2.7588888888888888E-2</v>
@@ -67216,7 +67218,7 @@
         <v>109.35089444444441</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="H19" s="9" t="s">
         <v>164</v>
@@ -67245,11 +67247,11 @@
       <c r="R19" s="9"/>
       <c r="S19" s="9"/>
       <c r="T19" s="9" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="U19" s="9"/>
       <c r="V19" s="18" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="20" spans="1:22" ht="34.5">
@@ -67258,10 +67260,10 @@
       </c>
       <c r="B20" s="9"/>
       <c r="C20" s="8" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="E20" s="18">
         <v>-2.6594444444444441E-2</v>
@@ -67270,10 +67272,10 @@
         <v>109.3776361111111</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="I20" s="9" t="s">
         <v>69</v>
@@ -67303,7 +67305,7 @@
       <c r="T20" s="9"/>
       <c r="U20" s="9"/>
       <c r="V20" s="18" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="21" spans="1:22" ht="23">
@@ -67312,10 +67314,10 @@
       </c>
       <c r="B21" s="18"/>
       <c r="C21" s="8" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="E21" s="18">
         <v>-8.5055555555555561E-3</v>
@@ -67324,7 +67326,7 @@
         <v>109.3120555555556</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="H21" s="9" t="s">
         <v>135</v>
@@ -67353,11 +67355,11 @@
       <c r="R21" s="9"/>
       <c r="S21" s="9"/>
       <c r="T21" s="9" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="U21" s="9"/>
       <c r="V21" s="18" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="22" spans="1:22" ht="46">
@@ -67366,10 +67368,10 @@
       </c>
       <c r="B22" s="9"/>
       <c r="C22" s="8" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="E22" s="18">
         <v>-6.6555555555555561E-3</v>
@@ -67378,7 +67380,7 @@
         <v>109.3023222222222</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="H22" s="9" t="s">
         <v>81</v>
@@ -67390,7 +67392,7 @@
         <v>588</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="L22" s="9">
         <v>312.5</v>
@@ -67407,11 +67409,11 @@
       <c r="R22" s="9"/>
       <c r="S22" s="9"/>
       <c r="T22" s="9" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="U22" s="9"/>
       <c r="V22" s="18" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="46">
@@ -67420,10 +67422,10 @@
       </c>
       <c r="B23" s="18"/>
       <c r="C23" s="8" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="E23" s="18">
         <v>-1.3599999999999999E-2</v>
@@ -67432,7 +67434,7 @@
         <v>109.32073333333329</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="H23" s="9" t="s">
         <v>57</v>
@@ -67444,7 +67446,7 @@
         <v>588</v>
       </c>
       <c r="K23" s="9" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="L23" s="9">
         <v>721.62</v>
@@ -67459,11 +67461,11 @@
       <c r="R23" s="9"/>
       <c r="S23" s="9"/>
       <c r="T23" s="9" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="U23" s="9"/>
       <c r="V23" s="18" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="24" spans="1:22" ht="23">
@@ -67472,10 +67474,10 @@
       </c>
       <c r="B24" s="18"/>
       <c r="C24" s="8" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="E24" s="18">
         <v>-2.3930555555555559E-2</v>
@@ -67484,7 +67486,7 @@
         <v>109.2940722222222</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="H24" s="9" t="s">
         <v>90</v>
@@ -67513,11 +67515,11 @@
       <c r="R24" s="9"/>
       <c r="S24" s="9"/>
       <c r="T24" s="9" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="U24" s="9"/>
       <c r="V24" s="18" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="23">
@@ -67526,10 +67528,10 @@
       </c>
       <c r="B25" s="18"/>
       <c r="C25" s="8" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="E25" s="18">
         <v>-5.3363888888888891E-2</v>
@@ -67538,10 +67540,10 @@
         <v>109.3184055555556</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="I25" s="9" t="s">
         <v>29</v>
@@ -67567,11 +67569,11 @@
       <c r="R25" s="9"/>
       <c r="S25" s="9"/>
       <c r="T25" s="9" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="U25" s="9"/>
       <c r="V25" s="18" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="26" spans="1:22" ht="46">
@@ -67580,10 +67582,10 @@
       </c>
       <c r="B26" s="18"/>
       <c r="C26" s="8" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="E26" s="18">
         <v>-1.108333333333333E-2</v>
@@ -67592,7 +67594,7 @@
         <v>109.34288888888889</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="H26" s="9" t="s">
         <v>42</v>
@@ -67604,7 +67606,7 @@
         <v>588</v>
       </c>
       <c r="K26" s="9" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="L26" s="9">
         <v>315.3</v>
@@ -67614,18 +67616,18 @@
       </c>
       <c r="N26" s="9"/>
       <c r="O26" s="9" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="P26" s="18"/>
       <c r="Q26" s="18"/>
       <c r="R26" s="9"/>
       <c r="S26" s="9"/>
       <c r="T26" s="9" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="U26" s="9"/>
       <c r="V26" s="18" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="27" spans="1:22" ht="69">
@@ -67634,10 +67636,10 @@
       </c>
       <c r="B27" s="18"/>
       <c r="C27" s="8" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="E27" s="18">
         <v>-4.7805555555555559E-2</v>
@@ -67646,7 +67648,7 @@
         <v>109.35799166666671</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="H27" s="9" t="s">
         <v>784</v>
@@ -67658,7 +67660,7 @@
         <v>588</v>
       </c>
       <c r="K27" s="9" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="L27" s="9">
         <v>571</v>
@@ -67673,11 +67675,11 @@
       <c r="R27" s="9"/>
       <c r="S27" s="9"/>
       <c r="T27" s="9" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="U27" s="9"/>
       <c r="V27" s="18" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="34.5">
@@ -67686,10 +67688,10 @@
       </c>
       <c r="B28" s="18"/>
       <c r="C28" s="8" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="E28" s="18">
         <v>-7.407777777777777E-2</v>
@@ -67698,7 +67700,7 @@
         <v>109.34655833333331</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="H28" s="9" t="s">
         <v>108</v>
@@ -67731,7 +67733,7 @@
       <c r="T28" s="9"/>
       <c r="U28" s="9"/>
       <c r="V28" s="18" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="29" spans="1:22" ht="34.5">
@@ -67740,10 +67742,10 @@
       </c>
       <c r="B29" s="18"/>
       <c r="C29" s="45" t="s">
+        <v>1307</v>
+      </c>
+      <c r="D29" s="12" t="s">
         <v>1308</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>1309</v>
       </c>
       <c r="E29" s="24">
         <v>-4.15E-3</v>
@@ -67780,10 +67782,10 @@
       </c>
       <c r="B30" s="18"/>
       <c r="C30" s="45" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E30" s="24">
         <v>-1.073E-2</v>
@@ -67820,10 +67822,10 @@
       </c>
       <c r="B31" s="18"/>
       <c r="C31" s="45" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="E31" s="24">
         <v>-3.5799999999999998E-3</v>
@@ -67860,10 +67862,10 @@
       </c>
       <c r="B32" s="18"/>
       <c r="C32" s="45" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E32" s="24">
         <v>-4.1399999999999996E-3</v>
@@ -67900,10 +67902,10 @@
       </c>
       <c r="B33" s="18"/>
       <c r="C33" s="45" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="E33" s="24">
         <v>-1.265E-2</v>
@@ -67940,10 +67942,10 @@
       </c>
       <c r="B34" s="18"/>
       <c r="C34" s="45" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="E34" s="24">
         <v>-3.7200000000000002E-3</v>
@@ -67980,10 +67982,10 @@
       </c>
       <c r="B35" s="18"/>
       <c r="C35" s="45" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="E35" s="24">
         <v>-4.6600000000000001E-3</v>
@@ -68020,10 +68022,10 @@
       </c>
       <c r="B36" s="18"/>
       <c r="C36" s="45" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E36" s="24">
         <v>-1.264E-2</v>
@@ -68060,10 +68062,10 @@
       </c>
       <c r="B37" s="18"/>
       <c r="C37" s="45" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="E37" s="24">
         <v>-4.8199999999999996E-3</v>
@@ -68100,10 +68102,10 @@
       </c>
       <c r="B38" s="18"/>
       <c r="C38" s="45" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="E38" s="24">
         <v>-3.79E-3</v>
@@ -68140,10 +68142,10 @@
       </c>
       <c r="B39" s="18"/>
       <c r="C39" s="45" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="E39" s="24">
         <v>-1.8970000000000001E-2</v>
@@ -68180,10 +68182,10 @@
       </c>
       <c r="B40" s="18"/>
       <c r="C40" s="45" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="E40" s="24">
         <v>-1.222E-2</v>
@@ -68220,10 +68222,10 @@
       </c>
       <c r="B41" s="18"/>
       <c r="C41" s="45" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E41" s="24">
         <v>-3.2799999999999999E-3</v>
@@ -68260,10 +68262,10 @@
       </c>
       <c r="B42" s="18"/>
       <c r="C42" s="45" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="E42" s="24">
         <v>-5.1000000000000004E-3</v>
@@ -68300,10 +68302,10 @@
       </c>
       <c r="B43" s="18"/>
       <c r="C43" s="45" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E43" s="24">
         <v>-9.0200000000000002E-3</v>
@@ -68340,10 +68342,10 @@
       </c>
       <c r="B44" s="18"/>
       <c r="C44" s="45" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="E44" s="24">
         <v>-6.2700000000000004E-3</v>
@@ -68380,10 +68382,10 @@
       </c>
       <c r="B45" s="18"/>
       <c r="C45" s="45" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="D45" s="47" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="E45" s="24">
         <v>-5.0000000000000001E-3</v>
@@ -68420,10 +68422,10 @@
       </c>
       <c r="B46" s="18"/>
       <c r="C46" s="45" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="D46" s="18" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="E46" s="18">
         <v>-9.0581403224398605E-3</v>
@@ -68432,7 +68434,7 @@
         <v>109.334447184292</v>
       </c>
       <c r="G46" s="18" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="H46" s="18" t="s">
         <v>78</v>
@@ -68453,7 +68455,7 @@
         <v>4</v>
       </c>
       <c r="N46" s="18" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="O46" s="18">
         <v>2022</v>
@@ -68474,10 +68476,10 @@
       </c>
       <c r="B47" s="18"/>
       <c r="C47" s="45" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D47" s="18" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="E47" s="18">
         <v>-1.6127506931501698E-2</v>
@@ -68486,7 +68488,7 @@
         <v>109.34872462227599</v>
       </c>
       <c r="G47" s="18" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="H47" s="18" t="s">
         <v>88</v>
@@ -68501,13 +68503,13 @@
         <v>678</v>
       </c>
       <c r="L47" s="18" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="M47" s="18">
         <v>2</v>
       </c>
       <c r="N47" s="18" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="O47" s="18">
         <v>2026</v>
@@ -68528,10 +68530,10 @@
       </c>
       <c r="B48" s="18"/>
       <c r="C48" s="45" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D48" s="18" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="E48" s="18">
         <v>-2.4592909063837201E-3</v>
@@ -68540,7 +68542,7 @@
         <v>109.36364833802401</v>
       </c>
       <c r="G48" s="18" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="H48" s="18" t="s">
         <v>85</v>
@@ -68555,13 +68557,13 @@
         <v>678</v>
       </c>
       <c r="L48" s="18" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="M48" s="18">
         <v>2</v>
       </c>
       <c r="N48" s="18" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="O48" s="18">
         <v>2025</v>
@@ -68582,10 +68584,10 @@
       </c>
       <c r="B49" s="18"/>
       <c r="C49" s="45" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D49" s="18" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="E49" s="18">
         <v>-1.4751074355332201E-2</v>
@@ -68594,7 +68596,7 @@
         <v>109.35469980129901</v>
       </c>
       <c r="G49" s="18" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="H49" s="18" t="s">
         <v>85</v>
@@ -68609,13 +68611,13 @@
         <v>678</v>
       </c>
       <c r="L49" s="18" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="M49" s="18">
         <v>2</v>
       </c>
       <c r="N49" s="18" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="O49" s="18">
         <v>2025</v>
@@ -68636,10 +68638,10 @@
       </c>
       <c r="B50" s="18"/>
       <c r="C50" s="45" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D50" s="18" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="E50" s="18">
         <v>-1.24092327383439E-3</v>
@@ -68663,13 +68665,13 @@
         <v>678</v>
       </c>
       <c r="L50" s="18" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="M50" s="18">
         <v>2</v>
       </c>
       <c r="N50" s="18" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="O50" s="18">
         <v>2024</v>
@@ -68690,10 +68692,10 @@
       </c>
       <c r="B51" s="18"/>
       <c r="C51" s="45" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D51" s="18" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="E51" s="18">
         <v>5.8591767179658298E-3</v>
@@ -68702,7 +68704,7 @@
         <v>109.309824269063</v>
       </c>
       <c r="G51" s="18" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="H51" s="18" t="s">
         <v>65</v>
@@ -68723,7 +68725,7 @@
         <v>1</v>
       </c>
       <c r="N51" s="18" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="O51" s="18">
         <v>1990</v>
@@ -68740,11 +68742,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="V1:V3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="J1:O1"/>
@@ -68761,6 +68758,11 @@
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="C2:C3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="V1:V3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -68780,44 +68782,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" s="27" customFormat="1">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="89" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="90" t="s">
+      <c r="B1" s="93" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="91"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-      <c r="H1" s="92"/>
-      <c r="I1" s="93"/>
-      <c r="J1" s="90" t="s">
+      <c r="C1" s="86"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
+      <c r="H1" s="87"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="92"/>
-      <c r="L1" s="92"/>
-      <c r="M1" s="92"/>
-      <c r="N1" s="92"/>
-      <c r="O1" s="93"/>
-      <c r="P1" s="90" t="s">
+      <c r="K1" s="87"/>
+      <c r="L1" s="87"/>
+      <c r="M1" s="87"/>
+      <c r="N1" s="87"/>
+      <c r="O1" s="88"/>
+      <c r="P1" s="93" t="s">
         <v>3</v>
       </c>
-      <c r="Q1" s="92"/>
+      <c r="Q1" s="87"/>
       <c r="R1" s="75" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:18" s="27" customFormat="1" ht="36" customHeight="1">
-      <c r="A2" s="88"/>
-      <c r="B2" s="86" t="s">
+      <c r="A2" s="91"/>
+      <c r="B2" s="89" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="86" t="s">
+      <c r="C2" s="89" t="s">
         <v>674</v>
       </c>
-      <c r="D2" s="86" t="s">
+      <c r="D2" s="89" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="96" t="s">
@@ -68826,28 +68828,28 @@
       <c r="F2" s="96" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="86" t="s">
+      <c r="G2" s="89" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="86" t="s">
+      <c r="H2" s="89" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="86" t="s">
+      <c r="I2" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="90" t="s">
+      <c r="J2" s="93" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="93"/>
-      <c r="L2" s="91" t="s">
+      <c r="K2" s="88"/>
+      <c r="L2" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="92"/>
-      <c r="N2" s="93"/>
+      <c r="M2" s="87"/>
+      <c r="N2" s="88"/>
       <c r="O2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="86" t="s">
+      <c r="P2" s="89" t="s">
         <v>584</v>
       </c>
       <c r="Q2" s="94" t="s">
@@ -68856,15 +68858,15 @@
       <c r="R2" s="75"/>
     </row>
     <row r="3" spans="1:18" s="27" customFormat="1" ht="69">
-      <c r="A3" s="89"/>
-      <c r="B3" s="89"/>
-      <c r="C3" s="87"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="89"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="89"/>
-      <c r="I3" s="89"/>
+      <c r="A3" s="92"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="92"/>
       <c r="J3" s="1" t="s">
         <v>19</v>
       </c>
@@ -68883,7 +68885,7 @@
       <c r="O3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="P3" s="87"/>
+      <c r="P3" s="90"/>
       <c r="Q3" s="95"/>
       <c r="R3" s="75"/>
     </row>
@@ -68893,10 +68895,10 @@
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>1346</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>1347</v>
       </c>
       <c r="E4" s="23">
         <v>-3.305688317259E-2</v>
@@ -68920,7 +68922,7 @@
         <v>678</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="M4" s="4">
         <v>1</v>
@@ -68943,10 +68945,10 @@
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="E5" s="23">
         <v>-3.0528901570029E-2</v>
@@ -68970,7 +68972,7 @@
         <v>678</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="M5" s="4">
         <v>1</v>
@@ -68993,10 +68995,10 @@
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="E6" s="23">
         <v>-2.6897191063444299E-2</v>
@@ -69020,7 +69022,7 @@
         <v>678</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="M6" s="4">
         <v>1</v>
@@ -69043,16 +69045,16 @@
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>1351</v>
+      </c>
+      <c r="E7" s="23" t="s">
         <v>1352</v>
       </c>
-      <c r="E7" s="23" t="s">
+      <c r="F7" s="23" t="s">
         <v>1353</v>
-      </c>
-      <c r="F7" s="23" t="s">
-        <v>1354</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>677</v>
@@ -69070,7 +69072,7 @@
         <v>678</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="M7" s="4">
         <v>1</v>
@@ -69093,10 +69095,10 @@
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="E8" s="23">
         <v>-2.6451944370815599E-2</v>
@@ -69120,7 +69122,7 @@
         <v>678</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="M8" s="4">
         <v>1</v>
@@ -69143,10 +69145,10 @@
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E9" s="23">
         <v>-3.7100312511818501E-2</v>
@@ -69170,7 +69172,7 @@
         <v>678</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="M9" s="4">
         <v>2</v>
@@ -69193,10 +69195,10 @@
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="E10" s="23">
         <v>-3.3023355652657203E-2</v>
@@ -69220,7 +69222,7 @@
         <v>678</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="M10" s="4">
         <v>2</v>
@@ -69243,10 +69245,10 @@
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="E11" s="23">
         <v>-2.93004500107443E-2</v>
@@ -69270,7 +69272,7 @@
         <v>678</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="M11" s="4">
         <v>1</v>
@@ -69293,10 +69295,10 @@
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="E12" s="23">
         <v>-2.92521702510385E-2</v>
@@ -69320,7 +69322,7 @@
         <v>678</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="M12" s="4">
         <v>1</v>
@@ -69343,10 +69345,10 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="E13" s="23">
         <v>-4.8428432846192603E-2</v>
@@ -69370,7 +69372,7 @@
         <v>678</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="M13" s="4">
         <v>1</v>
@@ -69393,10 +69395,10 @@
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="E14" s="23">
         <v>-4.2825821525160103E-2</v>
@@ -69420,7 +69422,7 @@
         <v>678</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="M14" s="4">
         <v>1</v>
@@ -69443,10 +69445,10 @@
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="E15" s="23">
         <v>-5.9994818618451698E-2</v>
@@ -69470,7 +69472,7 @@
         <v>678</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="M15" s="4">
         <v>1</v>
@@ -69493,10 +69495,10 @@
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="E16" s="23">
         <v>-2.9933451252404E-2</v>
@@ -69520,7 +69522,7 @@
         <v>678</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="M16" s="4">
         <v>1</v>
@@ -69543,10 +69545,10 @@
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="E17" s="23">
         <v>-3.9020773734214503E-2</v>
@@ -69570,7 +69572,7 @@
         <v>678</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="M17" s="4">
         <v>1</v>
@@ -69593,10 +69595,10 @@
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="E18" s="23">
         <v>-3.8434027376651102E-2</v>
@@ -69620,7 +69622,7 @@
         <v>678</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="M18" s="4">
         <v>1</v>
@@ -69643,10 +69645,10 @@
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="E19" s="23">
         <v>-5.0111153476079098E-2</v>
@@ -69670,7 +69672,7 @@
         <v>678</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="M19" s="4">
         <v>1</v>
@@ -69679,7 +69681,7 @@
         <v>680</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="P19" s="4"/>
       <c r="Q19" s="48"/>
@@ -69693,10 +69695,10 @@
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="E20" s="23">
         <v>-4.9407450253117297E-2</v>
@@ -69720,7 +69722,7 @@
         <v>678</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="M20" s="4">
         <v>2</v>
@@ -69729,7 +69731,7 @@
         <v>680</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="P20" s="4"/>
       <c r="Q20" s="48"/>
@@ -69743,10 +69745,10 @@
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="E21" s="23">
         <v>-4.6866890051634601E-2</v>
@@ -69770,7 +69772,7 @@
         <v>678</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="M21" s="4">
         <v>1</v>
@@ -69779,7 +69781,7 @@
         <v>680</v>
       </c>
       <c r="O21" s="4" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="P21" s="4"/>
       <c r="Q21" s="48"/>
@@ -69793,10 +69795,10 @@
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="E22" s="23">
         <v>-4.5386311184041898E-2</v>
@@ -69820,7 +69822,7 @@
         <v>678</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="M22" s="4">
         <v>1</v>
@@ -69829,7 +69831,7 @@
         <v>680</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="P22" s="4"/>
       <c r="Q22" s="48"/>
@@ -69843,10 +69845,10 @@
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="E23" s="23">
         <v>-4.4334885592930397E-2</v>
@@ -69870,7 +69872,7 @@
         <v>678</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="M23" s="4">
         <v>1</v>
@@ -69879,7 +69881,7 @@
         <v>680</v>
       </c>
       <c r="O23" s="4" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="P23" s="4"/>
       <c r="Q23" s="48"/>
@@ -69893,10 +69895,10 @@
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="E24" s="23">
         <v>-4.3176171658923901E-2</v>
@@ -69920,7 +69922,7 @@
         <v>678</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="M24" s="4">
         <v>1</v>
@@ -69929,7 +69931,7 @@
         <v>680</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="P24" s="4"/>
       <c r="Q24" s="48"/>
@@ -69943,10 +69945,10 @@
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="E25" s="23">
         <v>-2.1591782213168102E-2</v>
@@ -69970,7 +69972,7 @@
         <v>678</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="M25" s="4">
         <v>2</v>
@@ -69993,10 +69995,10 @@
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="E26" s="23">
         <v>-4.1860253497890798E-2</v>
@@ -70020,7 +70022,7 @@
         <v>678</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="M26" s="4">
         <v>1</v>
@@ -70029,7 +70031,7 @@
         <v>680</v>
       </c>
       <c r="O26" s="4" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="P26" s="4"/>
       <c r="Q26" s="48"/>
@@ -70043,10 +70045,10 @@
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="E27" s="23">
         <v>-2.9150916876343101E-2</v>
@@ -70070,7 +70072,7 @@
         <v>678</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="M27" s="4">
         <v>1</v>
@@ -70079,7 +70081,7 @@
         <v>680</v>
       </c>
       <c r="O27" s="4" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="P27" s="4"/>
       <c r="Q27" s="48"/>
@@ -70093,10 +70095,10 @@
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="E28" s="23">
         <v>-2.3198546148105199E-2</v>
@@ -70120,7 +70122,7 @@
         <v>678</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="M28" s="4">
         <v>2</v>
@@ -70143,10 +70145,10 @@
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="E29" s="23">
         <v>-2.3848118571305501E-2</v>
@@ -70170,7 +70172,7 @@
         <v>678</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="M29" s="4">
         <v>1</v>
@@ -70179,7 +70181,7 @@
         <v>680</v>
       </c>
       <c r="O29" s="4" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="P29" s="4"/>
       <c r="Q29" s="48"/>
@@ -70193,10 +70195,10 @@
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="E30" s="23">
         <v>-2.6623807183040301E-2</v>
@@ -70220,7 +70222,7 @@
         <v>678</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="M30" s="4">
         <v>1</v>
@@ -70229,7 +70231,7 @@
         <v>680</v>
       </c>
       <c r="O30" s="4" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="P30" s="4"/>
       <c r="Q30" s="48"/>
@@ -70243,10 +70245,10 @@
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="E31" s="23">
         <v>-2.7306108144082498E-2</v>
@@ -70270,7 +70272,7 @@
         <v>678</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="M31" s="4">
         <v>1</v>
@@ -70279,7 +70281,7 @@
         <v>680</v>
       </c>
       <c r="O31" s="4" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="P31" s="4"/>
       <c r="Q31" s="48"/>
@@ -70293,10 +70295,10 @@
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="E32" s="23">
         <v>-2.03463571319339E-2</v>
@@ -70343,10 +70345,10 @@
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="E33" s="23">
         <v>-2.4389349275525499E-2</v>
@@ -70370,7 +70372,7 @@
         <v>678</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="M33" s="4">
         <v>1</v>
@@ -70393,10 +70395,10 @@
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="E34" s="23">
         <v>-2.4172066931815801E-2</v>
@@ -70420,7 +70422,7 @@
         <v>678</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="M34" s="4">
         <v>2</v>
@@ -70443,10 +70445,10 @@
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="E35" s="23">
         <v>-2.29838484346527E-2</v>
@@ -70470,7 +70472,7 @@
         <v>678</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="M35" s="4">
         <v>1</v>
@@ -70493,10 +70495,10 @@
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="E36" s="23">
         <v>-2.3058528451606899E-2</v>
@@ -70520,7 +70522,7 @@
         <v>678</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="M36" s="4">
         <v>1</v>
@@ -70543,10 +70545,10 @@
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="E37" s="23">
         <v>-2.55534044497241E-2</v>
@@ -70570,7 +70572,7 @@
         <v>678</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="M37" s="4">
         <v>1</v>
@@ -70579,7 +70581,7 @@
         <v>680</v>
       </c>
       <c r="O37" s="4" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="P37" s="4"/>
       <c r="Q37" s="48"/>
@@ -70593,10 +70595,10 @@
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E38" s="23">
         <v>-2.1931081476664199E-2</v>
@@ -70620,7 +70622,7 @@
         <v>678</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="M38" s="4">
         <v>1</v>
@@ -70643,10 +70645,10 @@
       </c>
       <c r="B39" s="17"/>
       <c r="C39" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="E39" s="31">
         <v>-1.92864235795423E-2</v>
@@ -70670,7 +70672,7 @@
         <v>678</v>
       </c>
       <c r="L39" s="17" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="M39" s="17">
         <v>1</v>
@@ -70693,10 +70695,10 @@
       </c>
       <c r="B40" s="9"/>
       <c r="C40" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D40" s="18" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="E40" s="24">
         <v>-6.8599999999999998E-3</v>
@@ -70729,10 +70731,10 @@
       </c>
       <c r="B41" s="9"/>
       <c r="C41" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D41" s="18" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="E41" s="24">
         <v>-3.29E-3</v>
@@ -70765,10 +70767,10 @@
       </c>
       <c r="B42" s="9"/>
       <c r="C42" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D42" s="18" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="E42" s="24">
         <v>-4.5199999999999997E-3</v>
@@ -70801,10 +70803,10 @@
       </c>
       <c r="B43" s="9"/>
       <c r="C43" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D43" s="18" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="E43" s="24">
         <v>-1.443E-2</v>
@@ -70837,10 +70839,10 @@
       </c>
       <c r="B44" s="9"/>
       <c r="C44" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D44" s="18" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="E44" s="24">
         <v>-1.1169999999999999E-2</v>
@@ -70873,10 +70875,10 @@
       </c>
       <c r="B45" s="9"/>
       <c r="C45" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D45" s="18" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="E45" s="24">
         <v>-5.7000000000000002E-3</v>
@@ -70909,10 +70911,10 @@
       </c>
       <c r="B46" s="9"/>
       <c r="C46" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D46" s="18" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="E46" s="24">
         <v>-2.5500000000000002E-3</v>
@@ -70945,10 +70947,10 @@
       </c>
       <c r="B47" s="9"/>
       <c r="C47" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D47" s="18" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="E47" s="24">
         <v>-4.9699999999999996E-3</v>
@@ -70981,10 +70983,10 @@
       </c>
       <c r="B48" s="9"/>
       <c r="C48" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D48" s="18" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="E48" s="24">
         <v>-8.7000000000000001E-4</v>
@@ -71017,10 +71019,10 @@
       </c>
       <c r="B49" s="9"/>
       <c r="C49" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D49" s="18" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="E49" s="24">
         <v>-7.9600000000000001E-3</v>
@@ -71053,10 +71055,10 @@
       </c>
       <c r="B50" s="9"/>
       <c r="C50" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D50" s="18" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="E50" s="24">
         <v>-6.9199999999999999E-3</v>
@@ -71089,10 +71091,10 @@
       </c>
       <c r="B51" s="9"/>
       <c r="C51" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D51" s="18" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="E51" s="24">
         <v>-8.8800000000000007E-3</v>
@@ -71125,10 +71127,10 @@
       </c>
       <c r="B52" s="9"/>
       <c r="C52" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D52" s="18" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="E52" s="24">
         <v>-8.2400000000000008E-3</v>
@@ -71161,10 +71163,10 @@
       </c>
       <c r="B53" s="9"/>
       <c r="C53" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D53" s="18" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="E53" s="24">
         <v>-1.278E-2</v>
@@ -71197,10 +71199,10 @@
       </c>
       <c r="B54" s="9"/>
       <c r="C54" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D54" s="18" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="E54" s="24">
         <v>-9.0699999999999999E-3</v>
@@ -71233,10 +71235,10 @@
       </c>
       <c r="B55" s="9"/>
       <c r="C55" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D55" s="18" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="E55" s="24">
         <v>-0.41952</v>
@@ -71269,10 +71271,10 @@
       </c>
       <c r="B56" s="9"/>
       <c r="C56" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D56" s="18" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="E56" s="24">
         <v>-6.77E-3</v>
@@ -71305,10 +71307,10 @@
       </c>
       <c r="B57" s="9"/>
       <c r="C57" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D57" s="18" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="E57" s="24">
         <v>-9.2099999999999994E-3</v>
@@ -71341,10 +71343,10 @@
       </c>
       <c r="B58" s="9"/>
       <c r="C58" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D58" s="18" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="E58" s="24">
         <v>-4.62E-3</v>
@@ -71377,10 +71379,10 @@
       </c>
       <c r="B59" s="9"/>
       <c r="C59" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D59" s="18" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="E59" s="24">
         <v>-7.9299999999999995E-3</v>
@@ -71413,10 +71415,10 @@
       </c>
       <c r="B60" s="9"/>
       <c r="C60" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D60" s="18" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="E60" s="24">
         <v>-1.01E-3</v>
@@ -71449,10 +71451,10 @@
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="2" t="s">
+        <v>1428</v>
+      </c>
+      <c r="D61" s="4" t="s">
         <v>1429</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>1430</v>
       </c>
       <c r="E61" s="23">
         <v>-2.7182175694019099E-2</v>
@@ -71476,7 +71478,7 @@
         <v>678</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="M61" s="4">
         <v>2</v>
@@ -71499,10 +71501,10 @@
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="2" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="E62" s="23">
         <v>-2.9823940361993598E-2</v>
@@ -71549,10 +71551,10 @@
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="2" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="E63" s="23">
         <v>-3.1931255091528297E-2</v>
@@ -71576,7 +71578,7 @@
         <v>678</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="M63" s="4">
         <v>1</v>
@@ -71599,10 +71601,10 @@
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="2" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="E64" s="23">
         <v>-4.8528322280354898E-2</v>
@@ -71626,7 +71628,7 @@
         <v>678</v>
       </c>
       <c r="L64" s="4" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="M64" s="4">
         <v>2</v>
@@ -71649,10 +71651,10 @@
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="2" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="E65" s="23">
         <v>-6.1779094808755097E-2</v>
@@ -71676,7 +71678,7 @@
         <v>678</v>
       </c>
       <c r="L65" s="4" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="M65" s="4">
         <v>2</v>
@@ -71685,7 +71687,7 @@
         <v>730</v>
       </c>
       <c r="O65" s="4" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="P65" s="4"/>
       <c r="Q65" s="48"/>
@@ -71699,10 +71701,10 @@
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="2" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E66" s="23">
         <v>-4.8171445719323899E-2</v>
@@ -71726,7 +71728,7 @@
         <v>678</v>
       </c>
       <c r="L66" s="4" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="M66" s="4">
         <v>1</v>
@@ -71735,7 +71737,7 @@
         <v>730</v>
       </c>
       <c r="O66" s="4" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="P66" s="4"/>
       <c r="Q66" s="48"/>
@@ -71749,10 +71751,10 @@
       </c>
       <c r="B67" s="4"/>
       <c r="C67" s="2" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="E67" s="23">
         <v>-2.85172450700832E-2</v>
@@ -71776,7 +71778,7 @@
         <v>678</v>
       </c>
       <c r="L67" s="4" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="M67" s="4">
         <v>2</v>
@@ -71799,10 +71801,10 @@
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="2" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="E68" s="23">
         <v>-2.4917720963034601E-2</v>
@@ -71826,7 +71828,7 @@
         <v>678</v>
       </c>
       <c r="L68" s="4" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="M68" s="4">
         <v>1</v>
@@ -71849,10 +71851,10 @@
       </c>
       <c r="B69" s="17"/>
       <c r="C69" s="2" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="D69" s="17" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="E69" s="31">
         <v>-2.1007700520245701E-2</v>
@@ -71876,7 +71878,7 @@
         <v>678</v>
       </c>
       <c r="L69" s="17" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="M69" s="17">
         <v>1</v>
@@ -71899,10 +71901,10 @@
       </c>
       <c r="B70" s="9"/>
       <c r="C70" s="2" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="D70" s="18" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="E70" s="24">
         <v>-5.1900000000000002E-3</v>
@@ -71935,10 +71937,10 @@
       </c>
       <c r="B71" s="9"/>
       <c r="C71" s="2" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="D71" s="18" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="E71" s="24">
         <v>-1.1690000000000001E-2</v>
@@ -71971,10 +71973,10 @@
       </c>
       <c r="B72" s="9"/>
       <c r="C72" s="2" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="D72" s="18" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="E72" s="24">
         <v>-8.8800000000000007E-3</v>
@@ -72007,10 +72009,10 @@
       </c>
       <c r="B73" s="18"/>
       <c r="C73" s="2" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="D73" s="18" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="E73" s="24">
         <v>-5.3099999999999996E-3</v>
@@ -72043,10 +72045,10 @@
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="2" t="s">
+        <v>1446</v>
+      </c>
+      <c r="D74" s="4" t="s">
         <v>1447</v>
-      </c>
-      <c r="D74" s="4" t="s">
-        <v>1448</v>
       </c>
       <c r="E74" s="23">
         <v>-2.8281828567388999E-2</v>
@@ -72067,10 +72069,10 @@
         <v>588</v>
       </c>
       <c r="K74" s="4" t="s">
+        <v>1448</v>
+      </c>
+      <c r="L74" s="4" t="s">
         <v>1449</v>
-      </c>
-      <c r="L74" s="4" t="s">
-        <v>1450</v>
       </c>
       <c r="M74" s="4">
         <v>1</v>
@@ -72093,10 +72095,10 @@
       </c>
       <c r="B75" s="4"/>
       <c r="C75" s="2" t="s">
+        <v>1450</v>
+      </c>
+      <c r="D75" s="4" t="s">
         <v>1451</v>
-      </c>
-      <c r="D75" s="4" t="s">
-        <v>1452</v>
       </c>
       <c r="E75" s="23">
         <v>-2.3534371787800299E-2</v>
@@ -72139,11 +72141,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="J1:O1"/>
     <mergeCell ref="R1:R3"/>
     <mergeCell ref="P2:P3"/>
     <mergeCell ref="Q2:Q3"/>
@@ -72156,6 +72153,11 @@
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="J1:O1"/>
   </mergeCells>
   <phoneticPr fontId="22" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -72287,10 +72289,10 @@
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="8" t="s">
+        <v>1452</v>
+      </c>
+      <c r="D4" s="12" t="s">
         <v>1453</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>1454</v>
       </c>
       <c r="E4" s="10">
         <v>-8.5000000000000006E-3</v>
@@ -72323,10 +72325,10 @@
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="8" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="E5" s="10">
         <v>-1.0109999999999999E-2</v>
@@ -72359,10 +72361,10 @@
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="8" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="E6" s="10">
         <v>-8.5699999999999995E-3</v>
@@ -72395,10 +72397,10 @@
       </c>
       <c r="B7" s="9"/>
       <c r="C7" s="8" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="E7" s="10">
         <v>-9.1199999999999996E-3</v>
@@ -72431,10 +72433,10 @@
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="8" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="E8" s="10">
         <v>-1.42E-3</v>
@@ -72467,10 +72469,10 @@
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="8" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="E9" s="10">
         <v>-1.6039999999999999E-2</v>
@@ -72503,10 +72505,10 @@
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="8" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="E10" s="10">
         <v>-8.8999999999999995E-4</v>
@@ -72539,10 +72541,10 @@
       </c>
       <c r="B11" s="9"/>
       <c r="C11" s="8" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="E11" s="10">
         <v>-2.2100000000000002E-3</v>
@@ -72571,11 +72573,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="J1:O1"/>
     <mergeCell ref="R1:R3"/>
     <mergeCell ref="P2:P3"/>
     <mergeCell ref="Q2:Q3"/>
@@ -72588,32 +72585,17 @@
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="J1:O1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="15954fb3-4959-4f5b-ae14-d7aa01180869">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="4ce1a36b-806a-4732-b893-33b689d3fa0c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokumen" ma:contentTypeID="0x010100CCD785251A4E724B934A12AB8BE46060" ma:contentTypeVersion="12" ma:contentTypeDescription="Buat sebuah dokumen baru." ma:contentTypeScope="" ma:versionID="5ae3aba09e4cbefebb89020ec97f4692">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="15954fb3-4959-4f5b-ae14-d7aa01180869" xmlns:ns3="4ce1a36b-806a-4732-b893-33b689d3fa0c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f158cec65280218b3e83bd78c7c2c412" ns2:_="" ns3:_="">
     <xsd:import namespace="15954fb3-4959-4f5b-ae14-d7aa01180869"/>
@@ -72814,32 +72796,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54AE2609-C9F0-494C-8358-7B12B3AE88B2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="4ce1a36b-806a-4732-b893-33b689d3fa0c"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="15954fb3-4959-4f5b-ae14-d7aa01180869"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{513001CF-EFDC-47ED-A578-E98A932356EC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="15954fb3-4959-4f5b-ae14-d7aa01180869">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="4ce1a36b-806a-4732-b893-33b689d3fa0c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBC33977-723A-400F-835A-24336D65E3F5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -72856,4 +72833,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{513001CF-EFDC-47ED-A578-E98A932356EC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54AE2609-C9F0-494C-8358-7B12B3AE88B2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="4ce1a36b-806a-4732-b893-33b689d3fa0c"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="15954fb3-4959-4f5b-ae14-d7aa01180869"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/processed/eksposur_pontianak_0423.xlsx
+++ b/data/processed/eksposur_pontianak_0423.xlsx
@@ -5732,6 +5732,24 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5741,26 +5759,8 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -35361,11 +35361,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:K1"/>
-    <mergeCell ref="L1:Q1"/>
-    <mergeCell ref="R1:S1"/>
     <mergeCell ref="T1:T3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="F2:F3"/>
@@ -35378,6 +35373,11 @@
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="E2:E3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:K1"/>
+    <mergeCell ref="L1:Q1"/>
+    <mergeCell ref="R1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -36489,13 +36489,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="K1:P1"/>
-    <mergeCell ref="T1:T3"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="Q1:S1"/>
-    <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:O2"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="I2:I3"/>
@@ -36507,6 +36500,13 @@
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="C2:C3"/>
+    <mergeCell ref="K1:P1"/>
+    <mergeCell ref="T1:T3"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="Q1:S1"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:O2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -36585,7 +36585,7 @@
       <c r="M2" s="78" t="s">
         <v>1496</v>
       </c>
-      <c r="N2" s="90" t="s">
+      <c r="N2" s="89" t="s">
         <v>1497</v>
       </c>
       <c r="O2" s="98"/>
@@ -36612,7 +36612,7 @@
       <c r="K3" s="80"/>
       <c r="L3" s="99"/>
       <c r="M3" s="78"/>
-      <c r="N3" s="90"/>
+      <c r="N3" s="89"/>
       <c r="O3" s="98"/>
     </row>
     <row r="4" spans="1:15" ht="69">
@@ -45968,6 +45968,9 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="K1:P1"/>
     <mergeCell ref="Q1:R1"/>
     <mergeCell ref="U1:U3"/>
     <mergeCell ref="B2:B3"/>
@@ -45983,9 +45986,6 @@
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="K2:L2"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="K1:P1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -48690,14 +48690,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="R2:R3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="S1:S3"/>
-    <mergeCell ref="K1:P1"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:O2"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:B3"/>
@@ -48708,6 +48700,14 @@
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="E2:E3"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="R2:R3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="S1:S3"/>
+    <mergeCell ref="K1:P1"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:O2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -51669,6 +51669,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="C2:C3"/>
     <mergeCell ref="R1:R3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:I1"/>
@@ -51685,7 +51686,6 @@
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="P2:P3"/>
     <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="C2:C3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -68746,11 +68746,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="V1:V3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="J1:O1"/>
@@ -68767,6 +68762,11 @@
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="C2:C3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="V1:V3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -68789,25 +68789,25 @@
       <c r="A1" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="90" t="s">
+      <c r="B1" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="95"/>
+      <c r="C1" s="90"/>
       <c r="D1" s="91"/>
       <c r="E1" s="91"/>
       <c r="F1" s="91"/>
       <c r="G1" s="91"/>
       <c r="H1" s="91"/>
-      <c r="I1" s="94"/>
-      <c r="J1" s="90" t="s">
+      <c r="I1" s="92"/>
+      <c r="J1" s="89" t="s">
         <v>2</v>
       </c>
       <c r="K1" s="91"/>
       <c r="L1" s="91"/>
       <c r="M1" s="91"/>
       <c r="N1" s="91"/>
-      <c r="O1" s="94"/>
-      <c r="P1" s="90" t="s">
+      <c r="O1" s="92"/>
+      <c r="P1" s="89" t="s">
         <v>3</v>
       </c>
       <c r="Q1" s="91"/>
@@ -68816,7 +68816,7 @@
       </c>
     </row>
     <row r="2" spans="1:18" s="27" customFormat="1" ht="36" customHeight="1">
-      <c r="A2" s="96"/>
+      <c r="A2" s="87"/>
       <c r="B2" s="86" t="s">
         <v>5</v>
       </c>
@@ -68826,10 +68826,10 @@
       <c r="D2" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="93" t="s">
+      <c r="E2" s="96" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="93" t="s">
+      <c r="F2" s="96" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="86" t="s">
@@ -68841,36 +68841,36 @@
       <c r="I2" s="86" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="90" t="s">
+      <c r="J2" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="94"/>
-      <c r="L2" s="95" t="s">
+      <c r="K2" s="92"/>
+      <c r="L2" s="90" t="s">
         <v>15</v>
       </c>
       <c r="M2" s="91"/>
-      <c r="N2" s="94"/>
+      <c r="N2" s="92"/>
       <c r="O2" s="1" t="s">
         <v>16</v>
       </c>
       <c r="P2" s="86" t="s">
         <v>584</v>
       </c>
-      <c r="Q2" s="88" t="s">
+      <c r="Q2" s="94" t="s">
         <v>18</v>
       </c>
       <c r="R2" s="75"/>
     </row>
     <row r="3" spans="1:18" s="27" customFormat="1" ht="69">
-      <c r="A3" s="92"/>
-      <c r="B3" s="92"/>
-      <c r="C3" s="87"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="92"/>
-      <c r="G3" s="92"/>
-      <c r="H3" s="92"/>
-      <c r="I3" s="92"/>
+      <c r="A3" s="88"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
       <c r="J3" s="1" t="s">
         <v>19</v>
       </c>
@@ -68889,8 +68889,8 @@
       <c r="O3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="P3" s="87"/>
-      <c r="Q3" s="89"/>
+      <c r="P3" s="93"/>
+      <c r="Q3" s="95"/>
       <c r="R3" s="75"/>
     </row>
     <row r="4" spans="1:18" ht="34.5">
@@ -72145,6 +72145,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="C2:C3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="J1:O1"/>
@@ -72161,7 +72162,6 @@
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="L2:N2"/>
-    <mergeCell ref="C2:C3"/>
   </mergeCells>
   <phoneticPr fontId="22" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -72577,6 +72577,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="C2:C3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="J1:O1"/>
@@ -72593,7 +72594,6 @@
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="L2:N2"/>
-    <mergeCell ref="C2:C3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -72801,6 +72801,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="15954fb3-4959-4f5b-ae14-d7aa01180869">
@@ -72809,15 +72818,6 @@
     <TaxCatchAll xmlns="4ce1a36b-806a-4732-b893-33b689d3fa0c" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -72840,6 +72840,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{513001CF-EFDC-47ED-A578-E98A932356EC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54AE2609-C9F0-494C-8358-7B12B3AE88B2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -72854,12 +72862,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{513001CF-EFDC-47ED-A578-E98A932356EC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>